--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Code\CSharp\semix\xuankaizhi\netcore_semix_cuga_calibration\Sources\Cuga-Calibration-Solution\Assets\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963153BC-C597-4110-8CC9-FA0FCD736367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17680" tabRatio="500" firstSheet="3"/>
   </bookViews>
   <sheets>
     <sheet name="SysUser" sheetId="1" r:id="rId1"/>
@@ -42,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="201">
   <si>
     <t>Id</t>
   </si>
@@ -71,42 +65,51 @@
     <t>Remark</t>
   </si>
   <si>
+    <t>SuperAdmin</t>
+  </si>
+  <si>
+    <t>Super Admin</t>
+  </si>
+  <si>
+    <t>xuankaizhi@semixchina.com</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Teaching</t>
+  </si>
+  <si>
+    <t>UserId</t>
+  </si>
+  <si>
+    <t>PostId</t>
+  </si>
+  <si>
+    <t>RoleId</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>ParentId</t>
+  </si>
+  <si>
+    <t>OrderNum</t>
+  </si>
+  <si>
+    <t>LeaderUserId</t>
+  </si>
+  <si>
+    <t>Headquarters</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
     <t>Admin</t>
   </si>
   <si>
-    <t>xuankaizhi@semixchina.com</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>UserId</t>
-  </si>
-  <si>
-    <t>PostId</t>
-  </si>
-  <si>
-    <t>RoleId</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>ParentId</t>
-  </si>
-  <si>
-    <t>OrderNum</t>
-  </si>
-  <si>
-    <t>LeaderUserId</t>
-  </si>
-  <si>
-    <t>Headquarters</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
     <t>Engineer</t>
   </si>
   <si>
@@ -119,6 +122,12 @@
     <t>All</t>
   </si>
   <si>
+    <t>SkipDependencyCheck</t>
+  </si>
+  <si>
+    <t>Skip Dependency Check</t>
+  </si>
+  <si>
     <t>MenuId</t>
   </si>
   <si>
@@ -399,6 +408,15 @@
   </si>
   <si>
     <t>CugaCalibration.ViewModels.Optics.OpticsROOSViewModel</t>
+  </si>
+  <si>
+    <t>Fourier</t>
+  </si>
+  <si>
+    <t>Pupil Camera Alignment</t>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Fourier.FourierPupilCameraAlignmentViewModel</t>
   </si>
   <si>
     <t>Title</t>
@@ -674,26 +692,18 @@
   <si>
     <t>CugaCalibration.ViewModels.Common.Windows.Management.Permission.RolesManagementViewModel</t>
   </si>
-  <si>
-    <t>Fourier</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Fourier</t>
-  </si>
-  <si>
-    <t>Pupil Camera Alignment</t>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Fourier.FourierPupilCameraAlignmentViewModel</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -704,6 +714,12 @@
       <b/>
       <sz val="18"/>
       <color rgb="FF44546A"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -721,32 +737,157 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color rgb="FF44546A"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -759,8 +900,194 @@
         <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -797,6 +1124,104 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -806,14 +1231,155 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyProtection="0">
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -824,7 +1390,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -836,176 +1402,106 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="6" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Excel Built-in Heading 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="超链接" xfId="1" builtinId="8"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Excel Built-in Heading 2" xfId="49"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -1016,7 +1512,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1044,40 +1540,154 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1136,7 +1746,7 @@
         <a:cs typeface=""/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1253,21 +1863,21 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I42"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="5" width="20.625" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="9" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="1" ht="22.5" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1296,487 +1906,502 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6">
+    <row r="2" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="7">
         <v>1</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="6">
+      <c r="E2" s="7"/>
+      <c r="F2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="7">
         <v>666666</v>
       </c>
-      <c r="H2" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-    </row>
-    <row r="4" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-    </row>
-    <row r="5" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-    </row>
-    <row r="6" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-    </row>
-    <row r="7" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-    </row>
-    <row r="8" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-    </row>
-    <row r="9" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-    </row>
-    <row r="10" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-    </row>
-    <row r="11" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-    </row>
-    <row r="12" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-    </row>
-    <row r="13" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-    </row>
-    <row r="14" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-    </row>
-    <row r="15" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-    </row>
-    <row r="16" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-    </row>
-    <row r="17" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-    </row>
-    <row r="18" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-    </row>
-    <row r="19" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-    </row>
-    <row r="20" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-    </row>
-    <row r="21" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-    </row>
-    <row r="22" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-    </row>
-    <row r="23" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-    </row>
-    <row r="24" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-    </row>
-    <row r="25" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-    </row>
-    <row r="26" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-    </row>
-    <row r="27" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-    </row>
-    <row r="28" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-    </row>
-    <row r="29" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-    </row>
-    <row r="30" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-    </row>
-    <row r="31" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-    </row>
-    <row r="32" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-    </row>
-    <row r="33" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-    </row>
-    <row r="34" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-    </row>
-    <row r="35" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-    </row>
-    <row r="36" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="9"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-    </row>
-    <row r="37" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="9"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-    </row>
-    <row r="38" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="9"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-    </row>
-    <row r="39" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="9"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="9"/>
-    </row>
-    <row r="40" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="9"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="9"/>
-    </row>
-    <row r="41" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="9"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
-    </row>
-    <row r="42" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="9"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="9"/>
+      <c r="H2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A3" s="8">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="8">
+        <v>1</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="7">
+        <v>666666</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+    </row>
+    <row r="5" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+    </row>
+    <row r="6" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+    </row>
+    <row r="7" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+    </row>
+    <row r="8" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+    </row>
+    <row r="9" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+    </row>
+    <row r="10" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+    </row>
+    <row r="11" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+    </row>
+    <row r="12" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+    </row>
+    <row r="13" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+    </row>
+    <row r="14" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+    </row>
+    <row r="15" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+    </row>
+    <row r="16" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+    </row>
+    <row r="17" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+    </row>
+    <row r="18" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+    </row>
+    <row r="19" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+    </row>
+    <row r="20" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+    </row>
+    <row r="21" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+    </row>
+    <row r="22" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+    </row>
+    <row r="23" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+    </row>
+    <row r="24" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+    </row>
+    <row r="25" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+    </row>
+    <row r="26" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+    </row>
+    <row r="27" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+    </row>
+    <row r="28" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+    </row>
+    <row r="29" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+    </row>
+    <row r="30" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10"/>
+    </row>
+    <row r="31" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
+    </row>
+    <row r="32" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="10"/>
+    </row>
+    <row r="33" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
+    </row>
+    <row r="34" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A34" s="10"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
+    </row>
+    <row r="35" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
+    </row>
+    <row r="36" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A36" s="10"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
+    </row>
+    <row r="37" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A37" s="10"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
+    </row>
+    <row r="38" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A38" s="10"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="10"/>
+    </row>
+    <row r="39" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A39" s="10"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="10"/>
+    </row>
+    <row r="40" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A40" s="10"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="10"/>
+      <c r="I40" s="10"/>
+    </row>
+    <row r="41" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A41" s="10"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="10"/>
+    </row>
+    <row r="42" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A42" s="10"/>
+      <c r="B42" s="10"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="F2" r:id="rId1" display="xuankaizhi@semixchina.com"/>
   </hyperlinks>
-  <pageMargins left="0.70069444444444495" right="0.70069444444444495" top="0.75208333333333299" bottom="0.75208333333333299" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="20.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="45.375" customWidth="1"/>
@@ -1787,41 +2412,41 @@
     <col min="9" max="9" width="28.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="15" customHeight="1" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" ht="15" customHeight="1" spans="1:9">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C2" s="3">
         <v>-1</v>
@@ -1831,20 +2456,20 @@
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" spans="1:9">
       <c r="A3" s="3">
         <v>11</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="C3" s="3">
         <v>1</v>
@@ -1854,20 +2479,20 @@
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" spans="1:9">
       <c r="A4" s="3">
         <v>1101</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C4" s="3">
         <v>11</v>
@@ -1877,22 +2502,22 @@
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" spans="1:9">
       <c r="A5" s="3">
         <v>1102</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="C5" s="3">
         <v>11</v>
@@ -1902,22 +2527,22 @@
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:9">
       <c r="A6" s="3">
         <v>1103</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C6" s="3">
         <v>11</v>
@@ -1927,22 +2552,22 @@
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" spans="1:9">
       <c r="A7" s="3">
         <v>1104</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="C7" s="3">
         <v>11</v>
@@ -1952,1463 +2577,1487 @@
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="1" ht="22.5" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="7">
         <v>1</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-    </row>
-    <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-    </row>
-    <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-    </row>
-    <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-    </row>
-    <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-    </row>
-    <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-    </row>
-    <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-    </row>
-    <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-    </row>
-    <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-    </row>
-    <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-    </row>
-    <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-    </row>
-    <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-    </row>
-    <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-    </row>
-    <row r="16" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-    </row>
-    <row r="17" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-    </row>
-    <row r="18" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-    </row>
-    <row r="19" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-    </row>
-    <row r="20" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-    </row>
-    <row r="21" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-    </row>
-    <row r="22" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-    </row>
-    <row r="23" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-    </row>
-    <row r="24" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-    </row>
-    <row r="25" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-    </row>
-    <row r="26" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-    </row>
-    <row r="27" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-    </row>
-    <row r="28" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-    </row>
-    <row r="29" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
+    <row r="3" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+    </row>
+    <row r="4" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+    </row>
+    <row r="5" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+    </row>
+    <row r="6" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+    </row>
+    <row r="7" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+    </row>
+    <row r="8" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+    </row>
+    <row r="9" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+    </row>
+    <row r="10" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+    </row>
+    <row r="11" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+    </row>
+    <row r="12" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+    </row>
+    <row r="13" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+    </row>
+    <row r="14" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+    </row>
+    <row r="15" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+    </row>
+    <row r="16" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+    </row>
+    <row r="17" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+    </row>
+    <row r="18" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+    </row>
+    <row r="19" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+    </row>
+    <row r="20" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+    </row>
+    <row r="21" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+    </row>
+    <row r="22" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+    </row>
+    <row r="23" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+    </row>
+    <row r="24" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+    </row>
+    <row r="25" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+    </row>
+    <row r="26" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+    </row>
+    <row r="27" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+    </row>
+    <row r="28" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+    </row>
+    <row r="29" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.75208333333333299" right="0.75208333333333299" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="1" ht="22.5" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="7">
         <v>1</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-    </row>
-    <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-    </row>
-    <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-    </row>
-    <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-    </row>
-    <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-    </row>
-    <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-    </row>
-    <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-    </row>
-    <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-    </row>
-    <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-    </row>
-    <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-    </row>
-    <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-    </row>
-    <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-    </row>
-    <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-    </row>
-    <row r="16" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-    </row>
-    <row r="17" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-    </row>
-    <row r="18" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-    </row>
-    <row r="19" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-    </row>
-    <row r="20" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-    </row>
-    <row r="21" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-    </row>
-    <row r="22" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-    </row>
-    <row r="23" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-    </row>
-    <row r="24" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-    </row>
-    <row r="25" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-    </row>
-    <row r="26" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-    </row>
-    <row r="27" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-    </row>
-    <row r="28" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-    </row>
-    <row r="29" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
+    <row r="3" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A3" s="8">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8">
+        <v>2</v>
+      </c>
+      <c r="C3" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+    </row>
+    <row r="5" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+    </row>
+    <row r="6" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+    </row>
+    <row r="7" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+    </row>
+    <row r="8" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+    </row>
+    <row r="9" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+    </row>
+    <row r="10" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+    </row>
+    <row r="11" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+    </row>
+    <row r="12" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+    </row>
+    <row r="13" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+    </row>
+    <row r="14" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+    </row>
+    <row r="15" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+    </row>
+    <row r="16" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+    </row>
+    <row r="17" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+    </row>
+    <row r="18" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+    </row>
+    <row r="19" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+    </row>
+    <row r="20" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+    </row>
+    <row r="21" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+    </row>
+    <row r="22" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+    </row>
+    <row r="23" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+    </row>
+    <row r="24" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+    </row>
+    <row r="25" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+    </row>
+    <row r="26" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+    </row>
+    <row r="27" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+    </row>
+    <row r="28" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+    </row>
+    <row r="29" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.75208333333333299" right="0.75208333333333299" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="6" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="1" ht="22.5" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6">
+    <row r="2" ht="20.1" customHeight="1" spans="1:6">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="6">
+      <c r="B2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="7">
         <v>-1</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="7">
         <v>0</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="7">
         <v>1</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-    </row>
-    <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-    </row>
-    <row r="5" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-    </row>
-    <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-    </row>
-    <row r="8" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-    </row>
-    <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-    </row>
-    <row r="10" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-    </row>
-    <row r="11" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-    </row>
-    <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-    </row>
-    <row r="13" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-    </row>
-    <row r="14" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-    </row>
-    <row r="15" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="16" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-    </row>
-    <row r="17" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-    </row>
-    <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-    </row>
-    <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-    </row>
-    <row r="20" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-    </row>
-    <row r="21" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-    </row>
-    <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-    </row>
-    <row r="23" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-    </row>
-    <row r="24" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
+      <c r="F2" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" ht="20.1" customHeight="1" spans="1:6">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+    </row>
+    <row r="4" ht="20.1" customHeight="1" spans="1:6">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+    </row>
+    <row r="5" ht="20.1" customHeight="1" spans="1:6">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+    </row>
+    <row r="6" ht="20.1" customHeight="1" spans="1:6">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+    </row>
+    <row r="7" ht="20.1" customHeight="1" spans="1:6">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+    </row>
+    <row r="8" ht="20.1" customHeight="1" spans="1:6">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+    </row>
+    <row r="9" ht="20.1" customHeight="1" spans="1:6">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+    </row>
+    <row r="10" ht="20.1" customHeight="1" spans="1:6">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+    </row>
+    <row r="11" ht="20.1" customHeight="1" spans="1:6">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+    </row>
+    <row r="12" ht="20.1" customHeight="1" spans="1:6">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+    </row>
+    <row r="13" ht="20.1" customHeight="1" spans="1:6">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+    </row>
+    <row r="14" ht="20.1" customHeight="1" spans="1:6">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+    </row>
+    <row r="15" ht="20.1" customHeight="1" spans="1:6">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+    </row>
+    <row r="16" ht="20.1" customHeight="1" spans="1:6">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+    </row>
+    <row r="17" ht="20.1" customHeight="1" spans="1:6">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+    </row>
+    <row r="18" ht="20.1" customHeight="1" spans="1:6">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+    </row>
+    <row r="19" ht="20.1" customHeight="1" spans="1:6">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+    </row>
+    <row r="20" ht="20.1" customHeight="1" spans="1:6">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+    </row>
+    <row r="21" ht="20.1" customHeight="1" spans="1:6">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+    </row>
+    <row r="22" ht="20.1" customHeight="1" spans="1:6">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+    </row>
+    <row r="23" ht="20.1" customHeight="1" spans="1:6">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+    </row>
+    <row r="24" ht="20.1" customHeight="1" spans="1:6">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.70069444444444495" right="0.70069444444444495" top="0.75208333333333299" bottom="0.75208333333333299" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="5" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="1" ht="22.5" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6">
+    <row r="2" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="6">
+      <c r="B2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="7">
         <v>0</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="6">
+      <c r="E2" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A3" s="7">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="6">
+      <c r="B3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="7">
         <v>1</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="6">
+      <c r="E3" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="7">
+      <c r="B4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="8">
         <v>2</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-    </row>
-    <row r="6" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-    </row>
-    <row r="7" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-    </row>
-    <row r="8" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-    </row>
-    <row r="9" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-    </row>
-    <row r="10" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-    </row>
-    <row r="11" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-    </row>
-    <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-    </row>
-    <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-    </row>
-    <row r="14" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-    </row>
-    <row r="15" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-    </row>
-    <row r="16" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-    </row>
-    <row r="17" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-    </row>
-    <row r="18" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-    </row>
-    <row r="19" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-    </row>
-    <row r="20" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-    </row>
-    <row r="23" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-    </row>
-    <row r="24" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-    </row>
-    <row r="25" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-    </row>
-    <row r="26" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-    </row>
-    <row r="27" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-    </row>
-    <row r="28" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-    </row>
-    <row r="29" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-    </row>
-    <row r="30" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-    </row>
-    <row r="31" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
+      <c r="E4" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+    </row>
+    <row r="7" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+    </row>
+    <row r="8" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+    </row>
+    <row r="9" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+    </row>
+    <row r="10" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+    </row>
+    <row r="11" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+    </row>
+    <row r="13" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+    </row>
+    <row r="14" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+    </row>
+    <row r="15" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+    </row>
+    <row r="16" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+    </row>
+    <row r="17" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+    </row>
+    <row r="18" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+    </row>
+    <row r="19" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+    </row>
+    <row r="20" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+    </row>
+    <row r="21" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+    </row>
+    <row r="22" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+    </row>
+    <row r="23" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+    </row>
+    <row r="24" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+    </row>
+    <row r="25" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+    </row>
+    <row r="26" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+    </row>
+    <row r="27" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+    </row>
+    <row r="28" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+    </row>
+    <row r="29" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+    </row>
+    <row r="30" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+    </row>
+    <row r="31" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.70069444444444495" right="0.70069444444444495" top="0.75208333333333299" bottom="0.75208333333333299" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="2" width="20.625" customWidth="1"/>
     <col min="3" max="3" width="24.25" customWidth="1"/>
     <col min="4" max="5" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="1" ht="22.5" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6">
+    <row r="2" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="6" t="s">
+      <c r="B2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="7">
+        <v>0</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="6">
-        <v>0</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="6">
+      <c r="C3" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="7">
+        <v>1</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A4" s="7">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="7">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="6">
-        <v>1</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="6">
+      <c r="E4" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A5" s="8">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="8">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="6">
-        <v>2</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-    </row>
-    <row r="6" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-    </row>
-    <row r="7" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-    </row>
-    <row r="8" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-    </row>
-    <row r="9" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-    </row>
-    <row r="10" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-    </row>
-    <row r="11" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-    </row>
-    <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-    </row>
-    <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-    </row>
-    <row r="14" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-    </row>
-    <row r="15" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-    </row>
-    <row r="16" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-    </row>
-    <row r="17" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-    </row>
-    <row r="18" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-    </row>
-    <row r="19" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-    </row>
-    <row r="20" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-    </row>
-    <row r="23" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-    </row>
-    <row r="24" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-    </row>
-    <row r="25" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-    </row>
-    <row r="26" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-    </row>
-    <row r="27" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-    </row>
-    <row r="28" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-    </row>
-    <row r="29" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-    </row>
-    <row r="30" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-    </row>
-    <row r="31" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
+      <c r="E5" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+    </row>
+    <row r="7" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+    </row>
+    <row r="8" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+    </row>
+    <row r="9" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+    </row>
+    <row r="10" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+    </row>
+    <row r="11" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+    </row>
+    <row r="13" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+    </row>
+    <row r="14" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+    </row>
+    <row r="15" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+    </row>
+    <row r="16" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+    </row>
+    <row r="17" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+    </row>
+    <row r="18" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+    </row>
+    <row r="19" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+    </row>
+    <row r="20" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+    </row>
+    <row r="21" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+    </row>
+    <row r="22" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+    </row>
+    <row r="23" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+    </row>
+    <row r="24" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+    </row>
+    <row r="25" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+    </row>
+    <row r="26" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+    </row>
+    <row r="27" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+    </row>
+    <row r="28" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+    </row>
+    <row r="29" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+    </row>
+    <row r="30" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+    </row>
+    <row r="31" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.70069444444444495" right="0.70069444444444495" top="0.75208333333333299" bottom="0.75208333333333299" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="1" ht="22.5" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-    </row>
-    <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-    </row>
-    <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-    </row>
-    <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-    </row>
-    <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-    </row>
-    <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-    </row>
-    <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-    </row>
-    <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-    </row>
-    <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-    </row>
-    <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-    </row>
-    <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-    </row>
-    <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-    </row>
-    <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-    </row>
-    <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-    </row>
-    <row r="16" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-    </row>
-    <row r="17" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-    </row>
-    <row r="18" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-    </row>
-    <row r="19" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-    </row>
-    <row r="20" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-    </row>
-    <row r="21" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-    </row>
-    <row r="22" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-    </row>
-    <row r="23" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-    </row>
-    <row r="24" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-    </row>
-    <row r="25" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-    </row>
-    <row r="26" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-    </row>
-    <row r="27" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-    </row>
-    <row r="28" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-    </row>
-    <row r="29" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-    </row>
-    <row r="30" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-    </row>
-    <row r="31" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
+    <row r="2" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+    </row>
+    <row r="3" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+    </row>
+    <row r="4" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+    </row>
+    <row r="5" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+    </row>
+    <row r="6" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+    </row>
+    <row r="7" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+    </row>
+    <row r="8" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+    </row>
+    <row r="9" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+    </row>
+    <row r="10" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+    </row>
+    <row r="11" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+    </row>
+    <row r="12" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+    </row>
+    <row r="13" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+    </row>
+    <row r="14" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+    </row>
+    <row r="15" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+    </row>
+    <row r="16" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+    </row>
+    <row r="17" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+    </row>
+    <row r="18" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+    </row>
+    <row r="19" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+    </row>
+    <row r="20" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+    </row>
+    <row r="21" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+    </row>
+    <row r="22" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+    </row>
+    <row r="23" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+    </row>
+    <row r="24" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+    </row>
+    <row r="25" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+    </row>
+    <row r="26" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+    </row>
+    <row r="27" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+    </row>
+    <row r="28" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+    </row>
+    <row r="29" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+    </row>
+    <row r="30" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+    </row>
+    <row r="31" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.75208333333333299" right="0.75208333333333299" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="1" ht="22.5" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
       <c r="C2" s="3"/>
     </row>
-    <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="7"/>
-      <c r="B3" s="6"/>
+    <row r="3" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A3" s="8"/>
+      <c r="B3" s="7"/>
       <c r="C3" s="3"/>
     </row>
-    <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
+    <row r="4" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
       <c r="C4" s="3"/>
     </row>
-    <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
+    <row r="5" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="7"/>
-      <c r="B6" s="6"/>
+    <row r="6" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A6" s="8"/>
+      <c r="B6" s="7"/>
       <c r="C6" s="3"/>
     </row>
-    <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
+    <row r="7" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
+    <row r="8" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7"/>
-      <c r="B9" s="6"/>
+    <row r="9" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A9" s="8"/>
+      <c r="B9" s="7"/>
       <c r="C9" s="3"/>
     </row>
-    <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
+    <row r="10" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
+    <row r="11" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
       <c r="C11" s="3"/>
     </row>
-    <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="7"/>
-      <c r="B12" s="6"/>
+    <row r="12" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A12" s="8"/>
+      <c r="B12" s="7"/>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
+    <row r="13" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
+    <row r="14" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
       <c r="C14" s="3"/>
     </row>
-    <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="7"/>
-      <c r="B15" s="6"/>
+    <row r="15" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A15" s="8"/>
+      <c r="B15" s="7"/>
       <c r="C15" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.75208333333333299" right="0.75208333333333299" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I93"/>
-  <sheetFormatPr defaultColWidth="19.75" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="19.75" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="19.75" style="1"/>
-    <col min="2" max="2" width="40.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.25" customWidth="1"/>
     <col min="3" max="6" width="19.75" style="1"/>
-    <col min="7" max="7" width="118.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="118.25" customWidth="1"/>
     <col min="8" max="8" width="17.625" customWidth="1"/>
-    <col min="9" max="9" width="40.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="40.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="1" ht="22.5" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C2" s="3">
         <v>-1</v>
@@ -3418,20 +4067,20 @@
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="3">
         <v>11</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C3" s="3">
         <v>1</v>
@@ -3441,20 +4090,20 @@
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="3">
         <v>1101</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C4" s="3">
         <v>11</v>
@@ -3464,22 +4113,22 @@
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="3">
         <v>1102</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C5" s="3">
         <v>11</v>
@@ -3489,22 +4138,22 @@
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="3">
         <v>1103</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C6" s="3">
         <v>11</v>
@@ -3514,22 +4163,22 @@
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="3">
         <v>12</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C7" s="3">
         <v>1</v>
@@ -3539,20 +4188,20 @@
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
       <c r="I7" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="3">
         <v>1201</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C8" s="3">
         <v>12</v>
@@ -3562,22 +4211,22 @@
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="3">
         <v>1202</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C9" s="3">
         <v>12</v>
@@ -3587,22 +4236,22 @@
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="3">
         <v>1203</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C10" s="3">
         <v>12</v>
@@ -3612,22 +4261,22 @@
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="3">
         <v>1204</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C11" s="3">
         <v>12</v>
@@ -3637,22 +4286,22 @@
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="3">
         <v>13</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C12" s="3">
         <v>1</v>
@@ -3662,20 +4311,20 @@
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="3">
         <v>1301</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C13" s="3">
         <v>13</v>
@@ -3685,22 +4334,22 @@
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="3">
         <v>1302</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C14" s="3">
         <v>13</v>
@@ -3710,22 +4359,22 @@
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H14" s="4"/>
       <c r="I14" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="3">
         <v>1303</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C15" s="3">
         <v>13</v>
@@ -3735,22 +4384,22 @@
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="3">
         <v>1304</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C16" s="3">
         <v>13</v>
@@ -3760,22 +4409,22 @@
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="3">
         <v>1305</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C17" s="3">
         <v>13</v>
@@ -3785,22 +4434,22 @@
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H17" s="5"/>
       <c r="I17" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="3">
         <v>1306</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C18" s="3">
         <v>13</v>
@@ -3810,22 +4459,22 @@
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="3">
         <v>14</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C19" s="3">
         <v>1</v>
@@ -3835,20 +4484,20 @@
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="3">
         <v>1401</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C20" s="3">
         <v>14</v>
@@ -3858,22 +4507,22 @@
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="3">
         <v>1402</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C21" s="3">
         <v>14</v>
@@ -3883,22 +4532,22 @@
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H21" s="4"/>
       <c r="I21" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="3">
         <v>1403</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C22" s="3">
         <v>14</v>
@@ -3908,22 +4557,22 @@
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H22" s="4"/>
       <c r="I22" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="3">
         <v>15</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C23" s="3">
         <v>1</v>
@@ -3933,20 +4582,20 @@
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="3">
         <v>1501</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C24" s="3">
         <v>15</v>
@@ -3956,22 +4605,22 @@
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="H24" s="4"/>
       <c r="I24" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="3">
         <v>1502</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C25" s="3">
         <v>15</v>
@@ -3981,22 +4630,22 @@
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H25" s="4"/>
       <c r="I25" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="3">
         <v>1503</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C26" s="3">
         <v>15</v>
@@ -4006,22 +4655,22 @@
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H26" s="4"/>
       <c r="I26" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="3">
         <v>1504</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C27" s="3">
         <v>15</v>
@@ -4031,22 +4680,22 @@
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H27" s="4"/>
       <c r="I27" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="3">
         <v>16</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C28" s="3">
         <v>1</v>
@@ -4056,20 +4705,20 @@
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" s="3">
         <v>1601</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C29" s="3">
         <v>16</v>
@@ -4079,22 +4728,22 @@
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H29" s="4"/>
       <c r="I29" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" s="3">
         <v>1602</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C30" s="3">
         <v>16</v>
@@ -4104,22 +4753,22 @@
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="H30" s="4"/>
       <c r="I30" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" s="3">
         <v>1603</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C31" s="3">
         <v>16</v>
@@ -4129,22 +4778,22 @@
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H31" s="4"/>
       <c r="I31" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" s="3">
         <v>1604</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C32" s="3">
         <v>16</v>
@@ -4154,22 +4803,22 @@
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="H32" s="4"/>
       <c r="I32" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" s="3">
         <v>17</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C33" s="3">
         <v>1</v>
@@ -4179,20 +4828,20 @@
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" s="3">
         <v>1701</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C34" s="3">
         <v>17</v>
@@ -4202,22 +4851,22 @@
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="H34" s="4"/>
       <c r="I34" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" s="3">
         <v>1702</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C35" s="3">
         <v>17</v>
@@ -4227,22 +4876,22 @@
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="H35" s="5"/>
       <c r="I35" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" s="3">
         <v>1703</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C36" s="3">
         <v>17</v>
@@ -4252,22 +4901,22 @@
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="H36" s="4"/>
       <c r="I36" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" s="3">
         <v>1704</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C37" s="3">
         <v>17</v>
@@ -4277,22 +4926,22 @@
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H37" s="4"/>
       <c r="I37" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" s="3">
         <v>1705</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C38" s="3">
         <v>17</v>
@@ -4302,22 +4951,22 @@
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="H38" s="4"/>
       <c r="I38" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" s="3">
         <v>1706</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C39" s="3">
         <v>17</v>
@@ -4327,22 +4976,22 @@
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H39" s="4"/>
       <c r="I39" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40" s="3">
         <v>1707</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C40" s="3">
         <v>17</v>
@@ -4352,22 +5001,22 @@
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="H40" s="4"/>
       <c r="I40" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
       <c r="A41" s="3">
         <v>1708</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C41" s="3">
         <v>17</v>
@@ -4377,22 +5026,22 @@
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="H41" s="4"/>
       <c r="I41" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42" s="3">
         <v>1709</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C42" s="3">
         <v>17</v>
@@ -4402,22 +5051,22 @@
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="H42" s="4"/>
       <c r="I42" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43" s="3">
         <v>18</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C43" s="3">
         <v>1</v>
@@ -4427,20 +5076,20 @@
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44" s="3">
         <v>1801</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C44" s="3">
         <v>18</v>
@@ -4450,22 +5099,22 @@
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="H44" s="4"/>
       <c r="I44" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" s="3">
         <v>1802</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C45" s="3">
         <v>18</v>
@@ -4475,22 +5124,22 @@
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="H45" s="4"/>
       <c r="I45" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46" s="3">
         <v>1803</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C46" s="3">
         <v>18</v>
@@ -4500,22 +5149,22 @@
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="H46" s="4"/>
       <c r="I46" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" s="3">
         <v>1804</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C47" s="3">
         <v>18</v>
@@ -4525,22 +5174,22 @@
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="H47" s="4"/>
       <c r="I47" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" s="3">
         <v>1805</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C48" s="3">
         <v>18</v>
@@ -4550,22 +5199,22 @@
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="H48" s="4"/>
       <c r="I48" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" s="3">
         <v>1806</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C49" s="3">
         <v>18</v>
@@ -4575,22 +5224,22 @@
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="H49" s="4"/>
       <c r="I49" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" s="3">
         <v>19</v>
       </c>
-      <c r="B50" s="10" t="s">
-        <v>193</v>
+      <c r="B50" s="6" t="s">
+        <v>124</v>
       </c>
       <c r="C50" s="3">
         <v>1</v>
@@ -4600,20 +5249,20 @@
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
       <c r="I50" s="4" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" s="3">
         <v>1901</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>195</v>
+        <v>125</v>
       </c>
       <c r="C51" s="3">
         <v>19</v>
@@ -4623,22 +5272,22 @@
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G51" s="10" t="s">
-        <v>196</v>
+        <v>39</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>126</v>
       </c>
       <c r="H51" s="4"/>
       <c r="I51" s="4" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52" s="3">
         <v>2</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C52" s="3">
         <v>-1</v>
@@ -4648,20 +5297,20 @@
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53" s="3">
         <v>21</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C53" s="3">
         <v>2</v>
@@ -4671,20 +5320,20 @@
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54" s="3">
         <v>2110</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="C54" s="3">
         <v>21</v>
@@ -4694,22 +5343,22 @@
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="H54" s="4"/>
       <c r="I54" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" s="3">
         <v>2111</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C55" s="3">
         <v>21</v>
@@ -4719,22 +5368,22 @@
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="H55" s="4"/>
       <c r="I55" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56" s="3">
         <v>2112</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="C56" s="3">
         <v>21</v>
@@ -4744,22 +5393,22 @@
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="H56" s="4"/>
       <c r="I56" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
       <c r="A57" s="3">
         <v>2113</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="C57" s="3">
         <v>21</v>
@@ -4769,22 +5418,22 @@
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="H57" s="4"/>
       <c r="I57" s="4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
       <c r="A58" s="3">
         <v>22</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C58" s="3">
         <v>2</v>
@@ -4794,20 +5443,20 @@
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
       <c r="A59" s="3">
         <v>2201</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="C59" s="3">
         <v>22</v>
@@ -4817,22 +5466,22 @@
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="H59" s="4"/>
       <c r="I59" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
       <c r="A60" s="3">
         <v>2202</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="C60" s="3">
         <v>22</v>
@@ -4842,22 +5491,22 @@
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="H60" s="4"/>
       <c r="I60" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
       <c r="A61" s="3">
         <v>2203</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C61" s="3">
         <v>22</v>
@@ -4867,22 +5516,22 @@
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="H61" s="4"/>
       <c r="I61" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
       <c r="A62" s="3">
         <v>23</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="C62" s="3">
         <v>2</v>
@@ -4892,20 +5541,20 @@
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
       <c r="I62" s="4" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
       <c r="A63" s="3">
         <v>2301</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="C63" s="3">
         <v>23</v>
@@ -4915,22 +5564,22 @@
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="H63" s="4"/>
       <c r="I63" s="4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
       <c r="A64" s="3">
         <v>2302</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C64" s="3">
         <v>23</v>
@@ -4940,20 +5589,20 @@
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
       <c r="A65" s="3">
         <v>23021</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="C65" s="3">
         <v>2302</v>
@@ -4963,22 +5612,22 @@
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="H65" s="4"/>
       <c r="I65" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
       <c r="A66" s="3">
         <v>23022</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C66" s="3">
         <v>2302</v>
@@ -4988,22 +5637,22 @@
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="H66" s="4"/>
       <c r="I66" s="4" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
       <c r="A67" s="3">
         <v>2303</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C67" s="3">
         <v>23</v>
@@ -5013,20 +5662,20 @@
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
       <c r="I67" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
       <c r="A68" s="3">
         <v>23031</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C68" s="3">
         <v>2303</v>
@@ -5036,22 +5685,22 @@
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="H68" s="4"/>
       <c r="I68" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
       <c r="A69" s="3">
         <v>2304</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C69" s="3">
         <v>23</v>
@@ -5061,20 +5710,20 @@
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G69" s="4"/>
       <c r="H69" s="4"/>
       <c r="I69" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
       <c r="A70" s="3">
         <v>23041</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="C70" s="3">
         <v>2304</v>
@@ -5084,22 +5733,22 @@
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="H70" s="4"/>
       <c r="I70" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
       <c r="A71" s="3">
         <v>23042</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="C71" s="3">
         <v>2304</v>
@@ -5109,22 +5758,22 @@
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="H71" s="4"/>
       <c r="I71" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
       <c r="A72" s="3">
         <v>23043</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="C72" s="3">
         <v>2304</v>
@@ -5134,22 +5783,22 @@
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="H72" s="4"/>
       <c r="I72" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
       <c r="A73" s="3">
         <v>23044</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C73" s="3">
         <v>2304</v>
@@ -5159,22 +5808,22 @@
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H73" s="4"/>
       <c r="I73" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
       <c r="A74" s="3">
         <v>23045</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="C74" s="3">
         <v>2304</v>
@@ -5184,22 +5833,22 @@
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H74" s="4"/>
       <c r="I74" s="4" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
       <c r="A75" s="3">
         <v>23046</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C75" s="3">
         <v>2304</v>
@@ -5209,22 +5858,22 @@
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="H75" s="4"/>
       <c r="I75" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
       <c r="A76" s="3">
         <v>23047</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="C76" s="3">
         <v>2304</v>
@@ -5234,22 +5883,22 @@
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H76" s="4"/>
       <c r="I76" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
       <c r="A77" s="3">
         <v>2305</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C77" s="3">
         <v>23</v>
@@ -5259,20 +5908,20 @@
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G77" s="4"/>
       <c r="H77" s="4"/>
       <c r="I77" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
       <c r="A78" s="3">
         <v>23051</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C78" s="3">
         <v>2305</v>
@@ -5282,22 +5931,22 @@
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="H78" s="4"/>
       <c r="I78" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
       <c r="A79" s="3">
         <v>23052</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="C79" s="3">
         <v>2305</v>
@@ -5307,22 +5956,22 @@
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="H79" s="4"/>
       <c r="I79" s="4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
       <c r="A80" s="3">
         <v>23053</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C80" s="3">
         <v>2305</v>
@@ -5332,22 +5981,22 @@
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="H80" s="4"/>
       <c r="I80" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
       <c r="A81" s="3">
         <v>23054</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C81" s="3">
         <v>2305</v>
@@ -5357,22 +6006,22 @@
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="H81" s="4"/>
       <c r="I81" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
       <c r="A82" s="3">
         <v>23055</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C82" s="3">
         <v>2305</v>
@@ -5382,22 +6031,22 @@
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="H82" s="4"/>
       <c r="I82" s="4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
       <c r="A83" s="3">
         <v>23056</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="C83" s="3">
         <v>2305</v>
@@ -5407,22 +6056,22 @@
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="H83" s="4"/>
       <c r="I83" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
       <c r="A84" s="3">
         <v>2306</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C84" s="3">
         <v>23</v>
@@ -5432,20 +6081,20 @@
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G84" s="4"/>
       <c r="H84" s="4"/>
       <c r="I84" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
       <c r="A85" s="3">
         <v>23061</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C85" s="3">
         <v>2306</v>
@@ -5455,22 +6104,22 @@
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="H85" s="4"/>
       <c r="I85" s="4" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
       <c r="A86" s="3">
         <v>24</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C86" s="3">
         <v>2</v>
@@ -5480,20 +6129,20 @@
       </c>
       <c r="E86" s="4"/>
       <c r="F86" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G86" s="4"/>
       <c r="H86" s="4"/>
       <c r="I86" s="4" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
       <c r="A87" s="3">
         <v>2401</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="C87" s="3">
         <v>24</v>
@@ -5503,22 +6152,22 @@
       </c>
       <c r="E87" s="4"/>
       <c r="F87" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H87" s="4"/>
       <c r="I87" s="4" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
       <c r="A88" s="3">
         <v>25</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C88" s="3">
         <v>2</v>
@@ -5528,20 +6177,20 @@
       </c>
       <c r="E88" s="4"/>
       <c r="F88" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G88" s="4"/>
       <c r="H88" s="4"/>
       <c r="I88" s="4" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
       <c r="A89" s="3">
         <v>2501</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C89" s="3">
         <v>25</v>
@@ -5551,22 +6200,22 @@
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="H89" s="3"/>
       <c r="I89" s="4" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
       <c r="A90" s="3">
         <v>2502</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="C90" s="3">
         <v>25</v>
@@ -5576,22 +6225,22 @@
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="H90" s="5"/>
       <c r="I90" s="5" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
       <c r="A91" s="3">
         <v>2503</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="C91" s="3">
         <v>25</v>
@@ -5601,22 +6250,22 @@
       </c>
       <c r="E91" s="3"/>
       <c r="F91" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H91" s="4"/>
       <c r="I91" s="4" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
       <c r="A92" s="3">
         <v>26</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C92" s="3">
         <v>2</v>
@@ -5626,20 +6275,20 @@
       </c>
       <c r="E92" s="3"/>
       <c r="F92" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G92" s="4"/>
       <c r="H92" s="4"/>
       <c r="I92" s="4" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
       <c r="A93" s="3">
         <v>2601</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C93" s="3">
         <v>26</v>
@@ -5649,19 +6298,19 @@
       </c>
       <c r="E93" s="4"/>
       <c r="F93" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="H93" s="4"/>
       <c r="I93" s="4" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.70069444444444495" right="0.70069444444444495" top="0.75208333333333299" bottom="0.75208333333333299" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Code\CSharp\semix\xuankaizhi\netcore_semix_cuga_calibration\Sources\Cuga-Calibration-Solution\Assets\Data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF94D977-196D-43DB-85BF-C910A4EE969D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17680" tabRatio="500" firstSheet="3"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SysUser" sheetId="1" r:id="rId1"/>
@@ -36,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="201">
   <si>
     <t>Id</t>
   </si>
@@ -558,30 +564,6 @@
     <t>CugaCalibration.ViewModels.Common.Windows.Tools.AODWaveform.ChirpGenerateAODWaveformWindowViewModel</t>
   </si>
   <si>
-    <t>Prescan AOD Waveform Electrode Offset V1</t>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Common.Windows.Tools.AODWaveform.V0PrescanAODWaveformElectrodeOffsetWindowViewModel</t>
-  </si>
-  <si>
-    <t>Chirp AOD Waveform Electrode Offset V1</t>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Common.Windows.Tools.AODWaveform.V0ChirpAODWaveformElectrodeOffsetWindowViewModel</t>
-  </si>
-  <si>
-    <t>Prescan AOD Waveform Electrode Offset V2</t>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Common.Windows.Tools.AODWaveform.PrescanAODWaveformElectrodeOffsetWindowViewModel</t>
-  </si>
-  <si>
-    <t>Chirp AOD Waveform Electrode Offset V2</t>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Common.Windows.Tools.AODWaveform.ChirpAODWaveformElectrodeOffsetWindowViewModel</t>
-  </si>
-  <si>
     <t>Chirp AOD Waveform Training</t>
   </si>
   <si>
@@ -691,19 +673,45 @@
   </si>
   <si>
     <t>CugaCalibration.ViewModels.Common.Windows.Management.Permission.RolesManagementViewModel</t>
+  </si>
+  <si>
+    <t>Prescan AOD Waveform Electrode Delay V1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Common.Windows.Tools.AODWaveform.V0PrescanAODWaveformElectrodeDelayWindowViewModel</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chirp AOD Waveform Electrode Delay V1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Common.Windows.Tools.AODWaveform.V0ChirpAODWaveformElectrodeDelayWindowViewModel</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prescan AOD Waveform Electrode Delay V2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Common.Windows.Tools.AODWaveform.PrescanAODWaveformElectrodeDelayWindowViewModel</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chirp AOD Waveform Electrode Delay V2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Common.Windows.Tools.AODWaveform.ChirpAODWaveformElectrodeDelayWindowViewModel</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -737,157 +745,27 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="13"/>
       <color rgb="FF44546A"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -900,194 +778,8 @@
         <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1124,104 +816,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -1231,166 +825,25 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1411,97 +864,170 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="6" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="3">
+    <cellStyle name="Excel Built-in Heading 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="Excel Built-in Heading 2" xfId="49"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -1512,7 +1038,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1540,154 +1066,40 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1746,7 +1158,7 @@
         <a:cs typeface=""/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1863,21 +1275,21 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I42"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="20.625" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="9" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:9">
+    <row r="1" spans="1:9" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1906,7 +1318,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="20.1" customHeight="1" spans="1:9">
+    <row r="2" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -1933,7 +1345,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="20.1" customHeight="1" spans="1:9">
+    <row r="3" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
         <v>2</v>
       </c>
@@ -1947,7 +1359,9 @@
         <v>13</v>
       </c>
       <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
+      <c r="F3" s="9" t="s">
+        <v>11</v>
+      </c>
       <c r="G3" s="7">
         <v>666666</v>
       </c>
@@ -1958,7 +1372,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" ht="20.1" customHeight="1" spans="1:9">
+    <row r="4" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -1969,7 +1383,7 @@
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
     </row>
-    <row r="5" ht="20.1" customHeight="1" spans="1:9">
+    <row r="5" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -1980,7 +1394,7 @@
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
     </row>
-    <row r="6" ht="20.1" customHeight="1" spans="1:9">
+    <row r="6" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -1991,7 +1405,7 @@
       <c r="H6" s="8"/>
       <c r="I6" s="8"/>
     </row>
-    <row r="7" ht="20.1" customHeight="1" spans="1:9">
+    <row r="7" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -2002,7 +1416,7 @@
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
     </row>
-    <row r="8" ht="20.1" customHeight="1" spans="1:9">
+    <row r="8" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -2013,7 +1427,7 @@
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
     </row>
-    <row r="9" ht="20.1" customHeight="1" spans="1:9">
+    <row r="9" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -2024,7 +1438,7 @@
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
     </row>
-    <row r="10" ht="20.1" customHeight="1" spans="1:9">
+    <row r="10" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -2035,7 +1449,7 @@
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
     </row>
-    <row r="11" ht="20.1" customHeight="1" spans="1:9">
+    <row r="11" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -2046,7 +1460,7 @@
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
     </row>
-    <row r="12" ht="20.1" customHeight="1" spans="1:9">
+    <row r="12" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -2057,7 +1471,7 @@
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
     </row>
-    <row r="13" ht="20.1" customHeight="1" spans="1:9">
+    <row r="13" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -2068,7 +1482,7 @@
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
     </row>
-    <row r="14" ht="20.1" customHeight="1" spans="1:9">
+    <row r="14" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -2079,7 +1493,7 @@
       <c r="H14" s="8"/>
       <c r="I14" s="8"/>
     </row>
-    <row r="15" ht="20.1" customHeight="1" spans="1:9">
+    <row r="15" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -2090,7 +1504,7 @@
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
     </row>
-    <row r="16" ht="20.1" customHeight="1" spans="1:9">
+    <row r="16" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -2101,7 +1515,7 @@
       <c r="H16" s="8"/>
       <c r="I16" s="8"/>
     </row>
-    <row r="17" ht="20.1" customHeight="1" spans="1:9">
+    <row r="17" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -2112,7 +1526,7 @@
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
     </row>
-    <row r="18" ht="20.1" customHeight="1" spans="1:9">
+    <row r="18" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -2123,7 +1537,7 @@
       <c r="H18" s="8"/>
       <c r="I18" s="8"/>
     </row>
-    <row r="19" ht="20.1" customHeight="1" spans="1:9">
+    <row r="19" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -2134,7 +1548,7 @@
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
     </row>
-    <row r="20" ht="20.1" customHeight="1" spans="1:9">
+    <row r="20" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -2145,7 +1559,7 @@
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
     </row>
-    <row r="21" ht="20.1" customHeight="1" spans="1:9">
+    <row r="21" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -2156,7 +1570,7 @@
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
     </row>
-    <row r="22" ht="20.1" customHeight="1" spans="1:9">
+    <row r="22" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -2167,7 +1581,7 @@
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
     </row>
-    <row r="23" ht="20.1" customHeight="1" spans="1:9">
+    <row r="23" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -2178,7 +1592,7 @@
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
     </row>
-    <row r="24" ht="20.1" customHeight="1" spans="1:9">
+    <row r="24" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -2189,7 +1603,7 @@
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
     </row>
-    <row r="25" ht="20.1" customHeight="1" spans="1:9">
+    <row r="25" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
@@ -2200,7 +1614,7 @@
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
     </row>
-    <row r="26" ht="20.1" customHeight="1" spans="1:9">
+    <row r="26" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -2211,7 +1625,7 @@
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
     </row>
-    <row r="27" ht="20.1" customHeight="1" spans="1:9">
+    <row r="27" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -2222,7 +1636,7 @@
       <c r="H27" s="8"/>
       <c r="I27" s="8"/>
     </row>
-    <row r="28" ht="20.1" customHeight="1" spans="1:9">
+    <row r="28" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -2233,7 +1647,7 @@
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
     </row>
-    <row r="29" ht="20.1" customHeight="1" spans="1:9">
+    <row r="29" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -2244,7 +1658,7 @@
       <c r="H29" s="8"/>
       <c r="I29" s="8"/>
     </row>
-    <row r="30" ht="20.1" customHeight="1" spans="1:9">
+    <row r="30" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="10"/>
       <c r="B30" s="10"/>
       <c r="C30" s="10"/>
@@ -2255,7 +1669,7 @@
       <c r="H30" s="10"/>
       <c r="I30" s="10"/>
     </row>
-    <row r="31" ht="20.1" customHeight="1" spans="1:9">
+    <row r="31" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="10"/>
       <c r="B31" s="10"/>
       <c r="C31" s="10"/>
@@ -2266,7 +1680,7 @@
       <c r="H31" s="10"/>
       <c r="I31" s="10"/>
     </row>
-    <row r="32" ht="20.1" customHeight="1" spans="1:9">
+    <row r="32" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="10"/>
       <c r="B32" s="10"/>
       <c r="C32" s="10"/>
@@ -2277,7 +1691,7 @@
       <c r="H32" s="10"/>
       <c r="I32" s="10"/>
     </row>
-    <row r="33" ht="20.1" customHeight="1" spans="1:9">
+    <row r="33" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
@@ -2288,7 +1702,7 @@
       <c r="H33" s="10"/>
       <c r="I33" s="10"/>
     </row>
-    <row r="34" ht="20.1" customHeight="1" spans="1:9">
+    <row r="34" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
@@ -2299,7 +1713,7 @@
       <c r="H34" s="10"/>
       <c r="I34" s="10"/>
     </row>
-    <row r="35" ht="20.1" customHeight="1" spans="1:9">
+    <row r="35" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="10"/>
@@ -2310,7 +1724,7 @@
       <c r="H35" s="10"/>
       <c r="I35" s="10"/>
     </row>
-    <row r="36" ht="20.1" customHeight="1" spans="1:9">
+    <row r="36" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="10"/>
@@ -2321,7 +1735,7 @@
       <c r="H36" s="10"/>
       <c r="I36" s="10"/>
     </row>
-    <row r="37" ht="20.1" customHeight="1" spans="1:9">
+    <row r="37" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="10"/>
@@ -2332,7 +1746,7 @@
       <c r="H37" s="10"/>
       <c r="I37" s="10"/>
     </row>
-    <row r="38" ht="20.1" customHeight="1" spans="1:9">
+    <row r="38" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="10"/>
@@ -2343,7 +1757,7 @@
       <c r="H38" s="10"/>
       <c r="I38" s="10"/>
     </row>
-    <row r="39" ht="20.1" customHeight="1" spans="1:9">
+    <row r="39" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="10"/>
@@ -2354,7 +1768,7 @@
       <c r="H39" s="10"/>
       <c r="I39" s="10"/>
     </row>
-    <row r="40" ht="20.1" customHeight="1" spans="1:9">
+    <row r="40" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="10"/>
@@ -2365,7 +1779,7 @@
       <c r="H40" s="10"/>
       <c r="I40" s="10"/>
     </row>
-    <row r="41" ht="20.1" customHeight="1" spans="1:9">
+    <row r="41" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="10"/>
@@ -2376,7 +1790,7 @@
       <c r="H41" s="10"/>
       <c r="I41" s="10"/>
     </row>
-    <row r="42" ht="20.1" customHeight="1" spans="1:9">
+    <row r="42" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="10"/>
@@ -2388,20 +1802,20 @@
       <c r="I42" s="10"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="xuankaizhi@semixchina.com"/>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{24ACA4B2-97CF-4E83-B373-7B5A2DFD4F1C}"/>
   </hyperlinks>
-  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.70069444444444495" right="0.70069444444444495" top="0.75208333333333299" bottom="0.75208333333333299" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="45.375" customWidth="1"/>
@@ -2412,7 +1826,7 @@
     <col min="9" max="9" width="28.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" spans="1:9">
+    <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2441,12 +1855,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:9">
+    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C2" s="3">
         <v>-1</v>
@@ -2461,15 +1875,15 @@
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" spans="1:9">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>11</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C3" s="3">
         <v>1</v>
@@ -2484,15 +1898,15 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" spans="1:9">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>1101</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C4" s="3">
         <v>11</v>
@@ -2505,19 +1919,19 @@
         <v>39</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" spans="1:9">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>1102</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C5" s="3">
         <v>11</v>
@@ -2530,19 +1944,19 @@
         <v>39</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" spans="1:9">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>1103</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C6" s="3">
         <v>11</v>
@@ -2555,19 +1969,19 @@
         <v>39</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" spans="1:9">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>1104</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="C7" s="3">
         <v>11</v>
@@ -2580,29 +1994,28 @@
         <v>39</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:3">
+    <row r="1" spans="1:3" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2613,7 +2026,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" ht="20.1" customHeight="1" spans="1:3">
+    <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -2624,158 +2037,163 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-    </row>
-    <row r="4" ht="20.1" customHeight="1" spans="1:3">
+    <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="7">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7">
+        <v>2</v>
+      </c>
+      <c r="C3" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
     </row>
-    <row r="5" ht="20.1" customHeight="1" spans="1:3">
+    <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
     </row>
-    <row r="6" ht="20.1" customHeight="1" spans="1:3">
+    <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
     </row>
-    <row r="7" ht="20.1" customHeight="1" spans="1:3">
+    <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
     </row>
-    <row r="8" ht="20.1" customHeight="1" spans="1:3">
+    <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
     </row>
-    <row r="9" ht="20.1" customHeight="1" spans="1:3">
+    <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
     </row>
-    <row r="10" ht="20.1" customHeight="1" spans="1:3">
+    <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
     </row>
-    <row r="11" ht="20.1" customHeight="1" spans="1:3">
+    <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
     </row>
-    <row r="12" ht="20.1" customHeight="1" spans="1:3">
+    <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
     </row>
-    <row r="13" ht="20.1" customHeight="1" spans="1:3">
+    <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
     </row>
-    <row r="14" ht="20.1" customHeight="1" spans="1:3">
+    <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
     </row>
-    <row r="15" ht="20.1" customHeight="1" spans="1:3">
+    <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
     </row>
-    <row r="16" ht="20.1" customHeight="1" spans="1:3">
+    <row r="16" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
     </row>
-    <row r="17" ht="20.1" customHeight="1" spans="1:3">
+    <row r="17" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
     </row>
-    <row r="18" ht="20.1" customHeight="1" spans="1:3">
+    <row r="18" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
     </row>
-    <row r="19" ht="20.1" customHeight="1" spans="1:3">
+    <row r="19" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
     </row>
-    <row r="20" ht="20.1" customHeight="1" spans="1:3">
+    <row r="20" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
     </row>
-    <row r="21" ht="20.1" customHeight="1" spans="1:3">
+    <row r="21" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
     </row>
-    <row r="22" ht="20.1" customHeight="1" spans="1:3">
+    <row r="22" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
     </row>
-    <row r="23" ht="20.1" customHeight="1" spans="1:3">
+    <row r="23" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
     </row>
-    <row r="24" ht="20.1" customHeight="1" spans="1:3">
+    <row r="24" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
     </row>
-    <row r="25" ht="20.1" customHeight="1" spans="1:3">
+    <row r="25" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
     </row>
-    <row r="26" ht="20.1" customHeight="1" spans="1:3">
+    <row r="26" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
     </row>
-    <row r="27" ht="20.1" customHeight="1" spans="1:3">
+    <row r="27" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
     </row>
-    <row r="28" ht="20.1" customHeight="1" spans="1:3">
+    <row r="28" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
     </row>
-    <row r="29" ht="20.1" customHeight="1" spans="1:3">
+    <row r="29" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
     </row>
   </sheetData>
-  <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.75208333333333299" right="0.75208333333333299" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:3">
+    <row r="1" spans="1:3" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2786,7 +2204,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" ht="20.1" customHeight="1" spans="1:3">
+    <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -2797,7 +2215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="20.1" customHeight="1" spans="1:3">
+    <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
         <v>2</v>
       </c>
@@ -2808,153 +2226,152 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" ht="20.1" customHeight="1" spans="1:3">
+    <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
     </row>
-    <row r="5" ht="20.1" customHeight="1" spans="1:3">
+    <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
     </row>
-    <row r="6" ht="20.1" customHeight="1" spans="1:3">
+    <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
     </row>
-    <row r="7" ht="20.1" customHeight="1" spans="1:3">
+    <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
     </row>
-    <row r="8" ht="20.1" customHeight="1" spans="1:3">
+    <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
     </row>
-    <row r="9" ht="20.1" customHeight="1" spans="1:3">
+    <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
     </row>
-    <row r="10" ht="20.1" customHeight="1" spans="1:3">
+    <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
     </row>
-    <row r="11" ht="20.1" customHeight="1" spans="1:3">
+    <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
     </row>
-    <row r="12" ht="20.1" customHeight="1" spans="1:3">
+    <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
     </row>
-    <row r="13" ht="20.1" customHeight="1" spans="1:3">
+    <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
     </row>
-    <row r="14" ht="20.1" customHeight="1" spans="1:3">
+    <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
     </row>
-    <row r="15" ht="20.1" customHeight="1" spans="1:3">
+    <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
     </row>
-    <row r="16" ht="20.1" customHeight="1" spans="1:3">
+    <row r="16" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
     </row>
-    <row r="17" ht="20.1" customHeight="1" spans="1:3">
+    <row r="17" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
     </row>
-    <row r="18" ht="20.1" customHeight="1" spans="1:3">
+    <row r="18" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
     </row>
-    <row r="19" ht="20.1" customHeight="1" spans="1:3">
+    <row r="19" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
     </row>
-    <row r="20" ht="20.1" customHeight="1" spans="1:3">
+    <row r="20" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
     </row>
-    <row r="21" ht="20.1" customHeight="1" spans="1:3">
+    <row r="21" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
     </row>
-    <row r="22" ht="20.1" customHeight="1" spans="1:3">
+    <row r="22" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
     </row>
-    <row r="23" ht="20.1" customHeight="1" spans="1:3">
+    <row r="23" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
     </row>
-    <row r="24" ht="20.1" customHeight="1" spans="1:3">
+    <row r="24" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
     </row>
-    <row r="25" ht="20.1" customHeight="1" spans="1:3">
+    <row r="25" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
     </row>
-    <row r="26" ht="20.1" customHeight="1" spans="1:3">
+    <row r="26" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
     </row>
-    <row r="27" ht="20.1" customHeight="1" spans="1:3">
+    <row r="27" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
     </row>
-    <row r="28" ht="20.1" customHeight="1" spans="1:3">
+    <row r="28" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
     </row>
-    <row r="29" ht="20.1" customHeight="1" spans="1:3">
+    <row r="29" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
     </row>
   </sheetData>
-  <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.75208333333333299" right="0.75208333333333299" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="6" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:6">
+    <row r="1" spans="1:6" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2974,7 +2391,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="20.1" customHeight="1" spans="1:6">
+    <row r="2" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -2994,7 +2411,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" ht="20.1" customHeight="1" spans="1:6">
+    <row r="3" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -3002,7 +2419,7 @@
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
     </row>
-    <row r="4" ht="20.1" customHeight="1" spans="1:6">
+    <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -3010,7 +2427,7 @@
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
     </row>
-    <row r="5" ht="20.1" customHeight="1" spans="1:6">
+    <row r="5" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -3018,7 +2435,7 @@
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" ht="20.1" customHeight="1" spans="1:6">
+    <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -3026,7 +2443,7 @@
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
     </row>
-    <row r="7" ht="20.1" customHeight="1" spans="1:6">
+    <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -3034,7 +2451,7 @@
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
     </row>
-    <row r="8" ht="20.1" customHeight="1" spans="1:6">
+    <row r="8" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -3042,7 +2459,7 @@
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" ht="20.1" customHeight="1" spans="1:6">
+    <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -3050,7 +2467,7 @@
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
     </row>
-    <row r="10" ht="20.1" customHeight="1" spans="1:6">
+    <row r="10" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -3058,7 +2475,7 @@
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" ht="20.1" customHeight="1" spans="1:6">
+    <row r="11" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -3066,7 +2483,7 @@
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
     </row>
-    <row r="12" ht="20.1" customHeight="1" spans="1:6">
+    <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -3074,7 +2491,7 @@
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
     </row>
-    <row r="13" ht="20.1" customHeight="1" spans="1:6">
+    <row r="13" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -3082,7 +2499,7 @@
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
     </row>
-    <row r="14" ht="20.1" customHeight="1" spans="1:6">
+    <row r="14" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -3090,7 +2507,7 @@
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
     </row>
-    <row r="15" ht="20.1" customHeight="1" spans="1:6">
+    <row r="15" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -3098,7 +2515,7 @@
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
     </row>
-    <row r="16" ht="20.1" customHeight="1" spans="1:6">
+    <row r="16" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -3106,7 +2523,7 @@
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
     </row>
-    <row r="17" ht="20.1" customHeight="1" spans="1:6">
+    <row r="17" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -3114,7 +2531,7 @@
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
     </row>
-    <row r="18" ht="20.1" customHeight="1" spans="1:6">
+    <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -3122,7 +2539,7 @@
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
     </row>
-    <row r="19" ht="20.1" customHeight="1" spans="1:6">
+    <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -3130,7 +2547,7 @@
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
     </row>
-    <row r="20" ht="20.1" customHeight="1" spans="1:6">
+    <row r="20" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -3138,7 +2555,7 @@
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
     </row>
-    <row r="21" ht="20.1" customHeight="1" spans="1:6">
+    <row r="21" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -3146,7 +2563,7 @@
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
     </row>
-    <row r="22" ht="20.1" customHeight="1" spans="1:6">
+    <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -3154,7 +2571,7 @@
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
     </row>
-    <row r="23" ht="20.1" customHeight="1" spans="1:6">
+    <row r="23" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -3162,7 +2579,7 @@
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
     </row>
-    <row r="24" ht="20.1" customHeight="1" spans="1:6">
+    <row r="24" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -3171,22 +2588,21 @@
       <c r="F24" s="8"/>
     </row>
   </sheetData>
-  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.70069444444444495" right="0.70069444444444495" top="0.75208333333333299" bottom="0.75208333333333299" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:5">
+    <row r="1" spans="1:5" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3203,7 +2619,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="20.1" customHeight="1" spans="1:5">
+    <row r="2" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -3220,7 +2636,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" ht="20.1" customHeight="1" spans="1:5">
+    <row r="3" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>2</v>
       </c>
@@ -3237,7 +2653,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" ht="20.1" customHeight="1" spans="1:5">
+    <row r="4" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>3</v>
       </c>
@@ -3254,189 +2670,189 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" ht="20.1" customHeight="1" spans="1:5">
+    <row r="5" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
     </row>
-    <row r="6" ht="20.1" customHeight="1" spans="1:5">
+    <row r="6" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
     </row>
-    <row r="7" ht="20.1" customHeight="1" spans="1:5">
+    <row r="7" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
     </row>
-    <row r="8" ht="20.1" customHeight="1" spans="1:5">
+    <row r="8" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
     </row>
-    <row r="9" ht="20.1" customHeight="1" spans="1:5">
+    <row r="9" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
     </row>
-    <row r="10" ht="20.1" customHeight="1" spans="1:5">
+    <row r="10" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
     </row>
-    <row r="11" ht="20.1" customHeight="1" spans="1:5">
+    <row r="11" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
     </row>
-    <row r="12" ht="20.1" customHeight="1" spans="1:5">
+    <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
     </row>
-    <row r="13" ht="20.1" customHeight="1" spans="1:5">
+    <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
     </row>
-    <row r="14" ht="20.1" customHeight="1" spans="1:5">
+    <row r="14" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
     </row>
-    <row r="15" ht="20.1" customHeight="1" spans="1:5">
+    <row r="15" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
     </row>
-    <row r="16" ht="20.1" customHeight="1" spans="1:5">
+    <row r="16" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
     </row>
-    <row r="17" ht="20.1" customHeight="1" spans="1:5">
+    <row r="17" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
     </row>
-    <row r="18" ht="20.1" customHeight="1" spans="1:5">
+    <row r="18" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
     </row>
-    <row r="19" ht="20.1" customHeight="1" spans="1:5">
+    <row r="19" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
     </row>
-    <row r="20" ht="20.1" customHeight="1" spans="1:5">
+    <row r="20" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
     </row>
-    <row r="21" ht="20.1" customHeight="1" spans="1:5">
+    <row r="21" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
     </row>
-    <row r="22" ht="20.1" customHeight="1" spans="1:5">
+    <row r="22" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
     </row>
-    <row r="23" ht="20.1" customHeight="1" spans="1:5">
+    <row r="23" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
     </row>
-    <row r="24" ht="20.1" customHeight="1" spans="1:5">
+    <row r="24" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
     </row>
-    <row r="25" ht="20.1" customHeight="1" spans="1:5">
+    <row r="25" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
     </row>
-    <row r="26" ht="20.1" customHeight="1" spans="1:5">
+    <row r="26" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
     </row>
-    <row r="27" ht="20.1" customHeight="1" spans="1:5">
+    <row r="27" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
     </row>
-    <row r="28" ht="20.1" customHeight="1" spans="1:5">
+    <row r="28" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
     </row>
-    <row r="29" ht="20.1" customHeight="1" spans="1:5">
+    <row r="29" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
     </row>
-    <row r="30" ht="20.1" customHeight="1" spans="1:5">
+    <row r="30" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
     </row>
-    <row r="31" ht="20.1" customHeight="1" spans="1:5">
+    <row r="31" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -3444,24 +2860,25 @@
       <c r="E31" s="8"/>
     </row>
   </sheetData>
-  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.70069444444444495" right="0.70069444444444495" top="0.75208333333333299" bottom="0.75208333333333299" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="20.625" customWidth="1"/>
+    <col min="1" max="1" width="20.625" customWidth="1"/>
+    <col min="2" max="2" width="22.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.25" customWidth="1"/>
-    <col min="4" max="5" width="20.625" customWidth="1"/>
+    <col min="4" max="4" width="20.625" customWidth="1"/>
+    <col min="5" max="5" width="23.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:5">
+    <row r="1" spans="1:5" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3478,7 +2895,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="20.1" customHeight="1" spans="1:5">
+    <row r="2" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -3495,7 +2912,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" ht="20.1" customHeight="1" spans="1:5">
+    <row r="3" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>2</v>
       </c>
@@ -3512,7 +2929,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" ht="20.1" customHeight="1" spans="1:5">
+    <row r="4" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>3</v>
       </c>
@@ -3529,7 +2946,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" ht="20.1" customHeight="1" spans="1:5">
+    <row r="5" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
         <v>4</v>
       </c>
@@ -3546,182 +2963,182 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" ht="20.1" customHeight="1" spans="1:5">
+    <row r="6" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
     </row>
-    <row r="7" ht="20.1" customHeight="1" spans="1:5">
+    <row r="7" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
     </row>
-    <row r="8" ht="20.1" customHeight="1" spans="1:5">
+    <row r="8" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
     </row>
-    <row r="9" ht="20.1" customHeight="1" spans="1:5">
+    <row r="9" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
     </row>
-    <row r="10" ht="20.1" customHeight="1" spans="1:5">
+    <row r="10" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
     </row>
-    <row r="11" ht="20.1" customHeight="1" spans="1:5">
+    <row r="11" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
     </row>
-    <row r="12" ht="20.1" customHeight="1" spans="1:5">
+    <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
     </row>
-    <row r="13" ht="20.1" customHeight="1" spans="1:5">
+    <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
     </row>
-    <row r="14" ht="20.1" customHeight="1" spans="1:5">
+    <row r="14" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
     </row>
-    <row r="15" ht="20.1" customHeight="1" spans="1:5">
+    <row r="15" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
     </row>
-    <row r="16" ht="20.1" customHeight="1" spans="1:5">
+    <row r="16" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
     </row>
-    <row r="17" ht="20.1" customHeight="1" spans="1:5">
+    <row r="17" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
     </row>
-    <row r="18" ht="20.1" customHeight="1" spans="1:5">
+    <row r="18" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
     </row>
-    <row r="19" ht="20.1" customHeight="1" spans="1:5">
+    <row r="19" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
     </row>
-    <row r="20" ht="20.1" customHeight="1" spans="1:5">
+    <row r="20" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
     </row>
-    <row r="21" ht="20.1" customHeight="1" spans="1:5">
+    <row r="21" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
     </row>
-    <row r="22" ht="20.1" customHeight="1" spans="1:5">
+    <row r="22" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
     </row>
-    <row r="23" ht="20.1" customHeight="1" spans="1:5">
+    <row r="23" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
     </row>
-    <row r="24" ht="20.1" customHeight="1" spans="1:5">
+    <row r="24" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
     </row>
-    <row r="25" ht="20.1" customHeight="1" spans="1:5">
+    <row r="25" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
     </row>
-    <row r="26" ht="20.1" customHeight="1" spans="1:5">
+    <row r="26" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
     </row>
-    <row r="27" ht="20.1" customHeight="1" spans="1:5">
+    <row r="27" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
     </row>
-    <row r="28" ht="20.1" customHeight="1" spans="1:5">
+    <row r="28" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
     </row>
-    <row r="29" ht="20.1" customHeight="1" spans="1:5">
+    <row r="29" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
     </row>
-    <row r="30" ht="20.1" customHeight="1" spans="1:5">
+    <row r="30" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
     </row>
-    <row r="31" ht="20.1" customHeight="1" spans="1:5">
+    <row r="31" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -3729,22 +3146,21 @@
       <c r="E31" s="8"/>
     </row>
   </sheetData>
-  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.70069444444444495" right="0.70069444444444495" top="0.75208333333333299" bottom="0.75208333333333299" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:3">
+    <row r="1" spans="1:3" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3755,173 +3171,172 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="20.1" customHeight="1" spans="1:3">
+    <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
     </row>
-    <row r="3" ht="20.1" customHeight="1" spans="1:3">
+    <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
     </row>
-    <row r="4" ht="20.1" customHeight="1" spans="1:3">
+    <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
     </row>
-    <row r="5" ht="20.1" customHeight="1" spans="1:3">
+    <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
     </row>
-    <row r="6" ht="20.1" customHeight="1" spans="1:3">
+    <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
     </row>
-    <row r="7" ht="20.1" customHeight="1" spans="1:3">
+    <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
     </row>
-    <row r="8" ht="20.1" customHeight="1" spans="1:3">
+    <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
     </row>
-    <row r="9" ht="20.1" customHeight="1" spans="1:3">
+    <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
     </row>
-    <row r="10" ht="20.1" customHeight="1" spans="1:3">
+    <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
     </row>
-    <row r="11" ht="20.1" customHeight="1" spans="1:3">
+    <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
     </row>
-    <row r="12" ht="20.1" customHeight="1" spans="1:3">
+    <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
     </row>
-    <row r="13" ht="20.1" customHeight="1" spans="1:3">
+    <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
     </row>
-    <row r="14" ht="20.1" customHeight="1" spans="1:3">
+    <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
     </row>
-    <row r="15" ht="20.1" customHeight="1" spans="1:3">
+    <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
     </row>
-    <row r="16" ht="20.1" customHeight="1" spans="1:3">
+    <row r="16" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
     </row>
-    <row r="17" ht="20.1" customHeight="1" spans="1:3">
+    <row r="17" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
     </row>
-    <row r="18" ht="20.1" customHeight="1" spans="1:3">
+    <row r="18" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
     </row>
-    <row r="19" ht="20.1" customHeight="1" spans="1:3">
+    <row r="19" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
     </row>
-    <row r="20" ht="20.1" customHeight="1" spans="1:3">
+    <row r="20" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
     </row>
-    <row r="21" ht="20.1" customHeight="1" spans="1:3">
+    <row r="21" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
     </row>
-    <row r="22" ht="20.1" customHeight="1" spans="1:3">
+    <row r="22" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
     </row>
-    <row r="23" ht="20.1" customHeight="1" spans="1:3">
+    <row r="23" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
     </row>
-    <row r="24" ht="20.1" customHeight="1" spans="1:3">
+    <row r="24" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
     </row>
-    <row r="25" ht="20.1" customHeight="1" spans="1:3">
+    <row r="25" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
     </row>
-    <row r="26" ht="20.1" customHeight="1" spans="1:3">
+    <row r="26" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
     </row>
-    <row r="27" ht="20.1" customHeight="1" spans="1:3">
+    <row r="27" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
     </row>
-    <row r="28" ht="20.1" customHeight="1" spans="1:3">
+    <row r="28" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
     </row>
-    <row r="29" ht="20.1" customHeight="1" spans="1:3">
+    <row r="29" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
     </row>
-    <row r="30" ht="20.1" customHeight="1" spans="1:3">
+    <row r="30" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
     </row>
-    <row r="31" ht="20.1" customHeight="1" spans="1:3">
+    <row r="31" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
     </row>
   </sheetData>
-  <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.75208333333333299" right="0.75208333333333299" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:3">
+    <row r="1" spans="1:3" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3932,98 +3347,99 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" ht="20.1" customHeight="1" spans="1:3">
+    <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="3"/>
     </row>
-    <row r="3" ht="20.1" customHeight="1" spans="1:3">
+    <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="8"/>
       <c r="B3" s="7"/>
       <c r="C3" s="3"/>
     </row>
-    <row r="4" ht="20.1" customHeight="1" spans="1:3">
+    <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="3"/>
     </row>
-    <row r="5" ht="20.1" customHeight="1" spans="1:3">
+    <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" ht="20.1" customHeight="1" spans="1:3">
+    <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8"/>
       <c r="B6" s="7"/>
       <c r="C6" s="3"/>
     </row>
-    <row r="7" ht="20.1" customHeight="1" spans="1:3">
+    <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" ht="20.1" customHeight="1" spans="1:3">
+    <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" ht="20.1" customHeight="1" spans="1:3">
+    <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8"/>
       <c r="B9" s="7"/>
       <c r="C9" s="3"/>
     </row>
-    <row r="10" ht="20.1" customHeight="1" spans="1:3">
+    <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" ht="20.1" customHeight="1" spans="1:3">
+    <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="3"/>
     </row>
-    <row r="12" ht="20.1" customHeight="1" spans="1:3">
+    <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8"/>
       <c r="B12" s="7"/>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" ht="20.1" customHeight="1" spans="1:3">
+    <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" ht="20.1" customHeight="1" spans="1:3">
+    <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="3"/>
     </row>
-    <row r="15" ht="20.1" customHeight="1" spans="1:3">
+    <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8"/>
       <c r="B15" s="7"/>
       <c r="C15" s="3"/>
     </row>
   </sheetData>
-  <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.75208333333333299" right="0.75208333333333299" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:I93"/>
-  <sheetFormatPr defaultColWidth="19.75" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="19.75" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.75" style="1"/>
-    <col min="2" max="2" width="40.25" customWidth="1"/>
-    <col min="3" max="6" width="19.75" style="1"/>
-    <col min="7" max="7" width="118.25" customWidth="1"/>
+    <col min="2" max="2" width="40" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="19.75" style="1"/>
+    <col min="5" max="5" width="12.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="118" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.625" customWidth="1"/>
-    <col min="9" max="9" width="40.25" customWidth="1"/>
+    <col min="9" max="9" width="40" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:9">
+    <row r="1" spans="1:9" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4052,7 +3468,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -4075,7 +3491,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>11</v>
       </c>
@@ -4098,7 +3514,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>1101</v>
       </c>
@@ -4123,7 +3539,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>1102</v>
       </c>
@@ -4148,7 +3564,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>1103</v>
       </c>
@@ -4173,7 +3589,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>12</v>
       </c>
@@ -4196,7 +3612,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>1201</v>
       </c>
@@ -4221,7 +3637,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>1202</v>
       </c>
@@ -4246,7 +3662,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>1203</v>
       </c>
@@ -4271,7 +3687,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>1204</v>
       </c>
@@ -4296,7 +3712,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>13</v>
       </c>
@@ -4319,7 +3735,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>1301</v>
       </c>
@@ -4344,7 +3760,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>1302</v>
       </c>
@@ -4369,7 +3785,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>1303</v>
       </c>
@@ -4394,7 +3810,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>1304</v>
       </c>
@@ -4419,7 +3835,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>1305</v>
       </c>
@@ -4444,7 +3860,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>1306</v>
       </c>
@@ -4469,7 +3885,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>14</v>
       </c>
@@ -4492,7 +3908,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>1401</v>
       </c>
@@ -4517,7 +3933,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>1402</v>
       </c>
@@ -4542,7 +3958,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>1403</v>
       </c>
@@ -4567,7 +3983,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>15</v>
       </c>
@@ -4590,7 +4006,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>1501</v>
       </c>
@@ -4615,7 +4031,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>1502</v>
       </c>
@@ -4640,7 +4056,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>1503</v>
       </c>
@@ -4665,7 +4081,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>1504</v>
       </c>
@@ -4690,7 +4106,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>16</v>
       </c>
@@ -4713,7 +4129,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>1601</v>
       </c>
@@ -4738,7 +4154,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>1602</v>
       </c>
@@ -4763,7 +4179,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>1603</v>
       </c>
@@ -4788,7 +4204,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>1604</v>
       </c>
@@ -4813,7 +4229,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>17</v>
       </c>
@@ -4836,7 +4252,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>1701</v>
       </c>
@@ -4861,7 +4277,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>1702</v>
       </c>
@@ -4886,7 +4302,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <v>1703</v>
       </c>
@@ -4911,7 +4327,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
         <v>1704</v>
       </c>
@@ -4936,7 +4352,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
         <v>1705</v>
       </c>
@@ -4961,7 +4377,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
         <v>1706</v>
       </c>
@@ -4986,7 +4402,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
         <v>1707</v>
       </c>
@@ -5011,7 +4427,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
         <v>1708</v>
       </c>
@@ -5036,7 +4452,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
         <v>1709</v>
       </c>
@@ -5061,7 +4477,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>18</v>
       </c>
@@ -5084,7 +4500,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
         <v>1801</v>
       </c>
@@ -5109,7 +4525,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>1802</v>
       </c>
@@ -5134,7 +4550,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
         <v>1803</v>
       </c>
@@ -5159,7 +4575,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
         <v>1804</v>
       </c>
@@ -5184,7 +4600,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
         <v>1805</v>
       </c>
@@ -5209,7 +4625,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
         <v>1806</v>
       </c>
@@ -5234,7 +4650,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
         <v>19</v>
       </c>
@@ -5257,7 +4673,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
         <v>1901</v>
       </c>
@@ -5282,7 +4698,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="3">
         <v>2</v>
       </c>
@@ -5305,7 +4721,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="3">
         <v>21</v>
       </c>
@@ -5328,7 +4744,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
         <v>2110</v>
       </c>
@@ -5353,7 +4769,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="3">
         <v>2111</v>
       </c>
@@ -5378,7 +4794,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="3">
         <v>2112</v>
       </c>
@@ -5403,7 +4819,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="3">
         <v>2113</v>
       </c>
@@ -5428,7 +4844,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="3">
         <v>22</v>
       </c>
@@ -5451,7 +4867,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="3">
         <v>2201</v>
       </c>
@@ -5476,7 +4892,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="3">
         <v>2202</v>
       </c>
@@ -5501,7 +4917,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="3">
         <v>2203</v>
       </c>
@@ -5526,7 +4942,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="3">
         <v>23</v>
       </c>
@@ -5549,7 +4965,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
         <v>2301</v>
       </c>
@@ -5574,7 +4990,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="3">
         <v>2302</v>
       </c>
@@ -5597,7 +5013,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="3">
         <v>23021</v>
       </c>
@@ -5622,7 +5038,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="3">
         <v>23022</v>
       </c>
@@ -5647,7 +5063,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="3">
         <v>2303</v>
       </c>
@@ -5670,7 +5086,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="3">
         <v>23031</v>
       </c>
@@ -5695,7 +5111,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="3">
         <v>2304</v>
       </c>
@@ -5718,7 +5134,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="3">
         <v>23041</v>
       </c>
@@ -5743,7 +5159,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="3">
         <v>23042</v>
       </c>
@@ -5768,12 +5184,12 @@
         <v>154</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="3">
         <v>23043</v>
       </c>
-      <c r="B72" s="4" t="s">
-        <v>156</v>
+      <c r="B72" s="11" t="s">
+        <v>193</v>
       </c>
       <c r="C72" s="3">
         <v>2304</v>
@@ -5785,20 +5201,20 @@
       <c r="F72" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G72" s="4" t="s">
-        <v>157</v>
+      <c r="G72" s="11" t="s">
+        <v>194</v>
       </c>
       <c r="H72" s="4"/>
-      <c r="I72" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9">
+      <c r="I72" s="11" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="3">
         <v>23044</v>
       </c>
-      <c r="B73" s="4" t="s">
-        <v>158</v>
+      <c r="B73" s="11" t="s">
+        <v>195</v>
       </c>
       <c r="C73" s="3">
         <v>2304</v>
@@ -5810,20 +5226,20 @@
       <c r="F73" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G73" s="4" t="s">
-        <v>159</v>
+      <c r="G73" s="11" t="s">
+        <v>196</v>
       </c>
       <c r="H73" s="4"/>
-      <c r="I73" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9">
+      <c r="I73" s="11" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="3">
         <v>23045</v>
       </c>
-      <c r="B74" s="4" t="s">
-        <v>160</v>
+      <c r="B74" s="11" t="s">
+        <v>197</v>
       </c>
       <c r="C74" s="3">
         <v>2304</v>
@@ -5835,20 +5251,20 @@
       <c r="F74" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G74" s="4" t="s">
-        <v>161</v>
+      <c r="G74" s="11" t="s">
+        <v>198</v>
       </c>
       <c r="H74" s="4"/>
-      <c r="I74" s="4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9">
+      <c r="I74" s="11" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="3">
         <v>23046</v>
       </c>
-      <c r="B75" s="4" t="s">
-        <v>162</v>
+      <c r="B75" s="11" t="s">
+        <v>199</v>
       </c>
       <c r="C75" s="3">
         <v>2304</v>
@@ -5860,20 +5276,20 @@
       <c r="F75" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G75" s="4" t="s">
-        <v>163</v>
+      <c r="G75" s="11" t="s">
+        <v>200</v>
       </c>
       <c r="H75" s="4"/>
-      <c r="I75" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9">
+      <c r="I75" s="11" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="3">
         <v>23047</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C76" s="3">
         <v>2304</v>
@@ -5886,14 +5302,14 @@
         <v>39</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="H76" s="4"/>
       <c r="I76" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="3">
         <v>2305</v>
       </c>
@@ -5916,12 +5332,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="3">
         <v>23051</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C78" s="3">
         <v>2305</v>
@@ -5934,19 +5350,19 @@
         <v>39</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="H78" s="4"/>
       <c r="I78" s="4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="3">
         <v>23052</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C79" s="3">
         <v>2305</v>
@@ -5959,19 +5375,19 @@
         <v>39</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="H79" s="4"/>
       <c r="I79" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="3">
         <v>23053</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C80" s="3">
         <v>2305</v>
@@ -5984,19 +5400,19 @@
         <v>39</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="H80" s="4"/>
       <c r="I80" s="4" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="3">
         <v>23054</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C81" s="3">
         <v>2305</v>
@@ -6009,19 +5425,19 @@
         <v>39</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="H81" s="4"/>
       <c r="I81" s="4" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="3">
         <v>23055</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C82" s="3">
         <v>2305</v>
@@ -6034,19 +5450,19 @@
         <v>39</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="H82" s="4"/>
       <c r="I82" s="4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="3">
         <v>23056</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="C83" s="3">
         <v>2305</v>
@@ -6059,14 +5475,14 @@
         <v>39</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="H83" s="4"/>
       <c r="I83" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
         <v>2306</v>
       </c>
@@ -6089,12 +5505,12 @@
         <v>92</v>
       </c>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="3">
         <v>23061</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C85" s="3">
         <v>2306</v>
@@ -6107,19 +5523,19 @@
         <v>39</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="H85" s="4"/>
       <c r="I85" s="4" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="3">
         <v>24</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C86" s="3">
         <v>2</v>
@@ -6134,15 +5550,15 @@
       <c r="G86" s="4"/>
       <c r="H86" s="4"/>
       <c r="I86" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="3">
         <v>2401</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C87" s="3">
         <v>24</v>
@@ -6155,19 +5571,19 @@
         <v>39</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="H87" s="4"/>
       <c r="I87" s="4" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="3">
         <v>25</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C88" s="3">
         <v>2</v>
@@ -6182,15 +5598,15 @@
       <c r="G88" s="4"/>
       <c r="H88" s="4"/>
       <c r="I88" s="4" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" s="3">
         <v>2501</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C89" s="3">
         <v>25</v>
@@ -6203,19 +5619,19 @@
         <v>39</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="H89" s="3"/>
       <c r="I89" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="3">
         <v>2502</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C90" s="3">
         <v>25</v>
@@ -6228,19 +5644,19 @@
         <v>39</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="H90" s="5"/>
       <c r="I90" s="5" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="3">
         <v>2503</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="C91" s="3">
         <v>25</v>
@@ -6253,19 +5669,19 @@
         <v>39</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="H91" s="4"/>
       <c r="I91" s="4" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="3">
         <v>26</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="C92" s="3">
         <v>2</v>
@@ -6280,15 +5696,15 @@
       <c r="G92" s="4"/>
       <c r="H92" s="4"/>
       <c r="I92" s="4" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="3">
         <v>2601</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C93" s="3">
         <v>26</v>
@@ -6301,16 +5717,16 @@
         <v>39</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="H93" s="4"/>
       <c r="I93" s="4" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.70069444444444495" right="0.70069444444444495" top="0.75208333333333299" bottom="0.75208333333333299" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Code\CSharp\semix\xuankaizhi\netcore_semix_cuga_calibration\Sources\Cuga-Calibration-Solution\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF94D977-196D-43DB-85BF-C910A4EE969D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A88E05B-D443-4BF4-B2C7-BC7DD2CCBF76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="205">
   <si>
     <t>Id</t>
   </si>
@@ -705,6 +705,18 @@
   <si>
     <t>CugaCalibration.ViewModels.Common.Windows.Tools.AODWaveform.ChirpAODWaveformElectrodeDelayWindowViewModel</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Side Channel Flexible Aperture</t>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Fourier.FourierSideChannelFlexibleApertureViewModel</t>
+  </si>
+  <si>
+    <t>Side Channel Specular Blocker</t>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Fourier.FourierSideChannelSpecularBlockerViewModel</t>
   </si>
 </sst>
 </file>
@@ -3426,7 +3438,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:I95"/>
   <sheetFormatPr defaultColWidth="19.75" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.75" style="1"/>
@@ -4700,308 +4712,310 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="3">
-        <v>2</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>127</v>
+        <v>1902</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>201</v>
       </c>
       <c r="C52" s="3">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="D52" s="3">
-        <v>2</v>
+        <v>1902</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G52" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>202</v>
+      </c>
       <c r="H52" s="4"/>
-      <c r="I52" s="4" t="s">
-        <v>127</v>
+      <c r="I52" s="6" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="3">
-        <v>21</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>128</v>
+        <v>1903</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>203</v>
       </c>
       <c r="C53" s="3">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D53" s="3">
-        <v>21</v>
+        <v>1903</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G53" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>204</v>
+      </c>
       <c r="H53" s="4"/>
-      <c r="I53" s="4" t="s">
-        <v>128</v>
+      <c r="I53" s="6" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
-        <v>2110</v>
+        <v>2</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C54" s="3">
-        <v>21</v>
+        <v>-1</v>
       </c>
       <c r="D54" s="3">
-        <v>2110</v>
+        <v>2</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>130</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G54" s="4"/>
       <c r="H54" s="4"/>
       <c r="I54" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="3">
-        <v>2111</v>
+        <v>21</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C55" s="3">
+        <v>2</v>
+      </c>
+      <c r="D55" s="3">
         <v>21</v>
-      </c>
-      <c r="D55" s="3">
-        <v>2111</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>132</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G55" s="4"/>
       <c r="H55" s="4"/>
       <c r="I55" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="3">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C56" s="3">
         <v>21</v>
       </c>
       <c r="D56" s="3">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H56" s="4"/>
       <c r="I56" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="3">
-        <v>2113</v>
+        <v>2111</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C57" s="3">
         <v>21</v>
       </c>
       <c r="D57" s="3">
-        <v>2113</v>
+        <v>2111</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H57" s="4"/>
       <c r="I57" s="4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="3">
-        <v>22</v>
+        <v>2112</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C58" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D58" s="3">
-        <v>22</v>
+        <v>2112</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G58" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>134</v>
+      </c>
       <c r="H58" s="4"/>
       <c r="I58" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="3">
-        <v>2201</v>
+        <v>2113</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C59" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D59" s="3">
-        <v>2201</v>
+        <v>2113</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H59" s="4"/>
       <c r="I59" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="3">
-        <v>2202</v>
+        <v>22</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C60" s="3">
+        <v>2</v>
+      </c>
+      <c r="D60" s="3">
         <v>22</v>
-      </c>
-      <c r="D60" s="3">
-        <v>2202</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>140</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G60" s="4"/>
       <c r="H60" s="4"/>
       <c r="I60" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="3">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C61" s="3">
         <v>22</v>
       </c>
       <c r="D61" s="3">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H61" s="4"/>
       <c r="I61" s="4" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="3">
-        <v>23</v>
+        <v>2202</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C62" s="3">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D62" s="3">
-        <v>23</v>
+        <v>2202</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G62" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>140</v>
+      </c>
       <c r="H62" s="4"/>
       <c r="I62" s="4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
-        <v>2301</v>
+        <v>2203</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C63" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D63" s="3">
-        <v>2301</v>
+        <v>2203</v>
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H63" s="4"/>
       <c r="I63" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="3">
-        <v>2302</v>
+        <v>23</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="C64" s="3">
+        <v>2</v>
+      </c>
+      <c r="D64" s="3">
         <v>23</v>
-      </c>
-      <c r="D64" s="3">
-        <v>2302</v>
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3" t="s">
@@ -5010,119 +5024,119 @@
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4" t="s">
-        <v>75</v>
+        <v>143</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="3">
-        <v>23021</v>
+        <v>2301</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C65" s="3">
-        <v>2302</v>
+        <v>23</v>
       </c>
       <c r="D65" s="3">
-        <v>23021</v>
+        <v>2301</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H65" s="4"/>
       <c r="I65" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="3">
-        <v>23022</v>
+        <v>2302</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="C66" s="3">
+        <v>23</v>
+      </c>
+      <c r="D66" s="3">
         <v>2302</v>
-      </c>
-      <c r="D66" s="3">
-        <v>23022</v>
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G66" s="4" t="s">
-        <v>149</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G66" s="4"/>
       <c r="H66" s="4"/>
       <c r="I66" s="4" t="s">
-        <v>148</v>
+        <v>75</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="3">
-        <v>2303</v>
+        <v>23021</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C67" s="3">
-        <v>23</v>
+        <v>2302</v>
       </c>
       <c r="D67" s="3">
-        <v>2303</v>
+        <v>23021</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G67" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>147</v>
+      </c>
       <c r="H67" s="4"/>
       <c r="I67" s="4" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="3">
-        <v>23031</v>
+        <v>23022</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>65</v>
+        <v>148</v>
       </c>
       <c r="C68" s="3">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="D68" s="3">
-        <v>23031</v>
+        <v>23022</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H68" s="4"/>
       <c r="I68" s="4" t="s">
-        <v>65</v>
+        <v>148</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="3">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>74</v>
+        <v>150</v>
       </c>
       <c r="C69" s="3">
         <v>23</v>
       </c>
       <c r="D69" s="3">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3" t="s">
@@ -5131,465 +5145,465 @@
       <c r="G69" s="4"/>
       <c r="H69" s="4"/>
       <c r="I69" s="4" t="s">
-        <v>74</v>
+        <v>150</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="3">
-        <v>23041</v>
+        <v>23031</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>152</v>
+        <v>65</v>
       </c>
       <c r="C70" s="3">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="D70" s="3">
-        <v>23041</v>
+        <v>23031</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H70" s="4"/>
       <c r="I70" s="4" t="s">
-        <v>152</v>
+        <v>65</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="3">
-        <v>23042</v>
+        <v>2304</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>154</v>
+        <v>74</v>
       </c>
       <c r="C71" s="3">
+        <v>23</v>
+      </c>
+      <c r="D71" s="3">
         <v>2304</v>
-      </c>
-      <c r="D71" s="3">
-        <v>23042</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>155</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G71" s="4"/>
       <c r="H71" s="4"/>
       <c r="I71" s="4" t="s">
-        <v>154</v>
+        <v>74</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="3">
-        <v>23043</v>
-      </c>
-      <c r="B72" s="11" t="s">
-        <v>193</v>
+        <v>23041</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>152</v>
       </c>
       <c r="C72" s="3">
         <v>2304</v>
       </c>
       <c r="D72" s="3">
-        <v>23043</v>
+        <v>23041</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G72" s="11" t="s">
-        <v>194</v>
+      <c r="G72" s="4" t="s">
+        <v>153</v>
       </c>
       <c r="H72" s="4"/>
-      <c r="I72" s="11" t="s">
-        <v>193</v>
+      <c r="I72" s="4" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="3">
-        <v>23044</v>
-      </c>
-      <c r="B73" s="11" t="s">
-        <v>195</v>
+        <v>23042</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>154</v>
       </c>
       <c r="C73" s="3">
         <v>2304</v>
       </c>
       <c r="D73" s="3">
-        <v>23044</v>
+        <v>23042</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G73" s="11" t="s">
-        <v>196</v>
+      <c r="G73" s="4" t="s">
+        <v>155</v>
       </c>
       <c r="H73" s="4"/>
-      <c r="I73" s="11" t="s">
-        <v>195</v>
+      <c r="I73" s="4" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="3">
-        <v>23045</v>
+        <v>23043</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C74" s="3">
         <v>2304</v>
       </c>
       <c r="D74" s="3">
-        <v>23045</v>
+        <v>23043</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G74" s="11" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="H74" s="4"/>
       <c r="I74" s="11" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="3">
-        <v>23046</v>
+        <v>23044</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C75" s="3">
         <v>2304</v>
       </c>
       <c r="D75" s="3">
-        <v>23046</v>
+        <v>23044</v>
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G75" s="11" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="H75" s="4"/>
       <c r="I75" s="11" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="3">
-        <v>23047</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>156</v>
+        <v>23045</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>197</v>
       </c>
       <c r="C76" s="3">
         <v>2304</v>
       </c>
       <c r="D76" s="3">
-        <v>23047</v>
+        <v>23045</v>
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G76" s="4" t="s">
-        <v>157</v>
+      <c r="G76" s="11" t="s">
+        <v>198</v>
       </c>
       <c r="H76" s="4"/>
-      <c r="I76" s="4" t="s">
-        <v>156</v>
+      <c r="I76" s="11" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="3">
-        <v>2305</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>111</v>
+        <v>23046</v>
+      </c>
+      <c r="B77" s="11" t="s">
+        <v>199</v>
       </c>
       <c r="C77" s="3">
-        <v>23</v>
+        <v>2304</v>
       </c>
       <c r="D77" s="3">
-        <v>2305</v>
+        <v>23046</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G77" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G77" s="11" t="s">
+        <v>200</v>
+      </c>
       <c r="H77" s="4"/>
-      <c r="I77" s="4" t="s">
-        <v>111</v>
+      <c r="I77" s="11" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="3">
-        <v>23051</v>
+        <v>23047</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C78" s="3">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="D78" s="3">
-        <v>23051</v>
+        <v>23047</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H78" s="4"/>
       <c r="I78" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="3">
-        <v>23052</v>
+        <v>2305</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>160</v>
+        <v>111</v>
       </c>
       <c r="C79" s="3">
+        <v>23</v>
+      </c>
+      <c r="D79" s="3">
         <v>2305</v>
-      </c>
-      <c r="D79" s="3">
-        <v>23052</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G79" s="4" t="s">
-        <v>161</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G79" s="4"/>
       <c r="H79" s="4"/>
       <c r="I79" s="4" t="s">
-        <v>160</v>
+        <v>111</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="3">
-        <v>23053</v>
+        <v>23051</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C80" s="3">
         <v>2305</v>
       </c>
       <c r="D80" s="3">
-        <v>23053</v>
+        <v>23051</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H80" s="4"/>
       <c r="I80" s="4" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="3">
-        <v>23054</v>
+        <v>23052</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C81" s="3">
         <v>2305</v>
       </c>
       <c r="D81" s="3">
-        <v>23054</v>
+        <v>23052</v>
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H81" s="4"/>
       <c r="I81" s="4" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="3">
-        <v>23055</v>
+        <v>23053</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C82" s="3">
         <v>2305</v>
       </c>
       <c r="D82" s="3">
-        <v>23055</v>
+        <v>23053</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="H82" s="4"/>
       <c r="I82" s="4" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="3">
-        <v>23056</v>
+        <v>23054</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C83" s="3">
         <v>2305</v>
       </c>
       <c r="D83" s="3">
-        <v>23056</v>
+        <v>23054</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="H83" s="4"/>
       <c r="I83" s="4" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
-        <v>2306</v>
+        <v>23055</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>92</v>
+        <v>166</v>
       </c>
       <c r="C84" s="3">
-        <v>23</v>
+        <v>2305</v>
       </c>
       <c r="D84" s="3">
-        <v>2306</v>
+        <v>23055</v>
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G84" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>167</v>
+      </c>
       <c r="H84" s="4"/>
       <c r="I84" s="4" t="s">
-        <v>92</v>
+        <v>166</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="3">
-        <v>23061</v>
+        <v>23056</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C85" s="3">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="D85" s="3">
-        <v>23061</v>
+        <v>23056</v>
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H85" s="4"/>
       <c r="I85" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="3">
-        <v>24</v>
+        <v>2306</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>172</v>
+        <v>92</v>
       </c>
       <c r="C86" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D86" s="3">
-        <v>24</v>
-      </c>
-      <c r="E86" s="4"/>
+        <v>2306</v>
+      </c>
+      <c r="E86" s="3"/>
       <c r="F86" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G86" s="4"/>
       <c r="H86" s="4"/>
       <c r="I86" s="4" t="s">
-        <v>172</v>
+        <v>92</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="3">
-        <v>2401</v>
+        <v>23061</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C87" s="3">
-        <v>24</v>
+        <v>2306</v>
       </c>
       <c r="D87" s="3">
-        <v>2401</v>
-      </c>
-      <c r="E87" s="4"/>
+        <v>23061</v>
+      </c>
+      <c r="E87" s="3"/>
       <c r="F87" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H87" s="4"/>
       <c r="I87" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C88" s="3">
         <v>2</v>
       </c>
       <c r="D88" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E88" s="4"/>
       <c r="F88" s="3" t="s">
@@ -5598,129 +5612,177 @@
       <c r="G88" s="4"/>
       <c r="H88" s="4"/>
       <c r="I88" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" s="3">
-        <v>2501</v>
+        <v>2401</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C89" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D89" s="3">
-        <v>2501</v>
-      </c>
-      <c r="E89" s="3"/>
+        <v>2401</v>
+      </c>
+      <c r="E89" s="4"/>
       <c r="F89" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="H89" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="H89" s="4"/>
       <c r="I89" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="3">
-        <v>2502</v>
+        <v>25</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C90" s="3">
+        <v>2</v>
+      </c>
+      <c r="D90" s="3">
         <v>25</v>
       </c>
-      <c r="D90" s="3">
-        <v>2502</v>
-      </c>
-      <c r="E90" s="3"/>
+      <c r="E90" s="4"/>
       <c r="F90" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G90" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="H90" s="5"/>
-      <c r="I90" s="5" t="s">
-        <v>177</v>
+        <v>36</v>
+      </c>
+      <c r="G90" s="4"/>
+      <c r="H90" s="4"/>
+      <c r="I90" s="4" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="3">
-        <v>2503</v>
+        <v>2501</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C91" s="3">
         <v>25</v>
       </c>
       <c r="D91" s="3">
-        <v>2503</v>
+        <v>2501</v>
       </c>
       <c r="E91" s="3"/>
       <c r="F91" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="H91" s="4"/>
+        <v>176</v>
+      </c>
+      <c r="H91" s="3"/>
       <c r="I91" s="4" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="3">
-        <v>26</v>
+        <v>2502</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C92" s="3">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D92" s="3">
-        <v>26</v>
+        <v>2502</v>
       </c>
       <c r="E92" s="3"/>
       <c r="F92" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G92" s="4"/>
-      <c r="H92" s="4"/>
-      <c r="I92" s="4" t="s">
-        <v>181</v>
+        <v>39</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H92" s="5"/>
+      <c r="I92" s="5" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="3">
-        <v>2601</v>
+        <v>2503</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C93" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D93" s="3">
-        <v>2601</v>
-      </c>
-      <c r="E93" s="4"/>
+        <v>2503</v>
+      </c>
+      <c r="E93" s="3"/>
       <c r="F93" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H93" s="4"/>
       <c r="I93" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A94" s="3">
+        <v>26</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C94" s="3">
+        <v>2</v>
+      </c>
+      <c r="D94" s="3">
+        <v>26</v>
+      </c>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G94" s="4"/>
+      <c r="H94" s="4"/>
+      <c r="I94" s="4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A95" s="3">
+        <v>2601</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C95" s="3">
+        <v>26</v>
+      </c>
+      <c r="D95" s="3">
+        <v>2601</v>
+      </c>
+      <c r="E95" s="4"/>
+      <c r="F95" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="H95" s="4"/>
+      <c r="I95" s="4" t="s">
         <v>182</v>
       </c>
     </row>

--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="207">
   <si>
     <t>Id</t>
   </si>
@@ -717,6 +717,12 @@
   </si>
   <si>
     <t>CugaCalibration.ViewModels.Fourier.FourierSideChannelSpecularBlockerViewModel</t>
+  </si>
+  <si>
+    <t>Center Channel Flexible Aperture</t>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Fourier.FourierCenterChannelFlexibleApertureViewModel</t>
   </si>
 </sst>
 </file>
@@ -3438,7 +3444,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:I95"/>
+  <dimension ref="A1:I96"/>
   <sheetFormatPr defaultColWidth="19.75" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.75" style="1"/>
@@ -5786,6 +5792,31 @@
         <v>182</v>
       </c>
     </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A96" s="3">
+        <v>1904</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C96" s="3">
+        <v>19</v>
+      </c>
+      <c r="D96" s="3">
+        <v>1904</v>
+      </c>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G96" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="H96" s="4"/>
+      <c r="I96" s="6" t="s">
+        <v>205</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.70069444444444495" right="0.70069444444444495" top="0.75208333333333299" bottom="0.75208333333333299" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Code\CSharp\semix\xuankaizhi\netcore_semix_cuga_calibration\Sources\Cuga-Calibration-Solution\Assets\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A88E05B-D443-4BF4-B2C7-BC7DD2CCBF76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60155F2A-A4DF-4302-BD63-789F700D7C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SysUser" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="209">
   <si>
     <t>Id</t>
   </si>
@@ -719,10 +719,20 @@
     <t>CugaCalibration.ViewModels.Fourier.FourierSideChannelSpecularBlockerViewModel</t>
   </si>
   <si>
-    <t>Center Channel Flexible Aperture</t>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Fourier.FourierCenterChannelFlexibleApertureViewModel</t>
+    <t>Center Channel Flexible Aperture V1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Center Channel Specular Blocker V1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Fourier.V0FourierCenterChannelFlexibleApertureViewModel</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Fourier.V0FourierCenterChannelSpecularBlockerViewModel</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3444,7 +3454,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:I96"/>
+  <dimension ref="A1:I97"/>
   <sheetFormatPr defaultColWidth="19.75" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.75" style="1"/>
@@ -4768,308 +4778,310 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
-        <v>2</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>127</v>
+        <v>1903</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>205</v>
       </c>
       <c r="C54" s="3">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="D54" s="3">
-        <v>2</v>
+        <v>1903</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G54" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G54" s="11" t="s">
+        <v>207</v>
+      </c>
       <c r="H54" s="4"/>
-      <c r="I54" s="4" t="s">
-        <v>127</v>
+      <c r="I54" s="11" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="3">
-        <v>21</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>128</v>
+        <v>1904</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>206</v>
       </c>
       <c r="C55" s="3">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D55" s="3">
-        <v>21</v>
+        <v>1904</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G55" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G55" s="11" t="s">
+        <v>208</v>
+      </c>
       <c r="H55" s="4"/>
-      <c r="I55" s="4" t="s">
-        <v>128</v>
+      <c r="I55" s="11" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="3">
-        <v>2110</v>
+        <v>2</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C56" s="3">
-        <v>21</v>
+        <v>-1</v>
       </c>
       <c r="D56" s="3">
-        <v>2110</v>
+        <v>2</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>130</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G56" s="4"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="3">
-        <v>2111</v>
+        <v>21</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C57" s="3">
+        <v>2</v>
+      </c>
+      <c r="D57" s="3">
         <v>21</v>
-      </c>
-      <c r="D57" s="3">
-        <v>2111</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>132</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G57" s="4"/>
       <c r="H57" s="4"/>
       <c r="I57" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="3">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C58" s="3">
         <v>21</v>
       </c>
       <c r="D58" s="3">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H58" s="4"/>
       <c r="I58" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="3">
-        <v>2113</v>
+        <v>2111</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C59" s="3">
         <v>21</v>
       </c>
       <c r="D59" s="3">
-        <v>2113</v>
+        <v>2111</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H59" s="4"/>
       <c r="I59" s="4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="3">
-        <v>22</v>
+        <v>2112</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C60" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D60" s="3">
-        <v>22</v>
+        <v>2112</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G60" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>134</v>
+      </c>
       <c r="H60" s="4"/>
       <c r="I60" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="3">
-        <v>2201</v>
+        <v>2113</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C61" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D61" s="3">
-        <v>2201</v>
+        <v>2113</v>
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H61" s="4"/>
       <c r="I61" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="3">
-        <v>2202</v>
+        <v>22</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C62" s="3">
+        <v>2</v>
+      </c>
+      <c r="D62" s="3">
         <v>22</v>
-      </c>
-      <c r="D62" s="3">
-        <v>2202</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>140</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G62" s="4"/>
       <c r="H62" s="4"/>
       <c r="I62" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C63" s="3">
         <v>22</v>
       </c>
       <c r="D63" s="3">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H63" s="4"/>
       <c r="I63" s="4" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="3">
-        <v>23</v>
+        <v>2202</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C64" s="3">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D64" s="3">
-        <v>23</v>
+        <v>2202</v>
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G64" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>140</v>
+      </c>
       <c r="H64" s="4"/>
       <c r="I64" s="4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="3">
-        <v>2301</v>
+        <v>2203</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C65" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D65" s="3">
-        <v>2301</v>
+        <v>2203</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H65" s="4"/>
       <c r="I65" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="3">
-        <v>2302</v>
+        <v>23</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="C66" s="3">
+        <v>2</v>
+      </c>
+      <c r="D66" s="3">
         <v>23</v>
-      </c>
-      <c r="D66" s="3">
-        <v>2302</v>
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
@@ -5078,119 +5090,119 @@
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
       <c r="I66" s="4" t="s">
-        <v>75</v>
+        <v>143</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="3">
-        <v>23021</v>
+        <v>2301</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C67" s="3">
-        <v>2302</v>
+        <v>23</v>
       </c>
       <c r="D67" s="3">
-        <v>23021</v>
+        <v>2301</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H67" s="4"/>
       <c r="I67" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="3">
-        <v>23022</v>
+        <v>2302</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="C68" s="3">
+        <v>23</v>
+      </c>
+      <c r="D68" s="3">
         <v>2302</v>
-      </c>
-      <c r="D68" s="3">
-        <v>23022</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>149</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G68" s="4"/>
       <c r="H68" s="4"/>
       <c r="I68" s="4" t="s">
-        <v>148</v>
+        <v>75</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="3">
-        <v>2303</v>
+        <v>23021</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C69" s="3">
-        <v>23</v>
+        <v>2302</v>
       </c>
       <c r="D69" s="3">
-        <v>2303</v>
+        <v>23021</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G69" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>147</v>
+      </c>
       <c r="H69" s="4"/>
       <c r="I69" s="4" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="3">
-        <v>23031</v>
+        <v>23022</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>65</v>
+        <v>148</v>
       </c>
       <c r="C70" s="3">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="D70" s="3">
-        <v>23031</v>
+        <v>23022</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H70" s="4"/>
       <c r="I70" s="4" t="s">
-        <v>65</v>
+        <v>148</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="3">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>74</v>
+        <v>150</v>
       </c>
       <c r="C71" s="3">
         <v>23</v>
       </c>
       <c r="D71" s="3">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3" t="s">
@@ -5199,465 +5211,465 @@
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
       <c r="I71" s="4" t="s">
-        <v>74</v>
+        <v>150</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="3">
-        <v>23041</v>
+        <v>23031</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>152</v>
+        <v>65</v>
       </c>
       <c r="C72" s="3">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="D72" s="3">
-        <v>23041</v>
+        <v>23031</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H72" s="4"/>
       <c r="I72" s="4" t="s">
-        <v>152</v>
+        <v>65</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="3">
-        <v>23042</v>
+        <v>2304</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>154</v>
+        <v>74</v>
       </c>
       <c r="C73" s="3">
+        <v>23</v>
+      </c>
+      <c r="D73" s="3">
         <v>2304</v>
-      </c>
-      <c r="D73" s="3">
-        <v>23042</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>155</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G73" s="4"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4" t="s">
-        <v>154</v>
+        <v>74</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="3">
-        <v>23043</v>
-      </c>
-      <c r="B74" s="11" t="s">
-        <v>193</v>
+        <v>23041</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>152</v>
       </c>
       <c r="C74" s="3">
         <v>2304</v>
       </c>
       <c r="D74" s="3">
-        <v>23043</v>
+        <v>23041</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G74" s="11" t="s">
-        <v>194</v>
+      <c r="G74" s="4" t="s">
+        <v>153</v>
       </c>
       <c r="H74" s="4"/>
-      <c r="I74" s="11" t="s">
-        <v>193</v>
+      <c r="I74" s="4" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="3">
-        <v>23044</v>
-      </c>
-      <c r="B75" s="11" t="s">
-        <v>195</v>
+        <v>23042</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>154</v>
       </c>
       <c r="C75" s="3">
         <v>2304</v>
       </c>
       <c r="D75" s="3">
-        <v>23044</v>
+        <v>23042</v>
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G75" s="11" t="s">
-        <v>196</v>
+      <c r="G75" s="4" t="s">
+        <v>155</v>
       </c>
       <c r="H75" s="4"/>
-      <c r="I75" s="11" t="s">
-        <v>195</v>
+      <c r="I75" s="4" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="3">
-        <v>23045</v>
+        <v>23043</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C76" s="3">
         <v>2304</v>
       </c>
       <c r="D76" s="3">
-        <v>23045</v>
+        <v>23043</v>
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G76" s="11" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="H76" s="4"/>
       <c r="I76" s="11" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="3">
-        <v>23046</v>
+        <v>23044</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C77" s="3">
         <v>2304</v>
       </c>
       <c r="D77" s="3">
-        <v>23046</v>
+        <v>23044</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G77" s="11" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="H77" s="4"/>
       <c r="I77" s="11" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="3">
-        <v>23047</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>156</v>
+        <v>23045</v>
+      </c>
+      <c r="B78" s="11" t="s">
+        <v>197</v>
       </c>
       <c r="C78" s="3">
         <v>2304</v>
       </c>
       <c r="D78" s="3">
-        <v>23047</v>
+        <v>23045</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G78" s="4" t="s">
-        <v>157</v>
+      <c r="G78" s="11" t="s">
+        <v>198</v>
       </c>
       <c r="H78" s="4"/>
-      <c r="I78" s="4" t="s">
-        <v>156</v>
+      <c r="I78" s="11" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="3">
-        <v>2305</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>111</v>
+        <v>23046</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>199</v>
       </c>
       <c r="C79" s="3">
-        <v>23</v>
+        <v>2304</v>
       </c>
       <c r="D79" s="3">
-        <v>2305</v>
+        <v>23046</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G79" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G79" s="11" t="s">
+        <v>200</v>
+      </c>
       <c r="H79" s="4"/>
-      <c r="I79" s="4" t="s">
-        <v>111</v>
+      <c r="I79" s="11" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="3">
-        <v>23051</v>
+        <v>23047</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C80" s="3">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="D80" s="3">
-        <v>23051</v>
+        <v>23047</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H80" s="4"/>
       <c r="I80" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="3">
-        <v>23052</v>
+        <v>2305</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>160</v>
+        <v>111</v>
       </c>
       <c r="C81" s="3">
+        <v>23</v>
+      </c>
+      <c r="D81" s="3">
         <v>2305</v>
-      </c>
-      <c r="D81" s="3">
-        <v>23052</v>
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>161</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G81" s="4"/>
       <c r="H81" s="4"/>
       <c r="I81" s="4" t="s">
-        <v>160</v>
+        <v>111</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="3">
-        <v>23053</v>
+        <v>23051</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C82" s="3">
         <v>2305</v>
       </c>
       <c r="D82" s="3">
-        <v>23053</v>
+        <v>23051</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H82" s="4"/>
       <c r="I82" s="4" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="3">
-        <v>23054</v>
+        <v>23052</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C83" s="3">
         <v>2305</v>
       </c>
       <c r="D83" s="3">
-        <v>23054</v>
+        <v>23052</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H83" s="4"/>
       <c r="I83" s="4" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
-        <v>23055</v>
+        <v>23053</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C84" s="3">
         <v>2305</v>
       </c>
       <c r="D84" s="3">
-        <v>23055</v>
+        <v>23053</v>
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="H84" s="4"/>
       <c r="I84" s="4" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="3">
-        <v>23056</v>
+        <v>23054</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C85" s="3">
         <v>2305</v>
       </c>
       <c r="D85" s="3">
-        <v>23056</v>
+        <v>23054</v>
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="H85" s="4"/>
       <c r="I85" s="4" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="3">
-        <v>2306</v>
+        <v>23055</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>92</v>
+        <v>166</v>
       </c>
       <c r="C86" s="3">
-        <v>23</v>
+        <v>2305</v>
       </c>
       <c r="D86" s="3">
-        <v>2306</v>
+        <v>23055</v>
       </c>
       <c r="E86" s="3"/>
       <c r="F86" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G86" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>167</v>
+      </c>
       <c r="H86" s="4"/>
       <c r="I86" s="4" t="s">
-        <v>92</v>
+        <v>166</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="3">
-        <v>23061</v>
+        <v>23056</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C87" s="3">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="D87" s="3">
-        <v>23061</v>
+        <v>23056</v>
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H87" s="4"/>
       <c r="I87" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="3">
-        <v>24</v>
+        <v>2306</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>172</v>
+        <v>92</v>
       </c>
       <c r="C88" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D88" s="3">
-        <v>24</v>
-      </c>
-      <c r="E88" s="4"/>
+        <v>2306</v>
+      </c>
+      <c r="E88" s="3"/>
       <c r="F88" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G88" s="4"/>
       <c r="H88" s="4"/>
       <c r="I88" s="4" t="s">
-        <v>172</v>
+        <v>92</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" s="3">
-        <v>2401</v>
+        <v>23061</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C89" s="3">
-        <v>24</v>
+        <v>2306</v>
       </c>
       <c r="D89" s="3">
-        <v>2401</v>
-      </c>
-      <c r="E89" s="4"/>
+        <v>23061</v>
+      </c>
+      <c r="E89" s="3"/>
       <c r="F89" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H89" s="4"/>
       <c r="I89" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C90" s="3">
         <v>2</v>
       </c>
       <c r="D90" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E90" s="4"/>
       <c r="F90" s="3" t="s">
@@ -5666,155 +5678,178 @@
       <c r="G90" s="4"/>
       <c r="H90" s="4"/>
       <c r="I90" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="3">
-        <v>2501</v>
+        <v>2401</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C91" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D91" s="3">
-        <v>2501</v>
-      </c>
-      <c r="E91" s="3"/>
+        <v>2401</v>
+      </c>
+      <c r="E91" s="4"/>
       <c r="F91" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="H91" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="H91" s="4"/>
       <c r="I91" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="3">
-        <v>2502</v>
+        <v>25</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C92" s="3">
+        <v>2</v>
+      </c>
+      <c r="D92" s="3">
         <v>25</v>
       </c>
-      <c r="D92" s="3">
-        <v>2502</v>
-      </c>
-      <c r="E92" s="3"/>
+      <c r="E92" s="4"/>
       <c r="F92" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G92" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="H92" s="5"/>
-      <c r="I92" s="5" t="s">
-        <v>177</v>
+        <v>36</v>
+      </c>
+      <c r="G92" s="4"/>
+      <c r="H92" s="4"/>
+      <c r="I92" s="4" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="3">
-        <v>2503</v>
+        <v>2501</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C93" s="3">
         <v>25</v>
       </c>
       <c r="D93" s="3">
-        <v>2503</v>
+        <v>2501</v>
       </c>
       <c r="E93" s="3"/>
       <c r="F93" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="H93" s="4"/>
+        <v>176</v>
+      </c>
+      <c r="H93" s="3"/>
       <c r="I93" s="4" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" s="3">
-        <v>26</v>
+        <v>2502</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C94" s="3">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D94" s="3">
-        <v>26</v>
+        <v>2502</v>
       </c>
       <c r="E94" s="3"/>
       <c r="F94" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G94" s="4"/>
-      <c r="H94" s="4"/>
-      <c r="I94" s="4" t="s">
-        <v>181</v>
+        <v>39</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H94" s="5"/>
+      <c r="I94" s="5" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="3">
-        <v>2601</v>
+        <v>2503</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C95" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D95" s="3">
-        <v>2601</v>
-      </c>
-      <c r="E95" s="4"/>
+        <v>2503</v>
+      </c>
+      <c r="E95" s="3"/>
       <c r="F95" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H95" s="4"/>
       <c r="I95" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" s="3">
-        <v>1904</v>
-      </c>
-      <c r="B96" s="6" t="s">
-        <v>205</v>
+        <v>26</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>181</v>
       </c>
       <c r="C96" s="3">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D96" s="3">
-        <v>1904</v>
+        <v>26</v>
       </c>
       <c r="E96" s="3"/>
       <c r="F96" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G96" s="6" t="s">
-        <v>206</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G96" s="4"/>
       <c r="H96" s="4"/>
-      <c r="I96" s="6" t="s">
-        <v>205</v>
+      <c r="I96" s="4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A97" s="3">
+        <v>2601</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C97" s="3">
+        <v>26</v>
+      </c>
+      <c r="D97" s="3">
+        <v>2601</v>
+      </c>
+      <c r="E97" s="4"/>
+      <c r="F97" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G97" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="H97" s="4"/>
+      <c r="I97" s="4" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Code\CSharp\semix\xuankaizhi\netcore_semix_cuga_calibration\Sources\Cuga-Calibration-Solution\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60155F2A-A4DF-4302-BD63-789F700D7C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94FBE5BB-E979-4586-931C-895E1F979626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4778,7 +4778,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>205</v>
@@ -4787,7 +4787,7 @@
         <v>19</v>
       </c>
       <c r="D54" s="3">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3" t="s">
@@ -4803,7 +4803,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="3">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>206</v>
@@ -4812,7 +4812,7 @@
         <v>19</v>
       </c>
       <c r="D55" s="3">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3" t="s">

--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Code\CSharp\semix\xuankaizhi\netcore_semix_cuga_calibration\Sources\Cuga-Calibration-Solution\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A88E05B-D443-4BF4-B2C7-BC7DD2CCBF76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94FBE5BB-E979-4586-931C-895E1F979626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SysUser" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="209">
   <si>
     <t>Id</t>
   </si>
@@ -717,6 +717,22 @@
   </si>
   <si>
     <t>CugaCalibration.ViewModels.Fourier.FourierSideChannelSpecularBlockerViewModel</t>
+  </si>
+  <si>
+    <t>Center Channel Flexible Aperture V1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Center Channel Specular Blocker V1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Fourier.V0FourierCenterChannelFlexibleApertureViewModel</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Fourier.V0FourierCenterChannelSpecularBlockerViewModel</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3438,7 +3454,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:I95"/>
+  <dimension ref="A1:I97"/>
   <sheetFormatPr defaultColWidth="19.75" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.75" style="1"/>
@@ -4762,308 +4778,310 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
-        <v>2</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>127</v>
+        <v>1904</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>205</v>
       </c>
       <c r="C54" s="3">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="D54" s="3">
-        <v>2</v>
+        <v>1904</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G54" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G54" s="11" t="s">
+        <v>207</v>
+      </c>
       <c r="H54" s="4"/>
-      <c r="I54" s="4" t="s">
-        <v>127</v>
+      <c r="I54" s="11" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="3">
-        <v>21</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>128</v>
+        <v>1905</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>206</v>
       </c>
       <c r="C55" s="3">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D55" s="3">
-        <v>21</v>
+        <v>1905</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G55" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G55" s="11" t="s">
+        <v>208</v>
+      </c>
       <c r="H55" s="4"/>
-      <c r="I55" s="4" t="s">
-        <v>128</v>
+      <c r="I55" s="11" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="3">
-        <v>2110</v>
+        <v>2</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C56" s="3">
-        <v>21</v>
+        <v>-1</v>
       </c>
       <c r="D56" s="3">
-        <v>2110</v>
+        <v>2</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>130</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G56" s="4"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="3">
-        <v>2111</v>
+        <v>21</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C57" s="3">
+        <v>2</v>
+      </c>
+      <c r="D57" s="3">
         <v>21</v>
-      </c>
-      <c r="D57" s="3">
-        <v>2111</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>132</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G57" s="4"/>
       <c r="H57" s="4"/>
       <c r="I57" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="3">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C58" s="3">
         <v>21</v>
       </c>
       <c r="D58" s="3">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H58" s="4"/>
       <c r="I58" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="3">
-        <v>2113</v>
+        <v>2111</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C59" s="3">
         <v>21</v>
       </c>
       <c r="D59" s="3">
-        <v>2113</v>
+        <v>2111</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H59" s="4"/>
       <c r="I59" s="4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="3">
-        <v>22</v>
+        <v>2112</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C60" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D60" s="3">
-        <v>22</v>
+        <v>2112</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G60" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>134</v>
+      </c>
       <c r="H60" s="4"/>
       <c r="I60" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="3">
-        <v>2201</v>
+        <v>2113</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C61" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D61" s="3">
-        <v>2201</v>
+        <v>2113</v>
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H61" s="4"/>
       <c r="I61" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="3">
-        <v>2202</v>
+        <v>22</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C62" s="3">
+        <v>2</v>
+      </c>
+      <c r="D62" s="3">
         <v>22</v>
-      </c>
-      <c r="D62" s="3">
-        <v>2202</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>140</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G62" s="4"/>
       <c r="H62" s="4"/>
       <c r="I62" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C63" s="3">
         <v>22</v>
       </c>
       <c r="D63" s="3">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H63" s="4"/>
       <c r="I63" s="4" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="3">
-        <v>23</v>
+        <v>2202</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C64" s="3">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D64" s="3">
-        <v>23</v>
+        <v>2202</v>
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G64" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>140</v>
+      </c>
       <c r="H64" s="4"/>
       <c r="I64" s="4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="3">
-        <v>2301</v>
+        <v>2203</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C65" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D65" s="3">
-        <v>2301</v>
+        <v>2203</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H65" s="4"/>
       <c r="I65" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="3">
-        <v>2302</v>
+        <v>23</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="C66" s="3">
+        <v>2</v>
+      </c>
+      <c r="D66" s="3">
         <v>23</v>
-      </c>
-      <c r="D66" s="3">
-        <v>2302</v>
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
@@ -5072,119 +5090,119 @@
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
       <c r="I66" s="4" t="s">
-        <v>75</v>
+        <v>143</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="3">
-        <v>23021</v>
+        <v>2301</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C67" s="3">
-        <v>2302</v>
+        <v>23</v>
       </c>
       <c r="D67" s="3">
-        <v>23021</v>
+        <v>2301</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H67" s="4"/>
       <c r="I67" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="3">
-        <v>23022</v>
+        <v>2302</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="C68" s="3">
+        <v>23</v>
+      </c>
+      <c r="D68" s="3">
         <v>2302</v>
-      </c>
-      <c r="D68" s="3">
-        <v>23022</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>149</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G68" s="4"/>
       <c r="H68" s="4"/>
       <c r="I68" s="4" t="s">
-        <v>148</v>
+        <v>75</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="3">
-        <v>2303</v>
+        <v>23021</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C69" s="3">
-        <v>23</v>
+        <v>2302</v>
       </c>
       <c r="D69" s="3">
-        <v>2303</v>
+        <v>23021</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G69" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>147</v>
+      </c>
       <c r="H69" s="4"/>
       <c r="I69" s="4" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="3">
-        <v>23031</v>
+        <v>23022</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>65</v>
+        <v>148</v>
       </c>
       <c r="C70" s="3">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="D70" s="3">
-        <v>23031</v>
+        <v>23022</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H70" s="4"/>
       <c r="I70" s="4" t="s">
-        <v>65</v>
+        <v>148</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="3">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>74</v>
+        <v>150</v>
       </c>
       <c r="C71" s="3">
         <v>23</v>
       </c>
       <c r="D71" s="3">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3" t="s">
@@ -5193,465 +5211,465 @@
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
       <c r="I71" s="4" t="s">
-        <v>74</v>
+        <v>150</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="3">
-        <v>23041</v>
+        <v>23031</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>152</v>
+        <v>65</v>
       </c>
       <c r="C72" s="3">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="D72" s="3">
-        <v>23041</v>
+        <v>23031</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H72" s="4"/>
       <c r="I72" s="4" t="s">
-        <v>152</v>
+        <v>65</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="3">
-        <v>23042</v>
+        <v>2304</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>154</v>
+        <v>74</v>
       </c>
       <c r="C73" s="3">
+        <v>23</v>
+      </c>
+      <c r="D73" s="3">
         <v>2304</v>
-      </c>
-      <c r="D73" s="3">
-        <v>23042</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>155</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G73" s="4"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4" t="s">
-        <v>154</v>
+        <v>74</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="3">
-        <v>23043</v>
-      </c>
-      <c r="B74" s="11" t="s">
-        <v>193</v>
+        <v>23041</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>152</v>
       </c>
       <c r="C74" s="3">
         <v>2304</v>
       </c>
       <c r="D74" s="3">
-        <v>23043</v>
+        <v>23041</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G74" s="11" t="s">
-        <v>194</v>
+      <c r="G74" s="4" t="s">
+        <v>153</v>
       </c>
       <c r="H74" s="4"/>
-      <c r="I74" s="11" t="s">
-        <v>193</v>
+      <c r="I74" s="4" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="3">
-        <v>23044</v>
-      </c>
-      <c r="B75" s="11" t="s">
-        <v>195</v>
+        <v>23042</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>154</v>
       </c>
       <c r="C75" s="3">
         <v>2304</v>
       </c>
       <c r="D75" s="3">
-        <v>23044</v>
+        <v>23042</v>
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G75" s="11" t="s">
-        <v>196</v>
+      <c r="G75" s="4" t="s">
+        <v>155</v>
       </c>
       <c r="H75" s="4"/>
-      <c r="I75" s="11" t="s">
-        <v>195</v>
+      <c r="I75" s="4" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="3">
-        <v>23045</v>
+        <v>23043</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C76" s="3">
         <v>2304</v>
       </c>
       <c r="D76" s="3">
-        <v>23045</v>
+        <v>23043</v>
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G76" s="11" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="H76" s="4"/>
       <c r="I76" s="11" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="3">
-        <v>23046</v>
+        <v>23044</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C77" s="3">
         <v>2304</v>
       </c>
       <c r="D77" s="3">
-        <v>23046</v>
+        <v>23044</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G77" s="11" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="H77" s="4"/>
       <c r="I77" s="11" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="3">
-        <v>23047</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>156</v>
+        <v>23045</v>
+      </c>
+      <c r="B78" s="11" t="s">
+        <v>197</v>
       </c>
       <c r="C78" s="3">
         <v>2304</v>
       </c>
       <c r="D78" s="3">
-        <v>23047</v>
+        <v>23045</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G78" s="4" t="s">
-        <v>157</v>
+      <c r="G78" s="11" t="s">
+        <v>198</v>
       </c>
       <c r="H78" s="4"/>
-      <c r="I78" s="4" t="s">
-        <v>156</v>
+      <c r="I78" s="11" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="3">
-        <v>2305</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>111</v>
+        <v>23046</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>199</v>
       </c>
       <c r="C79" s="3">
-        <v>23</v>
+        <v>2304</v>
       </c>
       <c r="D79" s="3">
-        <v>2305</v>
+        <v>23046</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G79" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G79" s="11" t="s">
+        <v>200</v>
+      </c>
       <c r="H79" s="4"/>
-      <c r="I79" s="4" t="s">
-        <v>111</v>
+      <c r="I79" s="11" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="3">
-        <v>23051</v>
+        <v>23047</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C80" s="3">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="D80" s="3">
-        <v>23051</v>
+        <v>23047</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H80" s="4"/>
       <c r="I80" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="3">
-        <v>23052</v>
+        <v>2305</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>160</v>
+        <v>111</v>
       </c>
       <c r="C81" s="3">
+        <v>23</v>
+      </c>
+      <c r="D81" s="3">
         <v>2305</v>
-      </c>
-      <c r="D81" s="3">
-        <v>23052</v>
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>161</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G81" s="4"/>
       <c r="H81" s="4"/>
       <c r="I81" s="4" t="s">
-        <v>160</v>
+        <v>111</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="3">
-        <v>23053</v>
+        <v>23051</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C82" s="3">
         <v>2305</v>
       </c>
       <c r="D82" s="3">
-        <v>23053</v>
+        <v>23051</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H82" s="4"/>
       <c r="I82" s="4" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="3">
-        <v>23054</v>
+        <v>23052</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C83" s="3">
         <v>2305</v>
       </c>
       <c r="D83" s="3">
-        <v>23054</v>
+        <v>23052</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H83" s="4"/>
       <c r="I83" s="4" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
-        <v>23055</v>
+        <v>23053</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C84" s="3">
         <v>2305</v>
       </c>
       <c r="D84" s="3">
-        <v>23055</v>
+        <v>23053</v>
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="H84" s="4"/>
       <c r="I84" s="4" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="3">
-        <v>23056</v>
+        <v>23054</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C85" s="3">
         <v>2305</v>
       </c>
       <c r="D85" s="3">
-        <v>23056</v>
+        <v>23054</v>
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="H85" s="4"/>
       <c r="I85" s="4" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="3">
-        <v>2306</v>
+        <v>23055</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>92</v>
+        <v>166</v>
       </c>
       <c r="C86" s="3">
-        <v>23</v>
+        <v>2305</v>
       </c>
       <c r="D86" s="3">
-        <v>2306</v>
+        <v>23055</v>
       </c>
       <c r="E86" s="3"/>
       <c r="F86" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G86" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>167</v>
+      </c>
       <c r="H86" s="4"/>
       <c r="I86" s="4" t="s">
-        <v>92</v>
+        <v>166</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="3">
-        <v>23061</v>
+        <v>23056</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C87" s="3">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="D87" s="3">
-        <v>23061</v>
+        <v>23056</v>
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H87" s="4"/>
       <c r="I87" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="3">
-        <v>24</v>
+        <v>2306</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>172</v>
+        <v>92</v>
       </c>
       <c r="C88" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D88" s="3">
-        <v>24</v>
-      </c>
-      <c r="E88" s="4"/>
+        <v>2306</v>
+      </c>
+      <c r="E88" s="3"/>
       <c r="F88" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G88" s="4"/>
       <c r="H88" s="4"/>
       <c r="I88" s="4" t="s">
-        <v>172</v>
+        <v>92</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" s="3">
-        <v>2401</v>
+        <v>23061</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C89" s="3">
-        <v>24</v>
+        <v>2306</v>
       </c>
       <c r="D89" s="3">
-        <v>2401</v>
-      </c>
-      <c r="E89" s="4"/>
+        <v>23061</v>
+      </c>
+      <c r="E89" s="3"/>
       <c r="F89" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H89" s="4"/>
       <c r="I89" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C90" s="3">
         <v>2</v>
       </c>
       <c r="D90" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E90" s="4"/>
       <c r="F90" s="3" t="s">
@@ -5660,129 +5678,177 @@
       <c r="G90" s="4"/>
       <c r="H90" s="4"/>
       <c r="I90" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="3">
-        <v>2501</v>
+        <v>2401</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C91" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D91" s="3">
-        <v>2501</v>
-      </c>
-      <c r="E91" s="3"/>
+        <v>2401</v>
+      </c>
+      <c r="E91" s="4"/>
       <c r="F91" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="H91" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="H91" s="4"/>
       <c r="I91" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="3">
-        <v>2502</v>
+        <v>25</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C92" s="3">
+        <v>2</v>
+      </c>
+      <c r="D92" s="3">
         <v>25</v>
       </c>
-      <c r="D92" s="3">
-        <v>2502</v>
-      </c>
-      <c r="E92" s="3"/>
+      <c r="E92" s="4"/>
       <c r="F92" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G92" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="H92" s="5"/>
-      <c r="I92" s="5" t="s">
-        <v>177</v>
+        <v>36</v>
+      </c>
+      <c r="G92" s="4"/>
+      <c r="H92" s="4"/>
+      <c r="I92" s="4" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="3">
-        <v>2503</v>
+        <v>2501</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C93" s="3">
         <v>25</v>
       </c>
       <c r="D93" s="3">
-        <v>2503</v>
+        <v>2501</v>
       </c>
       <c r="E93" s="3"/>
       <c r="F93" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="H93" s="4"/>
+        <v>176</v>
+      </c>
+      <c r="H93" s="3"/>
       <c r="I93" s="4" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" s="3">
-        <v>26</v>
+        <v>2502</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C94" s="3">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D94" s="3">
-        <v>26</v>
+        <v>2502</v>
       </c>
       <c r="E94" s="3"/>
       <c r="F94" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G94" s="4"/>
-      <c r="H94" s="4"/>
-      <c r="I94" s="4" t="s">
-        <v>181</v>
+        <v>39</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H94" s="5"/>
+      <c r="I94" s="5" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="3">
-        <v>2601</v>
+        <v>2503</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C95" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D95" s="3">
-        <v>2601</v>
-      </c>
-      <c r="E95" s="4"/>
+        <v>2503</v>
+      </c>
+      <c r="E95" s="3"/>
       <c r="F95" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H95" s="4"/>
       <c r="I95" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A96" s="3">
+        <v>26</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C96" s="3">
+        <v>2</v>
+      </c>
+      <c r="D96" s="3">
+        <v>26</v>
+      </c>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G96" s="4"/>
+      <c r="H96" s="4"/>
+      <c r="I96" s="4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A97" s="3">
+        <v>2601</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C97" s="3">
+        <v>26</v>
+      </c>
+      <c r="D97" s="3">
+        <v>2601</v>
+      </c>
+      <c r="E97" s="4"/>
+      <c r="F97" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G97" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="H97" s="4"/>
+      <c r="I97" s="4" t="s">
         <v>182</v>
       </c>
     </row>

--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Code\CSharp\semix\xuankaizhi\netcore_semix_cuga_calibration\Sources\Cuga-Calibration-Solution\Assets\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94FBE5BB-E979-4586-931C-895E1F979626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17680" tabRatio="500" firstSheet="3" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="SysUser" sheetId="1" r:id="rId1"/>
@@ -42,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="201">
   <si>
     <t>Id</t>
   </si>
@@ -564,6 +558,30 @@
     <t>CugaCalibration.ViewModels.Common.Windows.Tools.AODWaveform.ChirpGenerateAODWaveformWindowViewModel</t>
   </si>
   <si>
+    <t>Prescan AOD Waveform Electrode Offset V1</t>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Common.Windows.Tools.AODWaveform.V0PrescanAODWaveformElectrodeOffsetWindowViewModel</t>
+  </si>
+  <si>
+    <t>Chirp AOD Waveform Electrode Offset V1</t>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Common.Windows.Tools.AODWaveform.V0ChirpAODWaveformElectrodeOffsetWindowViewModel</t>
+  </si>
+  <si>
+    <t>Prescan AOD Waveform Electrode Offset V2</t>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Common.Windows.Tools.AODWaveform.PrescanAODWaveformElectrodeOffsetWindowViewModel</t>
+  </si>
+  <si>
+    <t>Chirp AOD Waveform Electrode Offset V2</t>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Common.Windows.Tools.AODWaveform.ChirpAODWaveformElectrodeOffsetWindowViewModel</t>
+  </si>
+  <si>
     <t>Chirp AOD Waveform Training</t>
   </si>
   <si>
@@ -585,7 +603,7 @@
     <t>Collection Cross Talk</t>
   </si>
   <si>
-    <t>CugaCalibration.ViewModels.Common.Windows.Tools.Collection.CollectionCrossTalkWindowViewModel</t>
+    <t>CugaCalibration.ViewModels.Common.Windows.Tools.Optics.OpticsCrossTalkWindowViewModel</t>
   </si>
   <si>
     <t>Collection Y Ghost</t>
@@ -673,73 +691,19 @@
   </si>
   <si>
     <t>CugaCalibration.ViewModels.Common.Windows.Management.Permission.RolesManagementViewModel</t>
-  </si>
-  <si>
-    <t>Prescan AOD Waveform Electrode Delay V1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Common.Windows.Tools.AODWaveform.V0PrescanAODWaveformElectrodeDelayWindowViewModel</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Chirp AOD Waveform Electrode Delay V1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Common.Windows.Tools.AODWaveform.V0ChirpAODWaveformElectrodeDelayWindowViewModel</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prescan AOD Waveform Electrode Delay V2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Common.Windows.Tools.AODWaveform.PrescanAODWaveformElectrodeDelayWindowViewModel</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Chirp AOD Waveform Electrode Delay V2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Common.Windows.Tools.AODWaveform.ChirpAODWaveformElectrodeDelayWindowViewModel</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Side Channel Flexible Aperture</t>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Fourier.FourierSideChannelFlexibleApertureViewModel</t>
-  </si>
-  <si>
-    <t>Side Channel Specular Blocker</t>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Fourier.FourierSideChannelSpecularBlockerViewModel</t>
-  </si>
-  <si>
-    <t>Center Channel Flexible Aperture V1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Center Channel Specular Blocker V1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Fourier.V0FourierCenterChannelFlexibleApertureViewModel</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Fourier.V0FourierCenterChannelSpecularBlockerViewModel</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -750,12 +714,6 @@
       <b/>
       <sz val="18"/>
       <color rgb="FF44546A"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -773,27 +731,157 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color rgb="FF44546A"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -806,8 +894,194 @@
         <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -844,6 +1118,104 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -853,25 +1225,166 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyProtection="0">
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -883,179 +1396,106 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Excel Built-in Heading 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="超链接" xfId="1" builtinId="8"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Excel Built-in Heading 2" xfId="49"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -1066,7 +1506,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1094,40 +1534,154 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1186,7 +1740,7 @@
         <a:cs typeface=""/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1303,21 +1857,21 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I42"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="5" width="20.625" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="9" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="1" ht="22.5" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1346,7 +1900,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" ht="20.1" customHeight="1" spans="1:9">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -1373,7 +1927,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" ht="20.1" customHeight="1" spans="1:9">
       <c r="A3" s="8">
         <v>2</v>
       </c>
@@ -1387,9 +1941,7 @@
         <v>13</v>
       </c>
       <c r="E3" s="8"/>
-      <c r="F3" s="9" t="s">
-        <v>11</v>
-      </c>
+      <c r="F3" s="8"/>
       <c r="G3" s="7">
         <v>666666</v>
       </c>
@@ -1400,7 +1952,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="20.1" customHeight="1" spans="1:9">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -1411,7 +1963,7 @@
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
     </row>
-    <row r="5" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" ht="20.1" customHeight="1" spans="1:9">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -1422,7 +1974,7 @@
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
     </row>
-    <row r="6" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" ht="20.1" customHeight="1" spans="1:9">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -1433,7 +1985,7 @@
       <c r="H6" s="8"/>
       <c r="I6" s="8"/>
     </row>
-    <row r="7" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" ht="20.1" customHeight="1" spans="1:9">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -1444,7 +1996,7 @@
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
     </row>
-    <row r="8" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" ht="20.1" customHeight="1" spans="1:9">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -1455,7 +2007,7 @@
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
     </row>
-    <row r="9" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" ht="20.1" customHeight="1" spans="1:9">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -1466,7 +2018,7 @@
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
     </row>
-    <row r="10" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" ht="20.1" customHeight="1" spans="1:9">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -1477,7 +2029,7 @@
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
     </row>
-    <row r="11" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" ht="20.1" customHeight="1" spans="1:9">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -1488,7 +2040,7 @@
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
     </row>
-    <row r="12" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" ht="20.1" customHeight="1" spans="1:9">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -1499,7 +2051,7 @@
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
     </row>
-    <row r="13" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" ht="20.1" customHeight="1" spans="1:9">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -1510,7 +2062,7 @@
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
     </row>
-    <row r="14" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" ht="20.1" customHeight="1" spans="1:9">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -1521,7 +2073,7 @@
       <c r="H14" s="8"/>
       <c r="I14" s="8"/>
     </row>
-    <row r="15" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" ht="20.1" customHeight="1" spans="1:9">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -1532,7 +2084,7 @@
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
     </row>
-    <row r="16" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" ht="20.1" customHeight="1" spans="1:9">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -1543,7 +2095,7 @@
       <c r="H16" s="8"/>
       <c r="I16" s="8"/>
     </row>
-    <row r="17" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" ht="20.1" customHeight="1" spans="1:9">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -1554,7 +2106,7 @@
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
     </row>
-    <row r="18" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" ht="20.1" customHeight="1" spans="1:9">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -1565,7 +2117,7 @@
       <c r="H18" s="8"/>
       <c r="I18" s="8"/>
     </row>
-    <row r="19" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" ht="20.1" customHeight="1" spans="1:9">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -1576,7 +2128,7 @@
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
     </row>
-    <row r="20" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" ht="20.1" customHeight="1" spans="1:9">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -1587,7 +2139,7 @@
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
     </row>
-    <row r="21" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" ht="20.1" customHeight="1" spans="1:9">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -1598,7 +2150,7 @@
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
     </row>
-    <row r="22" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" ht="20.1" customHeight="1" spans="1:9">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -1609,7 +2161,7 @@
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
     </row>
-    <row r="23" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" ht="20.1" customHeight="1" spans="1:9">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -1620,7 +2172,7 @@
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
     </row>
-    <row r="24" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" ht="20.1" customHeight="1" spans="1:9">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -1631,7 +2183,7 @@
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
     </row>
-    <row r="25" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" ht="20.1" customHeight="1" spans="1:9">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
@@ -1642,7 +2194,7 @@
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
     </row>
-    <row r="26" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" ht="20.1" customHeight="1" spans="1:9">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -1653,7 +2205,7 @@
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
     </row>
-    <row r="27" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" ht="20.1" customHeight="1" spans="1:9">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -1664,7 +2216,7 @@
       <c r="H27" s="8"/>
       <c r="I27" s="8"/>
     </row>
-    <row r="28" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" ht="20.1" customHeight="1" spans="1:9">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -1675,7 +2227,7 @@
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
     </row>
-    <row r="29" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" ht="20.1" customHeight="1" spans="1:9">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -1686,7 +2238,7 @@
       <c r="H29" s="8"/>
       <c r="I29" s="8"/>
     </row>
-    <row r="30" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" ht="20.1" customHeight="1" spans="1:9">
       <c r="A30" s="10"/>
       <c r="B30" s="10"/>
       <c r="C30" s="10"/>
@@ -1697,7 +2249,7 @@
       <c r="H30" s="10"/>
       <c r="I30" s="10"/>
     </row>
-    <row r="31" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" ht="20.1" customHeight="1" spans="1:9">
       <c r="A31" s="10"/>
       <c r="B31" s="10"/>
       <c r="C31" s="10"/>
@@ -1708,7 +2260,7 @@
       <c r="H31" s="10"/>
       <c r="I31" s="10"/>
     </row>
-    <row r="32" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" ht="20.1" customHeight="1" spans="1:9">
       <c r="A32" s="10"/>
       <c r="B32" s="10"/>
       <c r="C32" s="10"/>
@@ -1719,7 +2271,7 @@
       <c r="H32" s="10"/>
       <c r="I32" s="10"/>
     </row>
-    <row r="33" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" ht="20.1" customHeight="1" spans="1:9">
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
@@ -1730,7 +2282,7 @@
       <c r="H33" s="10"/>
       <c r="I33" s="10"/>
     </row>
-    <row r="34" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" ht="20.1" customHeight="1" spans="1:9">
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
@@ -1741,7 +2293,7 @@
       <c r="H34" s="10"/>
       <c r="I34" s="10"/>
     </row>
-    <row r="35" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" ht="20.1" customHeight="1" spans="1:9">
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="10"/>
@@ -1752,7 +2304,7 @@
       <c r="H35" s="10"/>
       <c r="I35" s="10"/>
     </row>
-    <row r="36" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" ht="20.1" customHeight="1" spans="1:9">
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="10"/>
@@ -1763,7 +2315,7 @@
       <c r="H36" s="10"/>
       <c r="I36" s="10"/>
     </row>
-    <row r="37" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" ht="20.1" customHeight="1" spans="1:9">
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="10"/>
@@ -1774,7 +2326,7 @@
       <c r="H37" s="10"/>
       <c r="I37" s="10"/>
     </row>
-    <row r="38" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" ht="20.1" customHeight="1" spans="1:9">
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="10"/>
@@ -1785,7 +2337,7 @@
       <c r="H38" s="10"/>
       <c r="I38" s="10"/>
     </row>
-    <row r="39" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" ht="20.1" customHeight="1" spans="1:9">
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="10"/>
@@ -1796,7 +2348,7 @@
       <c r="H39" s="10"/>
       <c r="I39" s="10"/>
     </row>
-    <row r="40" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" ht="20.1" customHeight="1" spans="1:9">
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="10"/>
@@ -1807,7 +2359,7 @@
       <c r="H40" s="10"/>
       <c r="I40" s="10"/>
     </row>
-    <row r="41" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" ht="20.1" customHeight="1" spans="1:9">
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="10"/>
@@ -1818,7 +2370,7 @@
       <c r="H41" s="10"/>
       <c r="I41" s="10"/>
     </row>
-    <row r="42" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" ht="20.1" customHeight="1" spans="1:9">
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="10"/>
@@ -1830,20 +2382,20 @@
       <c r="I42" s="10"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="F3" r:id="rId2" xr:uid="{24ACA4B2-97CF-4E83-B373-7B5A2DFD4F1C}"/>
+    <hyperlink ref="F2" r:id="rId1" display="xuankaizhi@semixchina.com"/>
   </hyperlinks>
-  <pageMargins left="0.70069444444444495" right="0.70069444444444495" top="0.75208333333333299" bottom="0.75208333333333299" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="20.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="45.375" customWidth="1"/>
@@ -1854,7 +2406,7 @@
     <col min="9" max="9" width="28.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="15" customHeight="1" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1883,12 +2435,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" ht="15" customHeight="1" spans="1:9">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C2" s="3">
         <v>-1</v>
@@ -1903,15 +2455,15 @@
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" spans="1:9">
       <c r="A3" s="3">
         <v>11</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="C3" s="3">
         <v>1</v>
@@ -1926,15 +2478,15 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" spans="1:9">
       <c r="A4" s="3">
         <v>1101</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C4" s="3">
         <v>11</v>
@@ -1947,19 +2499,19 @@
         <v>39</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" spans="1:9">
       <c r="A5" s="3">
         <v>1102</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="C5" s="3">
         <v>11</v>
@@ -1972,19 +2524,19 @@
         <v>39</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:9">
       <c r="A6" s="3">
         <v>1103</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C6" s="3">
         <v>11</v>
@@ -1997,19 +2549,19 @@
         <v>39</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" spans="1:9">
       <c r="A7" s="3">
         <v>1104</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="C7" s="3">
         <v>11</v>
@@ -2022,28 +2574,29 @@
         <v>39</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="1" ht="22.5" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2054,7 +2607,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" ht="20.1" customHeight="1" spans="1:3">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -2065,163 +2618,158 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="7">
-        <v>1</v>
-      </c>
-      <c r="B3" s="7">
-        <v>2</v>
-      </c>
-      <c r="C3" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+    </row>
+    <row r="4" ht="20.1" customHeight="1" spans="1:3">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
     </row>
-    <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" ht="20.1" customHeight="1" spans="1:3">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
     </row>
-    <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" ht="20.1" customHeight="1" spans="1:3">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
     </row>
-    <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" ht="20.1" customHeight="1" spans="1:3">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
     </row>
-    <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" ht="20.1" customHeight="1" spans="1:3">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
     </row>
-    <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" ht="20.1" customHeight="1" spans="1:3">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
     </row>
-    <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" ht="20.1" customHeight="1" spans="1:3">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
     </row>
-    <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" ht="20.1" customHeight="1" spans="1:3">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
     </row>
-    <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" ht="20.1" customHeight="1" spans="1:3">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
     </row>
-    <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" ht="20.1" customHeight="1" spans="1:3">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
     </row>
-    <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" ht="20.1" customHeight="1" spans="1:3">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
     </row>
-    <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" ht="20.1" customHeight="1" spans="1:3">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
     </row>
-    <row r="16" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" ht="20.1" customHeight="1" spans="1:3">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
     </row>
-    <row r="17" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" ht="20.1" customHeight="1" spans="1:3">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
     </row>
-    <row r="18" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" ht="20.1" customHeight="1" spans="1:3">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
     </row>
-    <row r="19" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" ht="20.1" customHeight="1" spans="1:3">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
     </row>
-    <row r="20" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" ht="20.1" customHeight="1" spans="1:3">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
     </row>
-    <row r="21" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" ht="20.1" customHeight="1" spans="1:3">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
     </row>
-    <row r="22" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" ht="20.1" customHeight="1" spans="1:3">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
     </row>
-    <row r="23" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" ht="20.1" customHeight="1" spans="1:3">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
     </row>
-    <row r="24" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" ht="20.1" customHeight="1" spans="1:3">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
     </row>
-    <row r="25" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" ht="20.1" customHeight="1" spans="1:3">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
     </row>
-    <row r="26" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" ht="20.1" customHeight="1" spans="1:3">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
     </row>
-    <row r="27" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" ht="20.1" customHeight="1" spans="1:3">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
     </row>
-    <row r="28" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" ht="20.1" customHeight="1" spans="1:3">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
     </row>
-    <row r="29" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" ht="20.1" customHeight="1" spans="1:3">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
-  <pageMargins left="0.75208333333333299" right="0.75208333333333299" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="1" ht="22.5" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2232,7 +2780,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" ht="20.1" customHeight="1" spans="1:3">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -2243,7 +2791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" ht="20.1" customHeight="1" spans="1:3">
       <c r="A3" s="8">
         <v>2</v>
       </c>
@@ -2254,152 +2802,153 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="20.1" customHeight="1" spans="1:3">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
     </row>
-    <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" ht="20.1" customHeight="1" spans="1:3">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
     </row>
-    <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" ht="20.1" customHeight="1" spans="1:3">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
     </row>
-    <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" ht="20.1" customHeight="1" spans="1:3">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
     </row>
-    <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" ht="20.1" customHeight="1" spans="1:3">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
     </row>
-    <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" ht="20.1" customHeight="1" spans="1:3">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
     </row>
-    <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" ht="20.1" customHeight="1" spans="1:3">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
     </row>
-    <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" ht="20.1" customHeight="1" spans="1:3">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
     </row>
-    <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" ht="20.1" customHeight="1" spans="1:3">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
     </row>
-    <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" ht="20.1" customHeight="1" spans="1:3">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
     </row>
-    <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" ht="20.1" customHeight="1" spans="1:3">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
     </row>
-    <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" ht="20.1" customHeight="1" spans="1:3">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
     </row>
-    <row r="16" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" ht="20.1" customHeight="1" spans="1:3">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
     </row>
-    <row r="17" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" ht="20.1" customHeight="1" spans="1:3">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
     </row>
-    <row r="18" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" ht="20.1" customHeight="1" spans="1:3">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
     </row>
-    <row r="19" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" ht="20.1" customHeight="1" spans="1:3">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
     </row>
-    <row r="20" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" ht="20.1" customHeight="1" spans="1:3">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
     </row>
-    <row r="21" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" ht="20.1" customHeight="1" spans="1:3">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
     </row>
-    <row r="22" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" ht="20.1" customHeight="1" spans="1:3">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
     </row>
-    <row r="23" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" ht="20.1" customHeight="1" spans="1:3">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
     </row>
-    <row r="24" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" ht="20.1" customHeight="1" spans="1:3">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
     </row>
-    <row r="25" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" ht="20.1" customHeight="1" spans="1:3">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
     </row>
-    <row r="26" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" ht="20.1" customHeight="1" spans="1:3">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
     </row>
-    <row r="27" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" ht="20.1" customHeight="1" spans="1:3">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
     </row>
-    <row r="28" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" ht="20.1" customHeight="1" spans="1:3">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
     </row>
-    <row r="29" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" ht="20.1" customHeight="1" spans="1:3">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
-  <pageMargins left="0.75208333333333299" right="0.75208333333333299" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="6" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="1" ht="22.5" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2419,7 +2968,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" ht="20.1" customHeight="1" spans="1:6">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -2439,7 +2988,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" ht="20.1" customHeight="1" spans="1:6">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -2447,7 +2996,7 @@
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
     </row>
-    <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="20.1" customHeight="1" spans="1:6">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -2455,7 +3004,7 @@
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
     </row>
-    <row r="5" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" ht="20.1" customHeight="1" spans="1:6">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -2463,7 +3012,7 @@
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" ht="20.1" customHeight="1" spans="1:6">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2471,7 +3020,7 @@
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
     </row>
-    <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" ht="20.1" customHeight="1" spans="1:6">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -2479,7 +3028,7 @@
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
     </row>
-    <row r="8" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" ht="20.1" customHeight="1" spans="1:6">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -2487,7 +3036,7 @@
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" ht="20.1" customHeight="1" spans="1:6">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -2495,7 +3044,7 @@
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
     </row>
-    <row r="10" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" ht="20.1" customHeight="1" spans="1:6">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -2503,7 +3052,7 @@
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" ht="20.1" customHeight="1" spans="1:6">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -2511,7 +3060,7 @@
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
     </row>
-    <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" ht="20.1" customHeight="1" spans="1:6">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -2519,7 +3068,7 @@
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
     </row>
-    <row r="13" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" ht="20.1" customHeight="1" spans="1:6">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -2527,7 +3076,7 @@
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
     </row>
-    <row r="14" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" ht="20.1" customHeight="1" spans="1:6">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -2535,7 +3084,7 @@
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
     </row>
-    <row r="15" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" ht="20.1" customHeight="1" spans="1:6">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -2543,7 +3092,7 @@
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
     </row>
-    <row r="16" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" ht="20.1" customHeight="1" spans="1:6">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -2551,7 +3100,7 @@
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
     </row>
-    <row r="17" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" ht="20.1" customHeight="1" spans="1:6">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -2559,7 +3108,7 @@
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
     </row>
-    <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" ht="20.1" customHeight="1" spans="1:6">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -2567,7 +3116,7 @@
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
     </row>
-    <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" ht="20.1" customHeight="1" spans="1:6">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -2575,7 +3124,7 @@
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
     </row>
-    <row r="20" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" ht="20.1" customHeight="1" spans="1:6">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -2583,7 +3132,7 @@
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
     </row>
-    <row r="21" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" ht="20.1" customHeight="1" spans="1:6">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -2591,7 +3140,7 @@
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
     </row>
-    <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" ht="20.1" customHeight="1" spans="1:6">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -2599,7 +3148,7 @@
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
     </row>
-    <row r="23" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" ht="20.1" customHeight="1" spans="1:6">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -2607,7 +3156,7 @@
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
     </row>
-    <row r="24" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" ht="20.1" customHeight="1" spans="1:6">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -2616,21 +3165,22 @@
       <c r="F24" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
-  <pageMargins left="0.70069444444444495" right="0.70069444444444495" top="0.75208333333333299" bottom="0.75208333333333299" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="5" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="1" ht="22.5" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2647,7 +3197,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" ht="20.1" customHeight="1" spans="1:5">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -2664,7 +3214,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" ht="20.1" customHeight="1" spans="1:5">
       <c r="A3" s="7">
         <v>2</v>
       </c>
@@ -2681,7 +3231,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="20.1" customHeight="1" spans="1:5">
       <c r="A4" s="7">
         <v>3</v>
       </c>
@@ -2698,189 +3248,189 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" ht="20.1" customHeight="1" spans="1:5">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
     </row>
-    <row r="6" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" ht="20.1" customHeight="1" spans="1:5">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
     </row>
-    <row r="7" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" ht="20.1" customHeight="1" spans="1:5">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
     </row>
-    <row r="8" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" ht="20.1" customHeight="1" spans="1:5">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
     </row>
-    <row r="9" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" ht="20.1" customHeight="1" spans="1:5">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
     </row>
-    <row r="10" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" ht="20.1" customHeight="1" spans="1:5">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
     </row>
-    <row r="11" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" ht="20.1" customHeight="1" spans="1:5">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
     </row>
-    <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" ht="20.1" customHeight="1" spans="1:5">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
     </row>
-    <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" ht="20.1" customHeight="1" spans="1:5">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
     </row>
-    <row r="14" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" ht="20.1" customHeight="1" spans="1:5">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
     </row>
-    <row r="15" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" ht="20.1" customHeight="1" spans="1:5">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
     </row>
-    <row r="16" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" ht="20.1" customHeight="1" spans="1:5">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
     </row>
-    <row r="17" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" ht="20.1" customHeight="1" spans="1:5">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
     </row>
-    <row r="18" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" ht="20.1" customHeight="1" spans="1:5">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
     </row>
-    <row r="19" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" ht="20.1" customHeight="1" spans="1:5">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
     </row>
-    <row r="20" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" ht="20.1" customHeight="1" spans="1:5">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
     </row>
-    <row r="21" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" ht="20.1" customHeight="1" spans="1:5">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
     </row>
-    <row r="22" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" ht="20.1" customHeight="1" spans="1:5">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
     </row>
-    <row r="23" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" ht="20.1" customHeight="1" spans="1:5">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
     </row>
-    <row r="24" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" ht="20.1" customHeight="1" spans="1:5">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
     </row>
-    <row r="25" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" ht="20.1" customHeight="1" spans="1:5">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
     </row>
-    <row r="26" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" ht="20.1" customHeight="1" spans="1:5">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
     </row>
-    <row r="27" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" ht="20.1" customHeight="1" spans="1:5">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
     </row>
-    <row r="28" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" ht="20.1" customHeight="1" spans="1:5">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
     </row>
-    <row r="29" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" ht="20.1" customHeight="1" spans="1:5">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
     </row>
-    <row r="30" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" ht="20.1" customHeight="1" spans="1:5">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
     </row>
-    <row r="31" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" ht="20.1" customHeight="1" spans="1:5">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -2888,25 +3438,24 @@
       <c r="E31" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
-  <pageMargins left="0.70069444444444495" right="0.70069444444444495" top="0.75208333333333299" bottom="0.75208333333333299" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="20.625" customWidth="1"/>
-    <col min="2" max="2" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="20.625" customWidth="1"/>
     <col min="3" max="3" width="24.25" customWidth="1"/>
-    <col min="4" max="4" width="20.625" customWidth="1"/>
-    <col min="5" max="5" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="1" ht="22.5" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2923,7 +3472,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" ht="20.1" customHeight="1" spans="1:5">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -2940,7 +3489,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" ht="20.1" customHeight="1" spans="1:5">
       <c r="A3" s="7">
         <v>2</v>
       </c>
@@ -2957,7 +3506,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="20.1" customHeight="1" spans="1:5">
       <c r="A4" s="7">
         <v>3</v>
       </c>
@@ -2974,7 +3523,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" ht="20.1" customHeight="1" spans="1:5">
       <c r="A5" s="8">
         <v>4</v>
       </c>
@@ -2991,182 +3540,182 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" ht="20.1" customHeight="1" spans="1:5">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
     </row>
-    <row r="7" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" ht="20.1" customHeight="1" spans="1:5">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
     </row>
-    <row r="8" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" ht="20.1" customHeight="1" spans="1:5">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
     </row>
-    <row r="9" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" ht="20.1" customHeight="1" spans="1:5">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
     </row>
-    <row r="10" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" ht="20.1" customHeight="1" spans="1:5">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
     </row>
-    <row r="11" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" ht="20.1" customHeight="1" spans="1:5">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
     </row>
-    <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" ht="20.1" customHeight="1" spans="1:5">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
     </row>
-    <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" ht="20.1" customHeight="1" spans="1:5">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
     </row>
-    <row r="14" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" ht="20.1" customHeight="1" spans="1:5">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
     </row>
-    <row r="15" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" ht="20.1" customHeight="1" spans="1:5">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
     </row>
-    <row r="16" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" ht="20.1" customHeight="1" spans="1:5">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
     </row>
-    <row r="17" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" ht="20.1" customHeight="1" spans="1:5">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
     </row>
-    <row r="18" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" ht="20.1" customHeight="1" spans="1:5">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
     </row>
-    <row r="19" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" ht="20.1" customHeight="1" spans="1:5">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
     </row>
-    <row r="20" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" ht="20.1" customHeight="1" spans="1:5">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
     </row>
-    <row r="21" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" ht="20.1" customHeight="1" spans="1:5">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
     </row>
-    <row r="22" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" ht="20.1" customHeight="1" spans="1:5">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
     </row>
-    <row r="23" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" ht="20.1" customHeight="1" spans="1:5">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
     </row>
-    <row r="24" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" ht="20.1" customHeight="1" spans="1:5">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
     </row>
-    <row r="25" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" ht="20.1" customHeight="1" spans="1:5">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
     </row>
-    <row r="26" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" ht="20.1" customHeight="1" spans="1:5">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
     </row>
-    <row r="27" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" ht="20.1" customHeight="1" spans="1:5">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
     </row>
-    <row r="28" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" ht="20.1" customHeight="1" spans="1:5">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
     </row>
-    <row r="29" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" ht="20.1" customHeight="1" spans="1:5">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
     </row>
-    <row r="30" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" ht="20.1" customHeight="1" spans="1:5">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
     </row>
-    <row r="31" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" ht="20.1" customHeight="1" spans="1:5">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -3174,21 +3723,22 @@
       <c r="E31" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
-  <pageMargins left="0.70069444444444495" right="0.70069444444444495" top="0.75208333333333299" bottom="0.75208333333333299" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="1" ht="22.5" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3199,172 +3749,173 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" ht="20.1" customHeight="1" spans="1:3">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
     </row>
-    <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" ht="20.1" customHeight="1" spans="1:3">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
     </row>
-    <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="20.1" customHeight="1" spans="1:3">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
     </row>
-    <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" ht="20.1" customHeight="1" spans="1:3">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
     </row>
-    <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" ht="20.1" customHeight="1" spans="1:3">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
     </row>
-    <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" ht="20.1" customHeight="1" spans="1:3">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
     </row>
-    <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" ht="20.1" customHeight="1" spans="1:3">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
     </row>
-    <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" ht="20.1" customHeight="1" spans="1:3">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
     </row>
-    <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" ht="20.1" customHeight="1" spans="1:3">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
     </row>
-    <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" ht="20.1" customHeight="1" spans="1:3">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
     </row>
-    <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" ht="20.1" customHeight="1" spans="1:3">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
     </row>
-    <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" ht="20.1" customHeight="1" spans="1:3">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
     </row>
-    <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" ht="20.1" customHeight="1" spans="1:3">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
     </row>
-    <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" ht="20.1" customHeight="1" spans="1:3">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
     </row>
-    <row r="16" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" ht="20.1" customHeight="1" spans="1:3">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
     </row>
-    <row r="17" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" ht="20.1" customHeight="1" spans="1:3">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
     </row>
-    <row r="18" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" ht="20.1" customHeight="1" spans="1:3">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
     </row>
-    <row r="19" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" ht="20.1" customHeight="1" spans="1:3">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
     </row>
-    <row r="20" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" ht="20.1" customHeight="1" spans="1:3">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
     </row>
-    <row r="21" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" ht="20.1" customHeight="1" spans="1:3">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
     </row>
-    <row r="22" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" ht="20.1" customHeight="1" spans="1:3">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
     </row>
-    <row r="23" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" ht="20.1" customHeight="1" spans="1:3">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
     </row>
-    <row r="24" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" ht="20.1" customHeight="1" spans="1:3">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
     </row>
-    <row r="25" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" ht="20.1" customHeight="1" spans="1:3">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
     </row>
-    <row r="26" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" ht="20.1" customHeight="1" spans="1:3">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
     </row>
-    <row r="27" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" ht="20.1" customHeight="1" spans="1:3">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
     </row>
-    <row r="28" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" ht="20.1" customHeight="1" spans="1:3">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
     </row>
-    <row r="29" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" ht="20.1" customHeight="1" spans="1:3">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
     </row>
-    <row r="30" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" ht="20.1" customHeight="1" spans="1:3">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
     </row>
-    <row r="31" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" ht="20.1" customHeight="1" spans="1:3">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
-  <pageMargins left="0.75208333333333299" right="0.75208333333333299" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="1" ht="22.5" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3375,99 +3926,98 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" ht="20.1" customHeight="1" spans="1:3">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="3"/>
     </row>
-    <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" ht="20.1" customHeight="1" spans="1:3">
       <c r="A3" s="8"/>
       <c r="B3" s="7"/>
       <c r="C3" s="3"/>
     </row>
-    <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="20.1" customHeight="1" spans="1:3">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="3"/>
     </row>
-    <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" ht="20.1" customHeight="1" spans="1:3">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" ht="20.1" customHeight="1" spans="1:3">
       <c r="A6" s="8"/>
       <c r="B6" s="7"/>
       <c r="C6" s="3"/>
     </row>
-    <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" ht="20.1" customHeight="1" spans="1:3">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" ht="20.1" customHeight="1" spans="1:3">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" ht="20.1" customHeight="1" spans="1:3">
       <c r="A9" s="8"/>
       <c r="B9" s="7"/>
       <c r="C9" s="3"/>
     </row>
-    <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" ht="20.1" customHeight="1" spans="1:3">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" ht="20.1" customHeight="1" spans="1:3">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="3"/>
     </row>
-    <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" ht="20.1" customHeight="1" spans="1:3">
       <c r="A12" s="8"/>
       <c r="B12" s="7"/>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" ht="20.1" customHeight="1" spans="1:3">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" ht="20.1" customHeight="1" spans="1:3">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="3"/>
     </row>
-    <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" ht="20.1" customHeight="1" spans="1:3">
       <c r="A15" s="8"/>
       <c r="B15" s="7"/>
       <c r="C15" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
-  <pageMargins left="0.75208333333333299" right="0.75208333333333299" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:I97"/>
-  <sheetFormatPr defaultColWidth="19.75" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I93"/>
+  <sheetFormatPr defaultColWidth="19.75" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="19.75" style="1"/>
-    <col min="2" max="2" width="40" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="19.75" style="1"/>
-    <col min="5" max="5" width="12.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="118" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.25" customWidth="1"/>
+    <col min="3" max="6" width="19.75" style="1"/>
+    <col min="7" max="7" width="118.25" customWidth="1"/>
     <col min="8" max="8" width="17.625" customWidth="1"/>
-    <col min="9" max="9" width="40" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="40.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="1" ht="22.5" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3496,7 +4046,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -3519,7 +4069,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9">
       <c r="A3" s="3">
         <v>11</v>
       </c>
@@ -3542,7 +4092,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9">
       <c r="A4" s="3">
         <v>1101</v>
       </c>
@@ -3567,7 +4117,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9">
       <c r="A5" s="3">
         <v>1102</v>
       </c>
@@ -3592,7 +4142,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9">
       <c r="A6" s="3">
         <v>1103</v>
       </c>
@@ -3617,7 +4167,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9">
       <c r="A7" s="3">
         <v>12</v>
       </c>
@@ -3640,7 +4190,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9">
       <c r="A8" s="3">
         <v>1201</v>
       </c>
@@ -3665,7 +4215,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9">
       <c r="A9" s="3">
         <v>1202</v>
       </c>
@@ -3690,7 +4240,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9">
       <c r="A10" s="3">
         <v>1203</v>
       </c>
@@ -3715,7 +4265,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9">
       <c r="A11" s="3">
         <v>1204</v>
       </c>
@@ -3740,7 +4290,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9">
       <c r="A12" s="3">
         <v>13</v>
       </c>
@@ -3763,7 +4313,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9">
       <c r="A13" s="3">
         <v>1301</v>
       </c>
@@ -3788,7 +4338,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9">
       <c r="A14" s="3">
         <v>1302</v>
       </c>
@@ -3813,7 +4363,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9">
       <c r="A15" s="3">
         <v>1303</v>
       </c>
@@ -3838,7 +4388,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9">
       <c r="A16" s="3">
         <v>1304</v>
       </c>
@@ -3863,7 +4413,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9">
       <c r="A17" s="3">
         <v>1305</v>
       </c>
@@ -3888,7 +4438,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9">
       <c r="A18" s="3">
         <v>1306</v>
       </c>
@@ -3913,7 +4463,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9">
       <c r="A19" s="3">
         <v>14</v>
       </c>
@@ -3936,7 +4486,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9">
       <c r="A20" s="3">
         <v>1401</v>
       </c>
@@ -3961,7 +4511,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9">
       <c r="A21" s="3">
         <v>1402</v>
       </c>
@@ -3986,7 +4536,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9">
       <c r="A22" s="3">
         <v>1403</v>
       </c>
@@ -4011,7 +4561,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9">
       <c r="A23" s="3">
         <v>15</v>
       </c>
@@ -4034,7 +4584,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9">
       <c r="A24" s="3">
         <v>1501</v>
       </c>
@@ -4059,7 +4609,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9">
       <c r="A25" s="3">
         <v>1502</v>
       </c>
@@ -4084,7 +4634,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9">
       <c r="A26" s="3">
         <v>1503</v>
       </c>
@@ -4109,7 +4659,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9">
       <c r="A27" s="3">
         <v>1504</v>
       </c>
@@ -4134,7 +4684,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9">
       <c r="A28" s="3">
         <v>16</v>
       </c>
@@ -4157,7 +4707,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9">
       <c r="A29" s="3">
         <v>1601</v>
       </c>
@@ -4182,7 +4732,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9">
       <c r="A30" s="3">
         <v>1602</v>
       </c>
@@ -4207,7 +4757,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9">
       <c r="A31" s="3">
         <v>1603</v>
       </c>
@@ -4232,7 +4782,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9">
       <c r="A32" s="3">
         <v>1604</v>
       </c>
@@ -4257,7 +4807,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9">
       <c r="A33" s="3">
         <v>17</v>
       </c>
@@ -4280,7 +4830,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9">
       <c r="A34" s="3">
         <v>1701</v>
       </c>
@@ -4305,7 +4855,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9">
       <c r="A35" s="3">
         <v>1702</v>
       </c>
@@ -4330,7 +4880,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9">
       <c r="A36" s="3">
         <v>1703</v>
       </c>
@@ -4355,7 +4905,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9">
       <c r="A37" s="3">
         <v>1704</v>
       </c>
@@ -4380,7 +4930,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9">
       <c r="A38" s="3">
         <v>1705</v>
       </c>
@@ -4405,7 +4955,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9">
       <c r="A39" s="3">
         <v>1706</v>
       </c>
@@ -4430,7 +4980,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9">
       <c r="A40" s="3">
         <v>1707</v>
       </c>
@@ -4455,7 +5005,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9">
       <c r="A41" s="3">
         <v>1708</v>
       </c>
@@ -4480,7 +5030,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9">
       <c r="A42" s="3">
         <v>1709</v>
       </c>
@@ -4505,7 +5055,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9">
       <c r="A43" s="3">
         <v>18</v>
       </c>
@@ -4528,7 +5078,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9">
       <c r="A44" s="3">
         <v>1801</v>
       </c>
@@ -4553,7 +5103,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9">
       <c r="A45" s="3">
         <v>1802</v>
       </c>
@@ -4578,7 +5128,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9">
       <c r="A46" s="3">
         <v>1803</v>
       </c>
@@ -4603,7 +5153,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9">
       <c r="A47" s="3">
         <v>1804</v>
       </c>
@@ -4628,7 +5178,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9">
       <c r="A48" s="3">
         <v>1805</v>
       </c>
@@ -4653,7 +5203,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9">
       <c r="A49" s="3">
         <v>1806</v>
       </c>
@@ -4678,7 +5228,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9">
       <c r="A50" s="3">
         <v>19</v>
       </c>
@@ -4701,7 +5251,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9">
       <c r="A51" s="3">
         <v>1901</v>
       </c>
@@ -4726,264 +5276,262 @@
         <v>125</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9">
       <c r="A52" s="3">
-        <v>1902</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>201</v>
+        <v>2</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>127</v>
       </c>
       <c r="C52" s="3">
-        <v>19</v>
+        <v>-1</v>
       </c>
       <c r="D52" s="3">
-        <v>1902</v>
+        <v>2</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>202</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G52" s="4"/>
       <c r="H52" s="4"/>
-      <c r="I52" s="6" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I52" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53" s="3">
-        <v>1903</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>203</v>
+        <v>21</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>128</v>
       </c>
       <c r="C53" s="3">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D53" s="3">
-        <v>1903</v>
+        <v>21</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G53" s="6" t="s">
-        <v>204</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G53" s="4"/>
       <c r="H53" s="4"/>
-      <c r="I53" s="6" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I53" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54" s="3">
-        <v>1904</v>
-      </c>
-      <c r="B54" s="11" t="s">
-        <v>205</v>
+        <v>2110</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>129</v>
       </c>
       <c r="C54" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D54" s="3">
-        <v>1904</v>
+        <v>2110</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G54" s="11" t="s">
-        <v>207</v>
+      <c r="G54" s="4" t="s">
+        <v>130</v>
       </c>
       <c r="H54" s="4"/>
-      <c r="I54" s="11" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I54" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" s="3">
-        <v>1905</v>
-      </c>
-      <c r="B55" s="11" t="s">
-        <v>206</v>
+        <v>2111</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>131</v>
       </c>
       <c r="C55" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D55" s="3">
-        <v>1905</v>
+        <v>2111</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G55" s="11" t="s">
-        <v>208</v>
+      <c r="G55" s="4" t="s">
+        <v>132</v>
       </c>
       <c r="H55" s="4"/>
-      <c r="I55" s="11" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I55" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56" s="3">
-        <v>2</v>
+        <v>2112</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C56" s="3">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="D56" s="3">
-        <v>2</v>
+        <v>2112</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G56" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>134</v>
+      </c>
       <c r="H56" s="4"/>
       <c r="I56" s="4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
       <c r="A57" s="3">
+        <v>2113</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C57" s="3">
         <v>21</v>
       </c>
-      <c r="B57" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C57" s="3">
-        <v>2</v>
-      </c>
       <c r="D57" s="3">
-        <v>21</v>
+        <v>2113</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G57" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>134</v>
+      </c>
       <c r="H57" s="4"/>
       <c r="I57" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
       <c r="A58" s="3">
-        <v>2110</v>
+        <v>22</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C58" s="3">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D58" s="3">
-        <v>2110</v>
+        <v>22</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>130</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
       <c r="A59" s="3">
-        <v>2111</v>
+        <v>2201</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C59" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D59" s="3">
-        <v>2111</v>
+        <v>2201</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="H59" s="4"/>
       <c r="I59" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
       <c r="A60" s="3">
-        <v>2112</v>
+        <v>2202</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C60" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D60" s="3">
-        <v>2112</v>
+        <v>2202</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H60" s="4"/>
       <c r="I60" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
       <c r="A61" s="3">
-        <v>2113</v>
+        <v>2203</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C61" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D61" s="3">
-        <v>2113</v>
+        <v>2203</v>
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="H61" s="4"/>
       <c r="I61" s="4" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
       <c r="A62" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C62" s="3">
         <v>2</v>
       </c>
       <c r="D62" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3" t="s">
@@ -4992,869 +5540,771 @@
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
       <c r="I62" s="4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
       <c r="A63" s="3">
-        <v>2201</v>
+        <v>2301</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="C63" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D63" s="3">
-        <v>2201</v>
+        <v>2301</v>
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="H63" s="4"/>
       <c r="I63" s="4" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
       <c r="A64" s="3">
-        <v>2202</v>
+        <v>2302</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="C64" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D64" s="3">
-        <v>2202</v>
+        <v>2302</v>
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>140</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G64" s="4"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
       <c r="A65" s="3">
-        <v>2203</v>
+        <v>23021</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C65" s="3">
-        <v>22</v>
+        <v>2302</v>
       </c>
       <c r="D65" s="3">
-        <v>2203</v>
+        <v>23021</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="H65" s="4"/>
       <c r="I65" s="4" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
       <c r="A66" s="3">
-        <v>23</v>
+        <v>23022</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C66" s="3">
-        <v>2</v>
+        <v>2302</v>
       </c>
       <c r="D66" s="3">
-        <v>23</v>
+        <v>23022</v>
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G66" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>149</v>
+      </c>
       <c r="H66" s="4"/>
       <c r="I66" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
       <c r="A67" s="3">
-        <v>2301</v>
+        <v>2303</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C67" s="3">
         <v>23</v>
       </c>
       <c r="D67" s="3">
-        <v>2301</v>
+        <v>2303</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G67" s="4" t="s">
-        <v>145</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G67" s="4"/>
       <c r="H67" s="4"/>
       <c r="I67" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
       <c r="A68" s="3">
-        <v>2302</v>
+        <v>23031</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C68" s="3">
-        <v>23</v>
+        <v>2303</v>
       </c>
       <c r="D68" s="3">
-        <v>2302</v>
+        <v>23031</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G68" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>151</v>
+      </c>
       <c r="H68" s="4"/>
       <c r="I68" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
       <c r="A69" s="3">
-        <v>23021</v>
+        <v>2304</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>146</v>
+        <v>74</v>
       </c>
       <c r="C69" s="3">
-        <v>2302</v>
+        <v>23</v>
       </c>
       <c r="D69" s="3">
-        <v>23021</v>
+        <v>2304</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G69" s="4" t="s">
-        <v>147</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G69" s="4"/>
       <c r="H69" s="4"/>
       <c r="I69" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
       <c r="A70" s="3">
-        <v>23022</v>
+        <v>23041</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C70" s="3">
-        <v>2302</v>
+        <v>2304</v>
       </c>
       <c r="D70" s="3">
-        <v>23022</v>
+        <v>23041</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H70" s="4"/>
       <c r="I70" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
       <c r="A71" s="3">
-        <v>2303</v>
+        <v>23042</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C71" s="3">
-        <v>23</v>
+        <v>2304</v>
       </c>
       <c r="D71" s="3">
-        <v>2303</v>
+        <v>23042</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G71" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>155</v>
+      </c>
       <c r="H71" s="4"/>
       <c r="I71" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
       <c r="A72" s="3">
-        <v>23031</v>
+        <v>23043</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>65</v>
+        <v>156</v>
       </c>
       <c r="C72" s="3">
-        <v>2303</v>
+        <v>2304</v>
       </c>
       <c r="D72" s="3">
-        <v>23031</v>
+        <v>23043</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="H72" s="4"/>
       <c r="I72" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
       <c r="A73" s="3">
+        <v>23044</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C73" s="3">
         <v>2304</v>
       </c>
-      <c r="B73" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C73" s="3">
-        <v>23</v>
-      </c>
       <c r="D73" s="3">
-        <v>2304</v>
+        <v>23044</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G73" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>159</v>
+      </c>
       <c r="H73" s="4"/>
       <c r="I73" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
       <c r="A74" s="3">
-        <v>23041</v>
+        <v>23045</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="C74" s="3">
         <v>2304</v>
       </c>
       <c r="D74" s="3">
-        <v>23041</v>
+        <v>23045</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H74" s="4"/>
       <c r="I74" s="4" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
       <c r="A75" s="3">
-        <v>23042</v>
+        <v>23046</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C75" s="3">
         <v>2304</v>
       </c>
       <c r="D75" s="3">
-        <v>23042</v>
+        <v>23046</v>
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="H75" s="4"/>
       <c r="I75" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
       <c r="A76" s="3">
-        <v>23043</v>
-      </c>
-      <c r="B76" s="11" t="s">
-        <v>193</v>
+        <v>23047</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>164</v>
       </c>
       <c r="C76" s="3">
         <v>2304</v>
       </c>
       <c r="D76" s="3">
-        <v>23043</v>
+        <v>23047</v>
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G76" s="11" t="s">
-        <v>194</v>
+      <c r="G76" s="4" t="s">
+        <v>165</v>
       </c>
       <c r="H76" s="4"/>
-      <c r="I76" s="11" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I76" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
       <c r="A77" s="3">
-        <v>23044</v>
-      </c>
-      <c r="B77" s="11" t="s">
-        <v>195</v>
+        <v>2305</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>111</v>
       </c>
       <c r="C77" s="3">
-        <v>2304</v>
+        <v>23</v>
       </c>
       <c r="D77" s="3">
-        <v>23044</v>
+        <v>2305</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G77" s="11" t="s">
-        <v>196</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G77" s="4"/>
       <c r="H77" s="4"/>
-      <c r="I77" s="11" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I77" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
       <c r="A78" s="3">
-        <v>23045</v>
-      </c>
-      <c r="B78" s="11" t="s">
-        <v>197</v>
+        <v>23051</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>166</v>
       </c>
       <c r="C78" s="3">
-        <v>2304</v>
+        <v>2305</v>
       </c>
       <c r="D78" s="3">
-        <v>23045</v>
+        <v>23051</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G78" s="11" t="s">
-        <v>198</v>
+      <c r="G78" s="4" t="s">
+        <v>167</v>
       </c>
       <c r="H78" s="4"/>
-      <c r="I78" s="11" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I78" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
       <c r="A79" s="3">
-        <v>23046</v>
-      </c>
-      <c r="B79" s="11" t="s">
-        <v>199</v>
+        <v>23052</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>168</v>
       </c>
       <c r="C79" s="3">
-        <v>2304</v>
+        <v>2305</v>
       </c>
       <c r="D79" s="3">
-        <v>23046</v>
+        <v>23052</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G79" s="11" t="s">
-        <v>200</v>
+      <c r="G79" s="4" t="s">
+        <v>169</v>
       </c>
       <c r="H79" s="4"/>
-      <c r="I79" s="11" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I79" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
       <c r="A80" s="3">
-        <v>23047</v>
+        <v>23053</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="C80" s="3">
-        <v>2304</v>
+        <v>2305</v>
       </c>
       <c r="D80" s="3">
-        <v>23047</v>
+        <v>23053</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="H80" s="4"/>
       <c r="I80" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
       <c r="A81" s="3">
+        <v>23054</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C81" s="3">
         <v>2305</v>
       </c>
-      <c r="B81" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="C81" s="3">
-        <v>23</v>
-      </c>
       <c r="D81" s="3">
-        <v>2305</v>
+        <v>23054</v>
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G81" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>173</v>
+      </c>
       <c r="H81" s="4"/>
       <c r="I81" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
       <c r="A82" s="3">
-        <v>23051</v>
+        <v>23055</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="C82" s="3">
         <v>2305</v>
       </c>
       <c r="D82" s="3">
-        <v>23051</v>
+        <v>23055</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="H82" s="4"/>
       <c r="I82" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
       <c r="A83" s="3">
-        <v>23052</v>
+        <v>23056</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="C83" s="3">
         <v>2305</v>
       </c>
       <c r="D83" s="3">
-        <v>23052</v>
+        <v>23056</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="H83" s="4"/>
       <c r="I83" s="4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
       <c r="A84" s="3">
-        <v>23053</v>
+        <v>2306</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>162</v>
+        <v>92</v>
       </c>
       <c r="C84" s="3">
-        <v>2305</v>
+        <v>23</v>
       </c>
       <c r="D84" s="3">
-        <v>23053</v>
+        <v>2306</v>
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G84" s="4" t="s">
-        <v>163</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G84" s="4"/>
       <c r="H84" s="4"/>
       <c r="I84" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
       <c r="A85" s="3">
-        <v>23054</v>
+        <v>23061</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="C85" s="3">
-        <v>2305</v>
+        <v>2306</v>
       </c>
       <c r="D85" s="3">
-        <v>23054</v>
+        <v>23061</v>
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="H85" s="4"/>
       <c r="I85" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
       <c r="A86" s="3">
-        <v>23055</v>
+        <v>24</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="C86" s="3">
-        <v>2305</v>
+        <v>2</v>
       </c>
       <c r="D86" s="3">
-        <v>23055</v>
-      </c>
-      <c r="E86" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="E86" s="4"/>
       <c r="F86" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G86" s="4" t="s">
-        <v>167</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G86" s="4"/>
       <c r="H86" s="4"/>
       <c r="I86" s="4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
       <c r="A87" s="3">
-        <v>23056</v>
+        <v>2401</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="C87" s="3">
-        <v>2305</v>
+        <v>24</v>
       </c>
       <c r="D87" s="3">
-        <v>23056</v>
-      </c>
-      <c r="E87" s="3"/>
+        <v>2401</v>
+      </c>
+      <c r="E87" s="4"/>
       <c r="F87" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="H87" s="4"/>
       <c r="I87" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
       <c r="A88" s="3">
-        <v>2306</v>
+        <v>25</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>92</v>
+        <v>183</v>
       </c>
       <c r="C88" s="3">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="D88" s="3">
-        <v>2306</v>
-      </c>
-      <c r="E88" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="E88" s="4"/>
       <c r="F88" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G88" s="4"/>
       <c r="H88" s="4"/>
       <c r="I88" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
       <c r="A89" s="3">
-        <v>23061</v>
+        <v>2501</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="C89" s="3">
-        <v>2306</v>
+        <v>25</v>
       </c>
       <c r="D89" s="3">
-        <v>23061</v>
+        <v>2501</v>
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="H89" s="4"/>
+        <v>184</v>
+      </c>
+      <c r="H89" s="3"/>
       <c r="I89" s="4" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
       <c r="A90" s="3">
-        <v>24</v>
+        <v>2502</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="C90" s="3">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D90" s="3">
-        <v>24</v>
-      </c>
-      <c r="E90" s="4"/>
+        <v>2502</v>
+      </c>
+      <c r="E90" s="3"/>
       <c r="F90" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G90" s="4"/>
-      <c r="H90" s="4"/>
-      <c r="I90" s="4" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="H90" s="5"/>
+      <c r="I90" s="5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
       <c r="A91" s="3">
-        <v>2401</v>
+        <v>2503</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="C91" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D91" s="3">
-        <v>2401</v>
-      </c>
-      <c r="E91" s="4"/>
+        <v>2503</v>
+      </c>
+      <c r="E91" s="3"/>
       <c r="F91" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="H91" s="4"/>
       <c r="I91" s="4" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
       <c r="A92" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="C92" s="3">
         <v>2</v>
       </c>
       <c r="D92" s="3">
-        <v>25</v>
-      </c>
-      <c r="E92" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="E92" s="3"/>
       <c r="F92" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G92" s="4"/>
       <c r="H92" s="4"/>
       <c r="I92" s="4" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
       <c r="A93" s="3">
-        <v>2501</v>
+        <v>2601</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="C93" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D93" s="3">
-        <v>2501</v>
-      </c>
-      <c r="E93" s="3"/>
+        <v>2601</v>
+      </c>
+      <c r="E93" s="4"/>
       <c r="F93" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="H93" s="3"/>
+        <v>191</v>
+      </c>
+      <c r="H93" s="4"/>
       <c r="I93" s="4" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A94" s="3">
-        <v>2502</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="C94" s="3">
-        <v>25</v>
-      </c>
-      <c r="D94" s="3">
-        <v>2502</v>
-      </c>
-      <c r="E94" s="3"/>
-      <c r="F94" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G94" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="H94" s="5"/>
-      <c r="I94" s="5" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A95" s="3">
-        <v>2503</v>
-      </c>
-      <c r="B95" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="C95" s="3">
-        <v>25</v>
-      </c>
-      <c r="D95" s="3">
-        <v>2503</v>
-      </c>
-      <c r="E95" s="3"/>
-      <c r="F95" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G95" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="H95" s="4"/>
-      <c r="I95" s="4" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A96" s="3">
-        <v>26</v>
-      </c>
-      <c r="B96" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="C96" s="3">
-        <v>2</v>
-      </c>
-      <c r="D96" s="3">
-        <v>26</v>
-      </c>
-      <c r="E96" s="3"/>
-      <c r="F96" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G96" s="4"/>
-      <c r="H96" s="4"/>
-      <c r="I96" s="4" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A97" s="3">
-        <v>2601</v>
-      </c>
-      <c r="B97" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="C97" s="3">
-        <v>26</v>
-      </c>
-      <c r="D97" s="3">
-        <v>2601</v>
-      </c>
-      <c r="E97" s="4"/>
-      <c r="F97" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G97" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="H97" s="4"/>
-      <c r="I97" s="4" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
-  <pageMargins left="0.70069444444444495" right="0.70069444444444495" top="0.75208333333333299" bottom="0.75208333333333299" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" tabRatio="500" firstSheet="3" activeTab="8"/>
+    <workbookView windowHeight="17680" tabRatio="500" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="SysUser" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="209">
   <si>
     <t>Id</t>
   </si>
@@ -417,6 +417,30 @@
   </si>
   <si>
     <t>CugaCalibration.ViewModels.Fourier.FourierPupilCameraAlignmentViewModel</t>
+  </si>
+  <si>
+    <t>Side Channel Flexible Aperture</t>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Fourier.FourierSideChannelFlexibleApertureViewModel</t>
+  </si>
+  <si>
+    <t>Side Channel Specular Blocker</t>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Fourier.FourierSideChannelSpecularBlockerViewModel</t>
+  </si>
+  <si>
+    <t>Center Channel Flexible Aperture V1</t>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Fourier.V0FourierCenterChannelFlexibleApertureViewModel</t>
+  </si>
+  <si>
+    <t>Center Channel Specular Blocker V1</t>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Fourier.V0FourierCenterChannelSpecularBlockerViewModel</t>
   </si>
   <si>
     <t>Title</t>
@@ -558,28 +582,28 @@
     <t>CugaCalibration.ViewModels.Common.Windows.Tools.AODWaveform.ChirpGenerateAODWaveformWindowViewModel</t>
   </si>
   <si>
-    <t>Prescan AOD Waveform Electrode Offset V1</t>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Common.Windows.Tools.AODWaveform.V0PrescanAODWaveformElectrodeOffsetWindowViewModel</t>
-  </si>
-  <si>
-    <t>Chirp AOD Waveform Electrode Offset V1</t>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Common.Windows.Tools.AODWaveform.V0ChirpAODWaveformElectrodeOffsetWindowViewModel</t>
-  </si>
-  <si>
-    <t>Prescan AOD Waveform Electrode Offset V2</t>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Common.Windows.Tools.AODWaveform.PrescanAODWaveformElectrodeOffsetWindowViewModel</t>
-  </si>
-  <si>
-    <t>Chirp AOD Waveform Electrode Offset V2</t>
-  </si>
-  <si>
-    <t>CugaCalibration.ViewModels.Common.Windows.Tools.AODWaveform.ChirpAODWaveformElectrodeOffsetWindowViewModel</t>
+    <t>Prescan AOD Waveform Electrode Delay V1</t>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Common.Windows.Tools.AODWaveform.V0PrescanAODWaveformElectrodeDelayWindowViewModel</t>
+  </si>
+  <si>
+    <t>Chirp AOD Waveform Electrode Delay V1</t>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Common.Windows.Tools.AODWaveform.V0ChirpAODWaveformElectrodeDelayWindowViewModel</t>
+  </si>
+  <si>
+    <t>Prescan AOD Waveform Electrode Delay V2</t>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Common.Windows.Tools.AODWaveform.PrescanAODWaveformElectrodeDelayWindowViewModel</t>
+  </si>
+  <si>
+    <t>Chirp AOD Waveform Electrode Delay V2</t>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Common.Windows.Tools.AODWaveform.ChirpAODWaveformElectrodeDelayWindowViewModel</t>
   </si>
   <si>
     <t>Chirp AOD Waveform Training</t>
@@ -609,7 +633,7 @@
     <t>Collection Y Ghost</t>
   </si>
   <si>
-    <t>CugaCalibration.ViewModels.Common.Windows.Tools.Collection.CollectionYGhostWindowViewModel</t>
+    <t>CugaCalibration.ViewModels.Common.Windows.Tools.Optics.OpticsYGhostWindowViewModel</t>
   </si>
   <si>
     <t>Collector Slit</t>
@@ -703,7 +727,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -714,6 +738,12 @@
       <b/>
       <sz val="18"/>
       <color rgb="FF44546A"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -1229,31 +1259,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1262,122 +1289,125 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1399,16 +1429,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="6" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1901,489 +1934,492 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A2" s="7">
+      <c r="A2" s="8">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="8">
         <v>1</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="9" t="s">
+      <c r="E2" s="8"/>
+      <c r="F2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="8">
         <v>666666</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A3" s="8">
+      <c r="A3" s="9">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="9">
         <v>1</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="7">
+      <c r="E3" s="9"/>
+      <c r="F3" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="8">
         <v>666666</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
+      <c r="A5" s="9"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
+      <c r="A30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
     </row>
     <row r="32" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
+      <c r="A32" s="11"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
     </row>
     <row r="33" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
+      <c r="A33" s="11"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
     </row>
     <row r="34" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
+      <c r="A34" s="11"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
     </row>
     <row r="35" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="10"/>
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
     </row>
     <row r="36" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A36" s="10"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
+      <c r="A36" s="11"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
     </row>
     <row r="37" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A37" s="10"/>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
+      <c r="A37" s="11"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
     </row>
     <row r="38" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A38" s="10"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
+      <c r="A38" s="11"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
     </row>
     <row r="39" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A39" s="10"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="10"/>
+      <c r="A39" s="11"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
     </row>
     <row r="40" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A40" s="10"/>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
+      <c r="A40" s="11"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
     </row>
     <row r="41" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A41" s="10"/>
-      <c r="B41" s="10"/>
-      <c r="C41" s="10"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
+      <c r="A41" s="11"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
     </row>
     <row r="42" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A42" s="10"/>
-      <c r="B42" s="10"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="10"/>
+      <c r="A42" s="11"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" display="xuankaizhi@semixchina.com"/>
+    <hyperlink ref="F3" r:id="rId1" display="xuankaizhi@semixchina.com"/>
   </hyperlinks>
   <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2440,7 +2476,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="C2" s="3">
         <v>-1</v>
@@ -2455,7 +2491,7 @@
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:9">
@@ -2463,7 +2499,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C3" s="3">
         <v>1</v>
@@ -2478,7 +2514,7 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:9">
@@ -2486,7 +2522,7 @@
         <v>1101</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="C4" s="3">
         <v>11</v>
@@ -2499,11 +2535,11 @@
         <v>39</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:9">
@@ -2511,7 +2547,7 @@
         <v>1102</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="C5" s="3">
         <v>11</v>
@@ -2524,11 +2560,11 @@
         <v>39</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:9">
@@ -2536,7 +2572,7 @@
         <v>1103</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="C6" s="3">
         <v>11</v>
@@ -2549,11 +2585,11 @@
         <v>39</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:9">
@@ -2561,7 +2597,7 @@
         <v>1104</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="C7" s="3">
         <v>11</v>
@@ -2574,11 +2610,11 @@
         <v>39</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -2608,150 +2644,156 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="7">
+      <c r="A2" s="8">
         <v>1</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="8">
         <v>1</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
+      <c r="A3" s="8">
+        <v>1</v>
+      </c>
+      <c r="B3" s="8">
+        <v>2</v>
+      </c>
+      <c r="C3" s="8">
+        <v>2</v>
+      </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
+      <c r="A5" s="9"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2781,156 +2823,156 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="7">
+      <c r="A2" s="8">
         <v>1</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="8">
         <v>1</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="8">
+      <c r="A3" s="9">
         <v>2</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="9">
         <v>2</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
+      <c r="A5" s="9"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2969,200 +3011,200 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A2" s="7">
+      <c r="A2" s="8">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="8">
         <v>-1</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="8">
         <v>0</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="8">
         <v>1</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
+      <c r="A5" s="9"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3198,244 +3240,244 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A2" s="7">
+      <c r="A2" s="8">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="8">
         <v>0</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="8" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A3" s="7">
+      <c r="A3" s="8">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="8">
         <v>1</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A4" s="7">
+      <c r="A4" s="8">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="9">
         <v>2</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
+      <c r="A5" s="9"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3450,9 +3492,11 @@
   <dimension ref="A1:E31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="2" width="20.625" customWidth="1"/>
+    <col min="1" max="1" width="20.625" customWidth="1"/>
+    <col min="2" max="2" width="22.375" customWidth="1"/>
     <col min="3" max="3" width="24.25" customWidth="1"/>
-    <col min="4" max="5" width="20.625" customWidth="1"/>
+    <col min="4" max="4" width="20.625" customWidth="1"/>
+    <col min="5" max="5" width="23.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22.5" spans="1:5">
@@ -3473,254 +3517,254 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A2" s="7">
+      <c r="A2" s="8">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="8">
         <v>0</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="8" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A3" s="7">
+      <c r="A3" s="8">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="8">
         <v>1</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A4" s="7">
+      <c r="A4" s="8">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="8">
         <v>2</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A5" s="8">
+      <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="9">
         <v>3</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="9" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3750,154 +3794,154 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
+      <c r="A5" s="9"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3927,73 +3971,73 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
       <c r="C2" s="3"/>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="7"/>
+      <c r="A3" s="9"/>
+      <c r="B3" s="8"/>
       <c r="C3" s="3"/>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
       <c r="C4" s="3"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="7"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="8"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="7"/>
+      <c r="A9" s="9"/>
+      <c r="B9" s="8"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
       <c r="C11" s="3"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="7"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="8"/>
       <c r="C12" s="3"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
       <c r="C13" s="3"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
       <c r="C14" s="3"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="7"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="8"/>
       <c r="C15" s="3"/>
     </row>
   </sheetData>
@@ -4006,15 +4050,17 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:I97"/>
   <sheetFormatPr defaultColWidth="19.75" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="19.75" style="1"/>
-    <col min="2" max="2" width="40.25" customWidth="1"/>
-    <col min="3" max="6" width="19.75" style="1"/>
-    <col min="7" max="7" width="118.25" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="4" width="19.75" style="1"/>
+    <col min="5" max="5" width="12.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="118" customWidth="1"/>
     <col min="8" max="8" width="17.625" customWidth="1"/>
-    <col min="9" max="9" width="40.25" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22.5" spans="1:9">
@@ -5278,235 +5324,237 @@
     </row>
     <row r="52" spans="1:9">
       <c r="A52" s="3">
-        <v>2</v>
-      </c>
-      <c r="B52" s="4" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B52" s="6" t="s">
         <v>127</v>
       </c>
       <c r="C52" s="3">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="D52" s="3">
-        <v>2</v>
+        <v>1902</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G52" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>128</v>
+      </c>
       <c r="H52" s="4"/>
-      <c r="I52" s="4" t="s">
+      <c r="I52" s="6" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" s="3">
-        <v>21</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>128</v>
+        <v>1903</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>129</v>
       </c>
       <c r="C53" s="3">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D53" s="3">
-        <v>21</v>
+        <v>1903</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G53" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>130</v>
+      </c>
       <c r="H53" s="4"/>
-      <c r="I53" s="4" t="s">
-        <v>128</v>
+      <c r="I53" s="6" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" s="3">
-        <v>2110</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>129</v>
+        <v>1904</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>131</v>
       </c>
       <c r="C54" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D54" s="3">
-        <v>2110</v>
+        <v>1904</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G54" s="4" t="s">
-        <v>130</v>
+      <c r="G54" s="7" t="s">
+        <v>132</v>
       </c>
       <c r="H54" s="4"/>
-      <c r="I54" s="4" t="s">
-        <v>129</v>
+      <c r="I54" s="7" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" s="3">
-        <v>2111</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>131</v>
+        <v>1905</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>133</v>
       </c>
       <c r="C55" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D55" s="3">
-        <v>2111</v>
+        <v>1905</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G55" s="4" t="s">
-        <v>132</v>
+      <c r="G55" s="7" t="s">
+        <v>134</v>
       </c>
       <c r="H55" s="4"/>
-      <c r="I55" s="4" t="s">
-        <v>131</v>
+      <c r="I55" s="7" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" s="3">
-        <v>2112</v>
+        <v>2</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C56" s="3">
-        <v>21</v>
+        <v>-1</v>
       </c>
       <c r="D56" s="3">
-        <v>2112</v>
+        <v>2</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>134</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G56" s="4"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="3">
-        <v>2113</v>
+        <v>21</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C57" s="3">
+        <v>2</v>
+      </c>
+      <c r="D57" s="3">
         <v>21</v>
-      </c>
-      <c r="D57" s="3">
-        <v>2113</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>134</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G57" s="4"/>
       <c r="H57" s="4"/>
       <c r="I57" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" s="3">
-        <v>22</v>
+        <v>2110</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C58" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D58" s="3">
-        <v>22</v>
+        <v>2110</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G58" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>138</v>
+      </c>
       <c r="H58" s="4"/>
       <c r="I58" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="59" spans="1:9">
       <c r="A59" s="3">
-        <v>2201</v>
+        <v>2111</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C59" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D59" s="3">
-        <v>2201</v>
+        <v>2111</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H59" s="4"/>
       <c r="I59" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="60" spans="1:9">
       <c r="A60" s="3">
-        <v>2202</v>
+        <v>2112</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C60" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D60" s="3">
-        <v>2202</v>
+        <v>2112</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H60" s="4"/>
       <c r="I60" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" s="3">
-        <v>2203</v>
+        <v>2113</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C61" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D61" s="3">
-        <v>2203</v>
+        <v>2113</v>
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3" t="s">
@@ -5517,21 +5565,21 @@
       </c>
       <c r="H61" s="4"/>
       <c r="I61" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="62" spans="1:9">
       <c r="A62" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C62" s="3">
         <v>2</v>
       </c>
       <c r="D62" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3" t="s">
@@ -5540,281 +5588,279 @@
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
       <c r="I62" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="63" spans="1:9">
       <c r="A63" s="3">
-        <v>2301</v>
+        <v>2201</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C63" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D63" s="3">
-        <v>2301</v>
+        <v>2201</v>
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H63" s="4"/>
       <c r="I63" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" s="3">
-        <v>2302</v>
+        <v>2202</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>75</v>
+        <v>147</v>
       </c>
       <c r="C64" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D64" s="3">
-        <v>2302</v>
+        <v>2202</v>
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G64" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>148</v>
+      </c>
       <c r="H64" s="4"/>
       <c r="I64" s="4" t="s">
-        <v>75</v>
+        <v>147</v>
       </c>
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="3">
-        <v>23021</v>
+        <v>2203</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C65" s="3">
-        <v>2302</v>
+        <v>22</v>
       </c>
       <c r="D65" s="3">
-        <v>23021</v>
+        <v>2203</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H65" s="4"/>
       <c r="I65" s="4" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="3">
-        <v>23022</v>
+        <v>23</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C66" s="3">
-        <v>2302</v>
+        <v>2</v>
       </c>
       <c r="D66" s="3">
-        <v>23022</v>
+        <v>23</v>
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G66" s="4" t="s">
-        <v>149</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G66" s="4"/>
       <c r="H66" s="4"/>
       <c r="I66" s="4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="67" spans="1:9">
       <c r="A67" s="3">
-        <v>2303</v>
+        <v>2301</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C67" s="3">
         <v>23</v>
       </c>
       <c r="D67" s="3">
-        <v>2303</v>
+        <v>2301</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G67" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>153</v>
+      </c>
       <c r="H67" s="4"/>
       <c r="I67" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="3">
-        <v>23031</v>
+        <v>2302</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C68" s="3">
-        <v>2303</v>
+        <v>23</v>
       </c>
       <c r="D68" s="3">
-        <v>23031</v>
+        <v>2302</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>151</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G68" s="4"/>
       <c r="H68" s="4"/>
       <c r="I68" s="4" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="3">
-        <v>2304</v>
+        <v>23021</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>74</v>
+        <v>154</v>
       </c>
       <c r="C69" s="3">
-        <v>23</v>
+        <v>2302</v>
       </c>
       <c r="D69" s="3">
-        <v>2304</v>
+        <v>23021</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G69" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>155</v>
+      </c>
       <c r="H69" s="4"/>
       <c r="I69" s="4" t="s">
-        <v>74</v>
+        <v>154</v>
       </c>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="3">
-        <v>23041</v>
+        <v>23022</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C70" s="3">
-        <v>2304</v>
+        <v>2302</v>
       </c>
       <c r="D70" s="3">
-        <v>23041</v>
+        <v>23022</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="H70" s="4"/>
       <c r="I70" s="4" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="71" spans="1:9">
       <c r="A71" s="3">
-        <v>23042</v>
+        <v>2303</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C71" s="3">
-        <v>2304</v>
+        <v>23</v>
       </c>
       <c r="D71" s="3">
-        <v>23042</v>
+        <v>2303</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>155</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G71" s="4"/>
       <c r="H71" s="4"/>
       <c r="I71" s="4" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="72" spans="1:9">
       <c r="A72" s="3">
-        <v>23043</v>
+        <v>23031</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>156</v>
+        <v>65</v>
       </c>
       <c r="C72" s="3">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="D72" s="3">
-        <v>23043</v>
+        <v>23031</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H72" s="4"/>
       <c r="I72" s="4" t="s">
-        <v>156</v>
+        <v>65</v>
       </c>
     </row>
     <row r="73" spans="1:9">
       <c r="A73" s="3">
-        <v>23044</v>
+        <v>2304</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>158</v>
+        <v>74</v>
       </c>
       <c r="C73" s="3">
+        <v>23</v>
+      </c>
+      <c r="D73" s="3">
         <v>2304</v>
-      </c>
-      <c r="D73" s="3">
-        <v>23044</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>159</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G73" s="4"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4" t="s">
-        <v>158</v>
+        <v>74</v>
       </c>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" s="3">
-        <v>23045</v>
+        <v>23041</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>160</v>
@@ -5823,7 +5869,7 @@
         <v>2304</v>
       </c>
       <c r="D74" s="3">
-        <v>23045</v>
+        <v>23041</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3" t="s">
@@ -5839,7 +5885,7 @@
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="3">
-        <v>23046</v>
+        <v>23042</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>162</v>
@@ -5848,7 +5894,7 @@
         <v>2304</v>
       </c>
       <c r="D75" s="3">
-        <v>23046</v>
+        <v>23042</v>
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="3" t="s">
@@ -5864,155 +5910,155 @@
     </row>
     <row r="76" spans="1:9">
       <c r="A76" s="3">
-        <v>23047</v>
-      </c>
-      <c r="B76" s="4" t="s">
+        <v>23043</v>
+      </c>
+      <c r="B76" s="7" t="s">
         <v>164</v>
       </c>
       <c r="C76" s="3">
         <v>2304</v>
       </c>
       <c r="D76" s="3">
-        <v>23047</v>
+        <v>23043</v>
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G76" s="4" t="s">
+      <c r="G76" s="7" t="s">
         <v>165</v>
       </c>
       <c r="H76" s="4"/>
-      <c r="I76" s="4" t="s">
+      <c r="I76" s="7" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="77" spans="1:9">
       <c r="A77" s="3">
-        <v>2305</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>111</v>
+        <v>23044</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>166</v>
       </c>
       <c r="C77" s="3">
-        <v>23</v>
+        <v>2304</v>
       </c>
       <c r="D77" s="3">
-        <v>2305</v>
+        <v>23044</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G77" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G77" s="7" t="s">
+        <v>167</v>
+      </c>
       <c r="H77" s="4"/>
-      <c r="I77" s="4" t="s">
-        <v>111</v>
+      <c r="I77" s="7" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" s="3">
-        <v>23051</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>166</v>
+        <v>23045</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>168</v>
       </c>
       <c r="C78" s="3">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="D78" s="3">
-        <v>23051</v>
+        <v>23045</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G78" s="4" t="s">
-        <v>167</v>
+      <c r="G78" s="7" t="s">
+        <v>169</v>
       </c>
       <c r="H78" s="4"/>
-      <c r="I78" s="4" t="s">
-        <v>166</v>
+      <c r="I78" s="7" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="3">
-        <v>23052</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>168</v>
+        <v>23046</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>170</v>
       </c>
       <c r="C79" s="3">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="D79" s="3">
-        <v>23052</v>
+        <v>23046</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G79" s="4" t="s">
-        <v>169</v>
+      <c r="G79" s="7" t="s">
+        <v>171</v>
       </c>
       <c r="H79" s="4"/>
-      <c r="I79" s="4" t="s">
-        <v>168</v>
+      <c r="I79" s="7" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="80" spans="1:9">
       <c r="A80" s="3">
-        <v>23053</v>
+        <v>23047</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C80" s="3">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="D80" s="3">
-        <v>23053</v>
+        <v>23047</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H80" s="4"/>
       <c r="I80" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="3">
-        <v>23054</v>
+        <v>2305</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>172</v>
+        <v>111</v>
       </c>
       <c r="C81" s="3">
+        <v>23</v>
+      </c>
+      <c r="D81" s="3">
         <v>2305</v>
-      </c>
-      <c r="D81" s="3">
-        <v>23054</v>
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>173</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G81" s="4"/>
       <c r="H81" s="4"/>
       <c r="I81" s="4" t="s">
-        <v>172</v>
+        <v>111</v>
       </c>
     </row>
     <row r="82" spans="1:9">
       <c r="A82" s="3">
-        <v>23055</v>
+        <v>23051</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>174</v>
@@ -6021,7 +6067,7 @@
         <v>2305</v>
       </c>
       <c r="D82" s="3">
-        <v>23055</v>
+        <v>23051</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3" t="s">
@@ -6037,7 +6083,7 @@
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="3">
-        <v>23056</v>
+        <v>23052</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>176</v>
@@ -6046,7 +6092,7 @@
         <v>2305</v>
       </c>
       <c r="D83" s="3">
-        <v>23056</v>
+        <v>23052</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3" t="s">
@@ -6062,244 +6108,344 @@
     </row>
     <row r="84" spans="1:9">
       <c r="A84" s="3">
-        <v>2306</v>
+        <v>23053</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="C84" s="3">
-        <v>23</v>
+        <v>2305</v>
       </c>
       <c r="D84" s="3">
-        <v>2306</v>
+        <v>23053</v>
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G84" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>179</v>
+      </c>
       <c r="H84" s="4"/>
       <c r="I84" s="4" t="s">
-        <v>92</v>
+        <v>178</v>
       </c>
     </row>
     <row r="85" spans="1:9">
       <c r="A85" s="3">
-        <v>23061</v>
+        <v>23054</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C85" s="3">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="D85" s="3">
-        <v>23061</v>
+        <v>23054</v>
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H85" s="4"/>
       <c r="I85" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="86" spans="1:9">
       <c r="A86" s="3">
-        <v>24</v>
+        <v>23055</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C86" s="3">
-        <v>2</v>
+        <v>2305</v>
       </c>
       <c r="D86" s="3">
-        <v>24</v>
-      </c>
-      <c r="E86" s="4"/>
+        <v>23055</v>
+      </c>
+      <c r="E86" s="3"/>
       <c r="F86" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G86" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>183</v>
+      </c>
       <c r="H86" s="4"/>
       <c r="I86" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="87" spans="1:9">
       <c r="A87" s="3">
-        <v>2401</v>
+        <v>23056</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C87" s="3">
-        <v>24</v>
+        <v>2305</v>
       </c>
       <c r="D87" s="3">
-        <v>2401</v>
-      </c>
-      <c r="E87" s="4"/>
+        <v>23056</v>
+      </c>
+      <c r="E87" s="3"/>
       <c r="F87" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H87" s="4"/>
       <c r="I87" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="3">
-        <v>25</v>
+        <v>2306</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>183</v>
+        <v>92</v>
       </c>
       <c r="C88" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D88" s="3">
-        <v>25</v>
-      </c>
-      <c r="E88" s="4"/>
+        <v>2306</v>
+      </c>
+      <c r="E88" s="3"/>
       <c r="F88" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G88" s="4"/>
       <c r="H88" s="4"/>
       <c r="I88" s="4" t="s">
-        <v>183</v>
+        <v>92</v>
       </c>
     </row>
     <row r="89" spans="1:9">
       <c r="A89" s="3">
-        <v>2501</v>
+        <v>23061</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C89" s="3">
-        <v>25</v>
+        <v>2306</v>
       </c>
       <c r="D89" s="3">
-        <v>2501</v>
+        <v>23061</v>
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="H89" s="3"/>
+        <v>187</v>
+      </c>
+      <c r="H89" s="4"/>
       <c r="I89" s="4" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
     </row>
     <row r="90" spans="1:9">
       <c r="A90" s="3">
-        <v>2502</v>
+        <v>24</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C90" s="3">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D90" s="3">
-        <v>2502</v>
-      </c>
-      <c r="E90" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="E90" s="4"/>
       <c r="F90" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G90" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="H90" s="5"/>
-      <c r="I90" s="5" t="s">
-        <v>185</v>
+        <v>36</v>
+      </c>
+      <c r="G90" s="4"/>
+      <c r="H90" s="4"/>
+      <c r="I90" s="4" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="91" spans="1:9">
       <c r="A91" s="3">
-        <v>2503</v>
+        <v>2401</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C91" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D91" s="3">
-        <v>2503</v>
-      </c>
-      <c r="E91" s="3"/>
+        <v>2401</v>
+      </c>
+      <c r="E91" s="4"/>
       <c r="F91" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H91" s="4"/>
       <c r="I91" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C92" s="3">
         <v>2</v>
       </c>
       <c r="D92" s="3">
-        <v>26</v>
-      </c>
-      <c r="E92" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="E92" s="4"/>
       <c r="F92" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G92" s="4"/>
       <c r="H92" s="4"/>
       <c r="I92" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="93" spans="1:9">
       <c r="A93" s="3">
+        <v>2501</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C93" s="3">
+        <v>25</v>
+      </c>
+      <c r="D93" s="3">
+        <v>2501</v>
+      </c>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="H93" s="3"/>
+      <c r="I93" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
+      <c r="A94" s="3">
+        <v>2502</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C94" s="3">
+        <v>25</v>
+      </c>
+      <c r="D94" s="3">
+        <v>2502</v>
+      </c>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="H94" s="5"/>
+      <c r="I94" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
+      <c r="A95" s="3">
+        <v>2503</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C95" s="3">
+        <v>25</v>
+      </c>
+      <c r="D95" s="3">
+        <v>2503</v>
+      </c>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="H95" s="4"/>
+      <c r="I95" s="4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
+      <c r="A96" s="3">
+        <v>26</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C96" s="3">
+        <v>2</v>
+      </c>
+      <c r="D96" s="3">
+        <v>26</v>
+      </c>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G96" s="4"/>
+      <c r="H96" s="4"/>
+      <c r="I96" s="4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
+      <c r="A97" s="3">
         <v>2601</v>
       </c>
-      <c r="B93" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="C93" s="3">
+      <c r="B97" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C97" s="3">
         <v>26</v>
       </c>
-      <c r="D93" s="3">
+      <c r="D97" s="3">
         <v>2601</v>
       </c>
-      <c r="E93" s="4"/>
-      <c r="F93" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G93" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="H93" s="4"/>
-      <c r="I93" s="4" t="s">
-        <v>190</v>
+      <c r="E97" s="4"/>
+      <c r="F97" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G97" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="H97" s="4"/>
+      <c r="I97" s="4" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>

--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" tabRatio="500" activeTab="8"/>
+    <workbookView windowWidth="24225" windowHeight="12540" tabRatio="500" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="SysUser" sheetId="1" r:id="rId1"/>
@@ -18,25 +18,12 @@
     <sheet name="SysMenu" sheetId="9" r:id="rId9"/>
     <sheet name="SysManagement" sheetId="10" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="213">
   <si>
     <t>Id</t>
   </si>
@@ -441,6 +428,18 @@
   </si>
   <si>
     <t>CugaCalibration.ViewModels.Fourier.V0FourierCenterChannelSpecularBlockerViewModel</t>
+  </si>
+  <si>
+    <t>Center Channel Flexible Aperture V2</t>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Fourier.FourierCenterChannelFlexibleApertureViewModel</t>
+  </si>
+  <si>
+    <t>Center Channel Specular Blocker V2</t>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Fourier.FourierCenterChannelSpecularBlockerViewModel</t>
   </si>
   <si>
     <t>Title</t>
@@ -720,14 +719,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -738,12 +737,6 @@
       <b/>
       <sz val="18"/>
       <color rgb="FF44546A"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -761,60 +754,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -824,23 +763,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -855,7 +792,59 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -869,36 +858,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -932,7 +925,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -944,7 +973,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -956,85 +1057,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1046,7 +1075,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1058,43 +1087,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1106,7 +1099,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1148,6 +1141,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -1163,20 +1165,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1196,6 +1195,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1207,30 +1215,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1249,6 +1233,15 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thick">
         <color rgb="FFA1B8E1"/>
       </bottom>
@@ -1259,155 +1252,155 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1429,70 +1422,67 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="6" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="10" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
     <cellStyle name="Excel Built-in Heading 2" xfId="49"/>
@@ -1690,7 +1680,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -1699,7 +1689,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -1897,14 +1887,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I42"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="5" width="20.625" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="9" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:9">
+    <row r="1" ht="23.25" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1934,487 +1924,487 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A2" s="8">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="7">
         <v>1</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="10" t="s">
+      <c r="E2" s="7"/>
+      <c r="F2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="7">
         <v>666666</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="7" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A3" s="9">
+      <c r="A3" s="8">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="8">
         <v>1</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="10" t="s">
+      <c r="E3" s="8"/>
+      <c r="F3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="7">
         <v>666666</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A30" s="11"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11"/>
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A31" s="11"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
     </row>
     <row r="32" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="10"/>
     </row>
     <row r="33" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
     </row>
     <row r="34" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="11"/>
+      <c r="A34" s="10"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
     </row>
     <row r="35" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
     </row>
     <row r="36" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A36" s="11"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="11"/>
+      <c r="A36" s="10"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
     </row>
     <row r="37" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A37" s="11"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="11"/>
+      <c r="A37" s="10"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
     </row>
     <row r="38" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A38" s="11"/>
-      <c r="B38" s="11"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="11"/>
-      <c r="I38" s="11"/>
+      <c r="A38" s="10"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="10"/>
     </row>
     <row r="39" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A39" s="11"/>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="11"/>
-      <c r="I39" s="11"/>
+      <c r="A39" s="10"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="10"/>
     </row>
     <row r="40" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A40" s="11"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="11"/>
-      <c r="I40" s="11"/>
+      <c r="A40" s="10"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="10"/>
+      <c r="I40" s="10"/>
     </row>
     <row r="41" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A41" s="11"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="11"/>
+      <c r="A41" s="10"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="10"/>
     </row>
     <row r="42" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A42" s="11"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="11"/>
-      <c r="I42" s="11"/>
+      <c r="A42" s="10"/>
+      <c r="B42" s="10"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2431,7 +2421,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="20.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="45.375" customWidth="1"/>
@@ -2476,7 +2466,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C2" s="3">
         <v>-1</v>
@@ -2491,7 +2481,7 @@
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:9">
@@ -2499,7 +2489,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C3" s="3">
         <v>1</v>
@@ -2514,7 +2504,7 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:9">
@@ -2522,7 +2512,7 @@
         <v>1101</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C4" s="3">
         <v>11</v>
@@ -2535,11 +2525,11 @@
         <v>39</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:9">
@@ -2547,7 +2537,7 @@
         <v>1102</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C5" s="3">
         <v>11</v>
@@ -2560,11 +2550,11 @@
         <v>39</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:9">
@@ -2572,7 +2562,7 @@
         <v>1103</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C6" s="3">
         <v>11</v>
@@ -2585,11 +2575,11 @@
         <v>39</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:9">
@@ -2597,7 +2587,7 @@
         <v>1104</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C7" s="3">
         <v>11</v>
@@ -2610,11 +2600,11 @@
         <v>39</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -2627,12 +2617,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:3">
+    <row r="1" ht="23.25" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2644,156 +2634,156 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="8">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="7">
         <v>1</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="8">
+      <c r="A3" s="7">
         <v>1</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="7">
         <v>2</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2806,12 +2796,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:3">
+    <row r="1" ht="23.25" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2823,156 +2813,156 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="8">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="7">
         <v>1</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="9">
+      <c r="A3" s="8">
         <v>2</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B3" s="8">
         <v>2</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2985,12 +2975,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="6" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:6">
+    <row r="1" ht="23.25" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3011,200 +3001,200 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A2" s="8">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="7">
         <v>-1</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="7">
         <v>0</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="7">
         <v>1</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3217,12 +3207,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="5" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:5">
+    <row r="1" ht="23.25" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3240,244 +3230,244 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A2" s="8">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="7">
         <v>0</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A3" s="8">
+      <c r="A3" s="7">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="7">
         <v>1</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A4" s="8">
+      <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="8">
         <v>2</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3490,7 +3480,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="20.625" customWidth="1"/>
     <col min="2" max="2" width="22.375" customWidth="1"/>
@@ -3499,7 +3489,7 @@
     <col min="5" max="5" width="23.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:5">
+    <row r="1" ht="23.25" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3517,254 +3507,254 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A2" s="8">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="7">
         <v>0</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A3" s="8">
+      <c r="A3" s="7">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="7">
         <v>1</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A4" s="8">
+      <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="7">
         <v>2</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A5" s="9">
+      <c r="A5" s="8">
         <v>4</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="8">
         <v>3</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3777,12 +3767,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:3">
+    <row r="1" ht="23.25" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3794,154 +3784,154 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3954,12 +3944,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:3">
+    <row r="1" ht="23.25" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3971,73 +3961,73 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
       <c r="C2" s="3"/>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="9"/>
-      <c r="B3" s="8"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="7"/>
       <c r="C3" s="3"/>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
       <c r="C4" s="3"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="9"/>
-      <c r="B6" s="8"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="7"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="8"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="7"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
       <c r="C11" s="3"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="9"/>
-      <c r="B12" s="8"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="7"/>
       <c r="C12" s="3"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
       <c r="C13" s="3"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
       <c r="C14" s="3"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="9"/>
-      <c r="B15" s="8"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="7"/>
       <c r="C15" s="3"/>
     </row>
   </sheetData>
@@ -4050,8 +4040,8 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I97"/>
-  <sheetFormatPr defaultColWidth="19.75" defaultRowHeight="14"/>
+  <dimension ref="A1:I99"/>
+  <sheetFormatPr defaultColWidth="19.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="19.75" style="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
@@ -4063,7 +4053,7 @@
     <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:9">
+    <row r="1" ht="23.25" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5376,7 +5366,7 @@
       <c r="A54" s="3">
         <v>1904</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B54" s="6" t="s">
         <v>131</v>
       </c>
       <c r="C54" s="3">
@@ -5389,11 +5379,11 @@
       <c r="F54" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G54" s="7" t="s">
+      <c r="G54" s="6" t="s">
         <v>132</v>
       </c>
       <c r="H54" s="4"/>
-      <c r="I54" s="7" t="s">
+      <c r="I54" s="6" t="s">
         <v>131</v>
       </c>
     </row>
@@ -5401,7 +5391,7 @@
       <c r="A55" s="3">
         <v>1905</v>
       </c>
-      <c r="B55" s="7" t="s">
+      <c r="B55" s="6" t="s">
         <v>133</v>
       </c>
       <c r="C55" s="3">
@@ -5414,113 +5404,113 @@
       <c r="F55" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G55" s="7" t="s">
+      <c r="G55" s="6" t="s">
         <v>134</v>
       </c>
       <c r="H55" s="4"/>
-      <c r="I55" s="7" t="s">
+      <c r="I55" s="6" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" s="3">
-        <v>2</v>
-      </c>
-      <c r="B56" s="4" t="s">
+        <v>1906</v>
+      </c>
+      <c r="B56" s="6" t="s">
         <v>135</v>
       </c>
       <c r="C56" s="3">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="D56" s="3">
-        <v>2</v>
+        <v>1906</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G56" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>136</v>
+      </c>
       <c r="H56" s="4"/>
-      <c r="I56" s="4" t="s">
+      <c r="I56" s="6" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="3">
-        <v>21</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>136</v>
+        <v>1907</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>137</v>
       </c>
       <c r="C57" s="3">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D57" s="3">
-        <v>21</v>
+        <v>1907</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G57" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>138</v>
+      </c>
       <c r="H57" s="4"/>
-      <c r="I57" s="4" t="s">
-        <v>136</v>
+      <c r="I57" s="6" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" s="3">
-        <v>2110</v>
+        <v>2</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C58" s="3">
-        <v>21</v>
+        <v>-1</v>
       </c>
       <c r="D58" s="3">
-        <v>2110</v>
+        <v>2</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>138</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="59" spans="1:9">
       <c r="A59" s="3">
-        <v>2111</v>
+        <v>21</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C59" s="3">
+        <v>2</v>
+      </c>
+      <c r="D59" s="3">
         <v>21</v>
-      </c>
-      <c r="D59" s="3">
-        <v>2111</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>140</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G59" s="4"/>
       <c r="H59" s="4"/>
       <c r="I59" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="60" spans="1:9">
       <c r="A60" s="3">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>141</v>
@@ -5529,7 +5519,7 @@
         <v>21</v>
       </c>
       <c r="D60" s="3">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3" t="s">
@@ -5545,7 +5535,7 @@
     </row>
     <row r="61" spans="1:9">
       <c r="A61" s="3">
-        <v>2113</v>
+        <v>2111</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>143</v>
@@ -5554,14 +5544,14 @@
         <v>21</v>
       </c>
       <c r="D61" s="3">
-        <v>2113</v>
+        <v>2111</v>
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H61" s="4"/>
       <c r="I61" s="4" t="s">
@@ -5570,39 +5560,41 @@
     </row>
     <row r="62" spans="1:9">
       <c r="A62" s="3">
-        <v>22</v>
+        <v>2112</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C62" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D62" s="3">
-        <v>22</v>
+        <v>2112</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G62" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>146</v>
+      </c>
       <c r="H62" s="4"/>
       <c r="I62" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="63" spans="1:9">
       <c r="A63" s="3">
-        <v>2201</v>
+        <v>2113</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C63" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D63" s="3">
-        <v>2201</v>
+        <v>2113</v>
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3" t="s">
@@ -5613,37 +5605,35 @@
       </c>
       <c r="H63" s="4"/>
       <c r="I63" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" s="3">
-        <v>2202</v>
+        <v>22</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C64" s="3">
+        <v>2</v>
+      </c>
+      <c r="D64" s="3">
         <v>22</v>
-      </c>
-      <c r="D64" s="3">
-        <v>2202</v>
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>148</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G64" s="4"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="3">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>149</v>
@@ -5652,7 +5642,7 @@
         <v>22</v>
       </c>
       <c r="D65" s="3">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3" t="s">
@@ -5668,22 +5658,24 @@
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="3">
-        <v>23</v>
+        <v>2202</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>151</v>
       </c>
       <c r="C66" s="3">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D66" s="3">
-        <v>23</v>
+        <v>2202</v>
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G66" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>152</v>
+      </c>
       <c r="H66" s="4"/>
       <c r="I66" s="4" t="s">
         <v>151</v>
@@ -5691,41 +5683,41 @@
     </row>
     <row r="67" spans="1:9">
       <c r="A67" s="3">
-        <v>2301</v>
+        <v>2203</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C67" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D67" s="3">
-        <v>2301</v>
+        <v>2203</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H67" s="4"/>
       <c r="I67" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="3">
-        <v>2302</v>
+        <v>23</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>75</v>
+        <v>155</v>
       </c>
       <c r="C68" s="3">
+        <v>2</v>
+      </c>
+      <c r="D68" s="3">
         <v>23</v>
-      </c>
-      <c r="D68" s="3">
-        <v>2302</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3" t="s">
@@ -5734,77 +5726,77 @@
       <c r="G68" s="4"/>
       <c r="H68" s="4"/>
       <c r="I68" s="4" t="s">
-        <v>75</v>
+        <v>155</v>
       </c>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="3">
-        <v>23021</v>
+        <v>2301</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C69" s="3">
-        <v>2302</v>
+        <v>23</v>
       </c>
       <c r="D69" s="3">
-        <v>23021</v>
+        <v>2301</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H69" s="4"/>
       <c r="I69" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="3">
-        <v>23022</v>
+        <v>2302</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>156</v>
+        <v>75</v>
       </c>
       <c r="C70" s="3">
+        <v>23</v>
+      </c>
+      <c r="D70" s="3">
         <v>2302</v>
-      </c>
-      <c r="D70" s="3">
-        <v>23022</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>157</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G70" s="4"/>
       <c r="H70" s="4"/>
       <c r="I70" s="4" t="s">
-        <v>156</v>
+        <v>75</v>
       </c>
     </row>
     <row r="71" spans="1:9">
       <c r="A71" s="3">
-        <v>2303</v>
+        <v>23021</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>158</v>
       </c>
       <c r="C71" s="3">
-        <v>23</v>
+        <v>2302</v>
       </c>
       <c r="D71" s="3">
-        <v>2303</v>
+        <v>23021</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G71" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>159</v>
+      </c>
       <c r="H71" s="4"/>
       <c r="I71" s="4" t="s">
         <v>158</v>
@@ -5812,41 +5804,41 @@
     </row>
     <row r="72" spans="1:9">
       <c r="A72" s="3">
-        <v>23031</v>
+        <v>23022</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="C72" s="3">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="D72" s="3">
-        <v>23031</v>
+        <v>23022</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H72" s="4"/>
       <c r="I72" s="4" t="s">
-        <v>65</v>
+        <v>160</v>
       </c>
     </row>
     <row r="73" spans="1:9">
       <c r="A73" s="3">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>74</v>
+        <v>162</v>
       </c>
       <c r="C73" s="3">
         <v>23</v>
       </c>
       <c r="D73" s="3">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3" t="s">
@@ -5855,260 +5847,258 @@
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4" t="s">
-        <v>74</v>
+        <v>162</v>
       </c>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" s="3">
-        <v>23041</v>
+        <v>23031</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="C74" s="3">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="D74" s="3">
-        <v>23041</v>
+        <v>23031</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H74" s="4"/>
       <c r="I74" s="4" t="s">
-        <v>160</v>
+        <v>65</v>
       </c>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="3">
-        <v>23042</v>
+        <v>2304</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>162</v>
+        <v>74</v>
       </c>
       <c r="C75" s="3">
+        <v>23</v>
+      </c>
+      <c r="D75" s="3">
         <v>2304</v>
-      </c>
-      <c r="D75" s="3">
-        <v>23042</v>
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>163</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G75" s="4"/>
       <c r="H75" s="4"/>
       <c r="I75" s="4" t="s">
-        <v>162</v>
+        <v>74</v>
       </c>
     </row>
     <row r="76" spans="1:9">
       <c r="A76" s="3">
-        <v>23043</v>
-      </c>
-      <c r="B76" s="7" t="s">
+        <v>23041</v>
+      </c>
+      <c r="B76" s="4" t="s">
         <v>164</v>
       </c>
       <c r="C76" s="3">
         <v>2304</v>
       </c>
       <c r="D76" s="3">
-        <v>23043</v>
+        <v>23041</v>
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G76" s="7" t="s">
+      <c r="G76" s="4" t="s">
         <v>165</v>
       </c>
       <c r="H76" s="4"/>
-      <c r="I76" s="7" t="s">
+      <c r="I76" s="4" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="77" spans="1:9">
       <c r="A77" s="3">
-        <v>23044</v>
-      </c>
-      <c r="B77" s="7" t="s">
+        <v>23042</v>
+      </c>
+      <c r="B77" s="4" t="s">
         <v>166</v>
       </c>
       <c r="C77" s="3">
         <v>2304</v>
       </c>
       <c r="D77" s="3">
-        <v>23044</v>
+        <v>23042</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G77" s="7" t="s">
+      <c r="G77" s="4" t="s">
         <v>167</v>
       </c>
       <c r="H77" s="4"/>
-      <c r="I77" s="7" t="s">
+      <c r="I77" s="4" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" s="3">
-        <v>23045</v>
-      </c>
-      <c r="B78" s="7" t="s">
+        <v>23043</v>
+      </c>
+      <c r="B78" s="6" t="s">
         <v>168</v>
       </c>
       <c r="C78" s="3">
         <v>2304</v>
       </c>
       <c r="D78" s="3">
-        <v>23045</v>
+        <v>23043</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G78" s="7" t="s">
+      <c r="G78" s="6" t="s">
         <v>169</v>
       </c>
       <c r="H78" s="4"/>
-      <c r="I78" s="7" t="s">
+      <c r="I78" s="6" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="3">
-        <v>23046</v>
-      </c>
-      <c r="B79" s="7" t="s">
+        <v>23044</v>
+      </c>
+      <c r="B79" s="6" t="s">
         <v>170</v>
       </c>
       <c r="C79" s="3">
         <v>2304</v>
       </c>
       <c r="D79" s="3">
-        <v>23046</v>
+        <v>23044</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G79" s="7" t="s">
+      <c r="G79" s="6" t="s">
         <v>171</v>
       </c>
       <c r="H79" s="4"/>
-      <c r="I79" s="7" t="s">
+      <c r="I79" s="6" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="80" spans="1:9">
       <c r="A80" s="3">
-        <v>23047</v>
-      </c>
-      <c r="B80" s="4" t="s">
+        <v>23045</v>
+      </c>
+      <c r="B80" s="6" t="s">
         <v>172</v>
       </c>
       <c r="C80" s="3">
         <v>2304</v>
       </c>
       <c r="D80" s="3">
-        <v>23047</v>
+        <v>23045</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G80" s="4" t="s">
+      <c r="G80" s="6" t="s">
         <v>173</v>
       </c>
       <c r="H80" s="4"/>
-      <c r="I80" s="4" t="s">
+      <c r="I80" s="6" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="3">
-        <v>2305</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>111</v>
+        <v>23046</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>174</v>
       </c>
       <c r="C81" s="3">
-        <v>23</v>
+        <v>2304</v>
       </c>
       <c r="D81" s="3">
-        <v>2305</v>
+        <v>23046</v>
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G81" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G81" s="6" t="s">
+        <v>175</v>
+      </c>
       <c r="H81" s="4"/>
-      <c r="I81" s="4" t="s">
-        <v>111</v>
+      <c r="I81" s="6" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="82" spans="1:9">
       <c r="A82" s="3">
-        <v>23051</v>
+        <v>23047</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C82" s="3">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="D82" s="3">
-        <v>23051</v>
+        <v>23047</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H82" s="4"/>
       <c r="I82" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="3">
-        <v>23052</v>
+        <v>2305</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>176</v>
+        <v>111</v>
       </c>
       <c r="C83" s="3">
+        <v>23</v>
+      </c>
+      <c r="D83" s="3">
         <v>2305</v>
-      </c>
-      <c r="D83" s="3">
-        <v>23052</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G83" s="4" t="s">
-        <v>177</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G83" s="4"/>
       <c r="H83" s="4"/>
       <c r="I83" s="4" t="s">
-        <v>176</v>
+        <v>111</v>
       </c>
     </row>
     <row r="84" spans="1:9">
       <c r="A84" s="3">
-        <v>23053</v>
+        <v>23051</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>178</v>
@@ -6117,7 +6107,7 @@
         <v>2305</v>
       </c>
       <c r="D84" s="3">
-        <v>23053</v>
+        <v>23051</v>
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3" t="s">
@@ -6133,7 +6123,7 @@
     </row>
     <row r="85" spans="1:9">
       <c r="A85" s="3">
-        <v>23054</v>
+        <v>23052</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>180</v>
@@ -6142,7 +6132,7 @@
         <v>2305</v>
       </c>
       <c r="D85" s="3">
-        <v>23054</v>
+        <v>23052</v>
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="3" t="s">
@@ -6158,7 +6148,7 @@
     </row>
     <row r="86" spans="1:9">
       <c r="A86" s="3">
-        <v>23055</v>
+        <v>23053</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>182</v>
@@ -6167,7 +6157,7 @@
         <v>2305</v>
       </c>
       <c r="D86" s="3">
-        <v>23055</v>
+        <v>23053</v>
       </c>
       <c r="E86" s="3"/>
       <c r="F86" s="3" t="s">
@@ -6183,7 +6173,7 @@
     </row>
     <row r="87" spans="1:9">
       <c r="A87" s="3">
-        <v>23056</v>
+        <v>23054</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>184</v>
@@ -6192,7 +6182,7 @@
         <v>2305</v>
       </c>
       <c r="D87" s="3">
-        <v>23056</v>
+        <v>23054</v>
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="3" t="s">
@@ -6208,112 +6198,114 @@
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="3">
-        <v>2306</v>
+        <v>23055</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>92</v>
+        <v>186</v>
       </c>
       <c r="C88" s="3">
-        <v>23</v>
+        <v>2305</v>
       </c>
       <c r="D88" s="3">
-        <v>2306</v>
+        <v>23055</v>
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G88" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>187</v>
+      </c>
       <c r="H88" s="4"/>
       <c r="I88" s="4" t="s">
-        <v>92</v>
+        <v>186</v>
       </c>
     </row>
     <row r="89" spans="1:9">
       <c r="A89" s="3">
-        <v>23061</v>
+        <v>23056</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C89" s="3">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="D89" s="3">
-        <v>23061</v>
+        <v>23056</v>
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H89" s="4"/>
       <c r="I89" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="90" spans="1:9">
       <c r="A90" s="3">
-        <v>24</v>
+        <v>2306</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>188</v>
+        <v>92</v>
       </c>
       <c r="C90" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D90" s="3">
-        <v>24</v>
-      </c>
-      <c r="E90" s="4"/>
+        <v>2306</v>
+      </c>
+      <c r="E90" s="3"/>
       <c r="F90" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G90" s="4"/>
       <c r="H90" s="4"/>
       <c r="I90" s="4" t="s">
-        <v>188</v>
+        <v>92</v>
       </c>
     </row>
     <row r="91" spans="1:9">
       <c r="A91" s="3">
-        <v>2401</v>
+        <v>23061</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C91" s="3">
-        <v>24</v>
+        <v>2306</v>
       </c>
       <c r="D91" s="3">
-        <v>2401</v>
-      </c>
-      <c r="E91" s="4"/>
+        <v>23061</v>
+      </c>
+      <c r="E91" s="3"/>
       <c r="F91" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H91" s="4"/>
       <c r="I91" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C92" s="3">
         <v>2</v>
       </c>
       <c r="D92" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E92" s="4"/>
       <c r="F92" s="3" t="s">
@@ -6322,71 +6314,69 @@
       <c r="G92" s="4"/>
       <c r="H92" s="4"/>
       <c r="I92" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="93" spans="1:9">
       <c r="A93" s="3">
-        <v>2501</v>
+        <v>2401</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C93" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D93" s="3">
-        <v>2501</v>
-      </c>
-      <c r="E93" s="3"/>
+        <v>2401</v>
+      </c>
+      <c r="E93" s="4"/>
       <c r="F93" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="H93" s="3"/>
+        <v>194</v>
+      </c>
+      <c r="H93" s="4"/>
       <c r="I93" s="4" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="94" spans="1:9">
       <c r="A94" s="3">
-        <v>2502</v>
+        <v>25</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C94" s="3">
+        <v>2</v>
+      </c>
+      <c r="D94" s="3">
         <v>25</v>
       </c>
-      <c r="D94" s="3">
-        <v>2502</v>
-      </c>
-      <c r="E94" s="3"/>
+      <c r="E94" s="4"/>
       <c r="F94" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G94" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="H94" s="5"/>
-      <c r="I94" s="5" t="s">
-        <v>193</v>
+        <v>36</v>
+      </c>
+      <c r="G94" s="4"/>
+      <c r="H94" s="4"/>
+      <c r="I94" s="4" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="95" spans="1:9">
       <c r="A95" s="3">
-        <v>2503</v>
+        <v>2501</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C95" s="3">
         <v>25</v>
       </c>
       <c r="D95" s="3">
-        <v>2503</v>
+        <v>2501</v>
       </c>
       <c r="E95" s="3"/>
       <c r="F95" s="3" t="s">
@@ -6395,57 +6385,107 @@
       <c r="G95" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="H95" s="4"/>
+      <c r="H95" s="3"/>
       <c r="I95" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="96" spans="1:9">
       <c r="A96" s="3">
-        <v>26</v>
+        <v>2502</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>197</v>
       </c>
       <c r="C96" s="3">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D96" s="3">
-        <v>26</v>
+        <v>2502</v>
       </c>
       <c r="E96" s="3"/>
       <c r="F96" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G96" s="4"/>
-      <c r="H96" s="4"/>
-      <c r="I96" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="H96" s="5"/>
+      <c r="I96" s="5" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="3">
-        <v>2601</v>
+        <v>2503</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C97" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D97" s="3">
-        <v>2601</v>
-      </c>
-      <c r="E97" s="4"/>
+        <v>2503</v>
+      </c>
+      <c r="E97" s="3"/>
       <c r="F97" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H97" s="4"/>
       <c r="I97" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="A98" s="3">
+        <v>26</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C98" s="3">
+        <v>2</v>
+      </c>
+      <c r="D98" s="3">
+        <v>26</v>
+      </c>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G98" s="4"/>
+      <c r="H98" s="4"/>
+      <c r="I98" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="A99" s="3">
+        <v>2601</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C99" s="3">
+        <v>26</v>
+      </c>
+      <c r="D99" s="3">
+        <v>2601</v>
+      </c>
+      <c r="E99" s="4"/>
+      <c r="F99" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="H99" s="4"/>
+      <c r="I99" s="4" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24225" windowHeight="12540" tabRatio="500" activeTab="8"/>
+    <workbookView windowHeight="17295" tabRatio="500" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="SysUser" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,25 @@
     <sheet name="SysMenu" sheetId="9" r:id="rId9"/>
     <sheet name="SysManagement" sheetId="10" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="215">
   <si>
     <t>Id</t>
   </si>
@@ -569,6 +582,12 @@
     <t>CugaCalibration.ViewModels.Common.Windows.Tools.Stage.StageMapWindowViewModel</t>
   </si>
   <si>
+    <t>RTA</t>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Common.Windows.Tools.Stage.RTAWindowViewModel</t>
+  </si>
+  <si>
     <t>Generate Prescan AOD Waveform</t>
   </si>
   <si>
@@ -719,12 +738,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -754,6 +773,60 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -763,21 +836,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -792,7 +867,29 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -806,92 +903,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -925,7 +944,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -937,7 +1034,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -949,67 +1112,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1019,92 +1122,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1116,6 +1135,19 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -1141,15 +1173,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -1161,6 +1184,54 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1180,41 +1251,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1233,15 +1274,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="thick">
         <color rgb="FFA1B8E1"/>
       </bottom>
@@ -1252,155 +1284,155 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1422,13 +1454,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="10" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1437,52 +1478,52 @@
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
     <cellStyle name="Excel Built-in Heading 2" xfId="49"/>
@@ -1680,7 +1721,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -1689,7 +1730,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -1924,487 +1965,487 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A2" s="7">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="10">
         <v>1</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="9" t="s">
+      <c r="E2" s="10"/>
+      <c r="F2" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="10">
         <v>666666</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A3" s="8">
+      <c r="A3" s="11">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="11">
         <v>1</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="9" t="s">
+      <c r="E3" s="11"/>
+      <c r="F3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="10">
         <v>666666</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
+      <c r="A31" s="13"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
     </row>
     <row r="32" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
+      <c r="A32" s="13"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
     </row>
     <row r="33" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
+      <c r="A33" s="13"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
     </row>
     <row r="34" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
+      <c r="A34" s="13"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
     </row>
     <row r="35" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="10"/>
+      <c r="A35" s="13"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
     </row>
     <row r="36" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A36" s="10"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
+      <c r="A36" s="13"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
     </row>
     <row r="37" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A37" s="10"/>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
+      <c r="A37" s="13"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
     </row>
     <row r="38" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A38" s="10"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
+      <c r="A38" s="13"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
     </row>
     <row r="39" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A39" s="10"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="10"/>
+      <c r="A39" s="13"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
     </row>
     <row r="40" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A40" s="10"/>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
+      <c r="A40" s="13"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
     </row>
     <row r="41" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A41" s="10"/>
-      <c r="B41" s="10"/>
-      <c r="C41" s="10"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
+      <c r="A41" s="13"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13"/>
     </row>
     <row r="42" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A42" s="10"/>
-      <c r="B42" s="10"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="10"/>
+      <c r="A42" s="13"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="13"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2466,7 +2507,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C2" s="3">
         <v>-1</v>
@@ -2481,7 +2522,7 @@
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:9">
@@ -2489,7 +2530,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C3" s="3">
         <v>1</v>
@@ -2504,7 +2545,7 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:9">
@@ -2512,7 +2553,7 @@
         <v>1101</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C4" s="3">
         <v>11</v>
@@ -2525,11 +2566,11 @@
         <v>39</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:9">
@@ -2537,7 +2578,7 @@
         <v>1102</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C5" s="3">
         <v>11</v>
@@ -2550,11 +2591,11 @@
         <v>39</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:9">
@@ -2562,7 +2603,7 @@
         <v>1103</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C6" s="3">
         <v>11</v>
@@ -2575,11 +2616,11 @@
         <v>39</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:9">
@@ -2587,7 +2628,7 @@
         <v>1104</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C7" s="3">
         <v>11</v>
@@ -2600,11 +2641,11 @@
         <v>39</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -2634,156 +2675,156 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="7">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="10">
         <v>1</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="7">
+      <c r="A3" s="10">
         <v>1</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="10">
         <v>2</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="10">
         <v>2</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2813,156 +2854,156 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="7">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="10">
         <v>1</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="8">
+      <c r="A3" s="11">
         <v>2</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="11">
         <v>2</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3001,200 +3042,200 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A2" s="7">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="10">
         <v>-1</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="10">
         <v>0</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="10">
         <v>1</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="10" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3230,244 +3271,244 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A2" s="7">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="10">
         <v>0</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="10" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A3" s="7">
+      <c r="A3" s="10">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="10">
         <v>1</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A4" s="7">
+      <c r="A4" s="10">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="11">
         <v>2</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
+      <c r="A30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3507,254 +3548,254 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A2" s="7">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="10">
         <v>0</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="10" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A3" s="7">
+      <c r="A3" s="10">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="10">
         <v>1</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A4" s="7">
+      <c r="A4" s="10">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="10">
         <v>2</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A5" s="8">
+      <c r="A5" s="11">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="11">
         <v>3</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="11" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
+      <c r="A30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3784,154 +3825,154 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
+      <c r="A30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3961,73 +4002,73 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
       <c r="C2" s="3"/>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="7"/>
+      <c r="A3" s="11"/>
+      <c r="B3" s="10"/>
       <c r="C3" s="3"/>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
       <c r="C4" s="3"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="7"/>
+      <c r="A6" s="11"/>
+      <c r="B6" s="10"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="7"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="10"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
       <c r="C11" s="3"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="7"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="10"/>
       <c r="C12" s="3"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
       <c r="C13" s="3"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
       <c r="C14" s="3"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="7"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="10"/>
       <c r="C15" s="3"/>
     </row>
   </sheetData>
@@ -4040,7 +4081,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I99"/>
+  <dimension ref="A1:I100"/>
   <sheetFormatPr defaultColWidth="19.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="19.75" style="1"/>
@@ -5876,56 +5917,56 @@
       </c>
     </row>
     <row r="75" spans="1:9">
-      <c r="A75" s="3">
-        <v>2304</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C75" s="3">
-        <v>23</v>
-      </c>
-      <c r="D75" s="3">
-        <v>2304</v>
-      </c>
-      <c r="E75" s="3"/>
-      <c r="F75" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G75" s="4"/>
-      <c r="H75" s="4"/>
-      <c r="I75" s="4" t="s">
-        <v>74</v>
+      <c r="A75" s="7">
+        <v>23032</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="C75" s="9">
+        <v>2303</v>
+      </c>
+      <c r="D75" s="9">
+        <v>23032</v>
+      </c>
+      <c r="E75" s="9"/>
+      <c r="F75" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="H75" s="8"/>
+      <c r="I75" s="8" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="76" spans="1:9">
       <c r="A76" s="3">
-        <v>23041</v>
+        <v>2304</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>164</v>
+        <v>74</v>
       </c>
       <c r="C76" s="3">
+        <v>23</v>
+      </c>
+      <c r="D76" s="3">
         <v>2304</v>
-      </c>
-      <c r="D76" s="3">
-        <v>23041</v>
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>165</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G76" s="4"/>
       <c r="H76" s="4"/>
       <c r="I76" s="4" t="s">
-        <v>164</v>
+        <v>74</v>
       </c>
     </row>
     <row r="77" spans="1:9">
       <c r="A77" s="3">
-        <v>23042</v>
+        <v>23041</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>166</v>
@@ -5934,7 +5975,7 @@
         <v>2304</v>
       </c>
       <c r="D77" s="3">
-        <v>23042</v>
+        <v>23041</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3" t="s">
@@ -5950,32 +5991,32 @@
     </row>
     <row r="78" spans="1:9">
       <c r="A78" s="3">
-        <v>23043</v>
-      </c>
-      <c r="B78" s="6" t="s">
+        <v>23042</v>
+      </c>
+      <c r="B78" s="4" t="s">
         <v>168</v>
       </c>
       <c r="C78" s="3">
         <v>2304</v>
       </c>
       <c r="D78" s="3">
-        <v>23043</v>
+        <v>23042</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G78" s="6" t="s">
+      <c r="G78" s="4" t="s">
         <v>169</v>
       </c>
       <c r="H78" s="4"/>
-      <c r="I78" s="6" t="s">
+      <c r="I78" s="4" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="3">
-        <v>23044</v>
+        <v>23043</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>170</v>
@@ -5984,7 +6025,7 @@
         <v>2304</v>
       </c>
       <c r="D79" s="3">
-        <v>23044</v>
+        <v>23043</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3" t="s">
@@ -6000,7 +6041,7 @@
     </row>
     <row r="80" spans="1:9">
       <c r="A80" s="3">
-        <v>23045</v>
+        <v>23044</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>172</v>
@@ -6009,7 +6050,7 @@
         <v>2304</v>
       </c>
       <c r="D80" s="3">
-        <v>23045</v>
+        <v>23044</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3" t="s">
@@ -6025,7 +6066,7 @@
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="3">
-        <v>23046</v>
+        <v>23045</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>174</v>
@@ -6034,7 +6075,7 @@
         <v>2304</v>
       </c>
       <c r="D81" s="3">
-        <v>23046</v>
+        <v>23045</v>
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3" t="s">
@@ -6050,80 +6091,80 @@
     </row>
     <row r="82" spans="1:9">
       <c r="A82" s="3">
-        <v>23047</v>
-      </c>
-      <c r="B82" s="4" t="s">
+        <v>23046</v>
+      </c>
+      <c r="B82" s="6" t="s">
         <v>176</v>
       </c>
       <c r="C82" s="3">
         <v>2304</v>
       </c>
       <c r="D82" s="3">
-        <v>23047</v>
+        <v>23046</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G82" s="4" t="s">
+      <c r="G82" s="6" t="s">
         <v>177</v>
       </c>
       <c r="H82" s="4"/>
-      <c r="I82" s="4" t="s">
+      <c r="I82" s="6" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="3">
-        <v>2305</v>
+        <v>23047</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>111</v>
+        <v>178</v>
       </c>
       <c r="C83" s="3">
-        <v>23</v>
+        <v>2304</v>
       </c>
       <c r="D83" s="3">
-        <v>2305</v>
+        <v>23047</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G83" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>179</v>
+      </c>
       <c r="H83" s="4"/>
       <c r="I83" s="4" t="s">
-        <v>111</v>
+        <v>178</v>
       </c>
     </row>
     <row r="84" spans="1:9">
       <c r="A84" s="3">
-        <v>23051</v>
+        <v>2305</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>178</v>
+        <v>111</v>
       </c>
       <c r="C84" s="3">
+        <v>23</v>
+      </c>
+      <c r="D84" s="3">
         <v>2305</v>
-      </c>
-      <c r="D84" s="3">
-        <v>23051</v>
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G84" s="4" t="s">
-        <v>179</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G84" s="4"/>
       <c r="H84" s="4"/>
       <c r="I84" s="4" t="s">
-        <v>178</v>
+        <v>111</v>
       </c>
     </row>
     <row r="85" spans="1:9">
       <c r="A85" s="3">
-        <v>23052</v>
+        <v>23051</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>180</v>
@@ -6132,7 +6173,7 @@
         <v>2305</v>
       </c>
       <c r="D85" s="3">
-        <v>23052</v>
+        <v>23051</v>
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="3" t="s">
@@ -6148,7 +6189,7 @@
     </row>
     <row r="86" spans="1:9">
       <c r="A86" s="3">
-        <v>23053</v>
+        <v>23052</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>182</v>
@@ -6157,7 +6198,7 @@
         <v>2305</v>
       </c>
       <c r="D86" s="3">
-        <v>23053</v>
+        <v>23052</v>
       </c>
       <c r="E86" s="3"/>
       <c r="F86" s="3" t="s">
@@ -6173,7 +6214,7 @@
     </row>
     <row r="87" spans="1:9">
       <c r="A87" s="3">
-        <v>23054</v>
+        <v>23053</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>184</v>
@@ -6182,7 +6223,7 @@
         <v>2305</v>
       </c>
       <c r="D87" s="3">
-        <v>23054</v>
+        <v>23053</v>
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="3" t="s">
@@ -6198,7 +6239,7 @@
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="3">
-        <v>23055</v>
+        <v>23054</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>186</v>
@@ -6207,7 +6248,7 @@
         <v>2305</v>
       </c>
       <c r="D88" s="3">
-        <v>23055</v>
+        <v>23054</v>
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3" t="s">
@@ -6223,7 +6264,7 @@
     </row>
     <row r="89" spans="1:9">
       <c r="A89" s="3">
-        <v>23056</v>
+        <v>23055</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>188</v>
@@ -6232,7 +6273,7 @@
         <v>2305</v>
       </c>
       <c r="D89" s="3">
-        <v>23056</v>
+        <v>23055</v>
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="3" t="s">
@@ -6248,70 +6289,72 @@
     </row>
     <row r="90" spans="1:9">
       <c r="A90" s="3">
-        <v>2306</v>
+        <v>23056</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>92</v>
+        <v>190</v>
       </c>
       <c r="C90" s="3">
-        <v>23</v>
+        <v>2305</v>
       </c>
       <c r="D90" s="3">
-        <v>2306</v>
+        <v>23056</v>
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G90" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>191</v>
+      </c>
       <c r="H90" s="4"/>
       <c r="I90" s="4" t="s">
-        <v>92</v>
+        <v>190</v>
       </c>
     </row>
     <row r="91" spans="1:9">
       <c r="A91" s="3">
-        <v>23061</v>
+        <v>2306</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>190</v>
+        <v>92</v>
       </c>
       <c r="C91" s="3">
+        <v>23</v>
+      </c>
+      <c r="D91" s="3">
         <v>2306</v>
-      </c>
-      <c r="D91" s="3">
-        <v>23061</v>
       </c>
       <c r="E91" s="3"/>
       <c r="F91" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G91" s="4" t="s">
-        <v>191</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G91" s="4"/>
       <c r="H91" s="4"/>
       <c r="I91" s="4" t="s">
-        <v>190</v>
+        <v>92</v>
       </c>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" s="3">
-        <v>24</v>
+        <v>23061</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>192</v>
       </c>
       <c r="C92" s="3">
-        <v>2</v>
+        <v>2306</v>
       </c>
       <c r="D92" s="3">
-        <v>24</v>
-      </c>
-      <c r="E92" s="4"/>
+        <v>23061</v>
+      </c>
+      <c r="E92" s="3"/>
       <c r="F92" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G92" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>193</v>
+      </c>
       <c r="H92" s="4"/>
       <c r="I92" s="4" t="s">
         <v>192</v>
@@ -6319,47 +6362,47 @@
     </row>
     <row r="93" spans="1:9">
       <c r="A93" s="3">
-        <v>2401</v>
+        <v>24</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C93" s="3">
+        <v>2</v>
+      </c>
+      <c r="D93" s="3">
         <v>24</v>
-      </c>
-      <c r="D93" s="3">
-        <v>2401</v>
       </c>
       <c r="E93" s="4"/>
       <c r="F93" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G93" s="4" t="s">
-        <v>194</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G93" s="4"/>
       <c r="H93" s="4"/>
       <c r="I93" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="94" spans="1:9">
       <c r="A94" s="3">
-        <v>25</v>
+        <v>2401</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>195</v>
       </c>
       <c r="C94" s="3">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D94" s="3">
-        <v>25</v>
+        <v>2401</v>
       </c>
       <c r="E94" s="4"/>
       <c r="F94" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G94" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>196</v>
+      </c>
       <c r="H94" s="4"/>
       <c r="I94" s="4" t="s">
         <v>195</v>
@@ -6367,41 +6410,39 @@
     </row>
     <row r="95" spans="1:9">
       <c r="A95" s="3">
-        <v>2501</v>
+        <v>25</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="C95" s="3">
+        <v>2</v>
+      </c>
+      <c r="D95" s="3">
         <v>25</v>
       </c>
-      <c r="D95" s="3">
-        <v>2501</v>
-      </c>
-      <c r="E95" s="3"/>
+      <c r="E95" s="4"/>
       <c r="F95" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G95" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="H95" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="G95" s="4"/>
+      <c r="H95" s="4"/>
       <c r="I95" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
     </row>
     <row r="96" spans="1:9">
       <c r="A96" s="3">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C96" s="3">
         <v>25</v>
       </c>
       <c r="D96" s="3">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="E96" s="3"/>
       <c r="F96" s="3" t="s">
@@ -6410,14 +6451,14 @@
       <c r="G96" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="H96" s="5"/>
-      <c r="I96" s="5" t="s">
-        <v>197</v>
+      <c r="H96" s="3"/>
+      <c r="I96" s="4" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="3">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>199</v>
@@ -6426,7 +6467,7 @@
         <v>25</v>
       </c>
       <c r="D97" s="3">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="E97" s="3"/>
       <c r="F97" s="3" t="s">
@@ -6435,29 +6476,31 @@
       <c r="G97" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="H97" s="4"/>
-      <c r="I97" s="4" t="s">
+      <c r="H97" s="5"/>
+      <c r="I97" s="5" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="3">
-        <v>26</v>
+        <v>2503</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>201</v>
       </c>
       <c r="C98" s="3">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D98" s="3">
-        <v>26</v>
+        <v>2503</v>
       </c>
       <c r="E98" s="3"/>
       <c r="F98" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G98" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>202</v>
+      </c>
       <c r="H98" s="4"/>
       <c r="I98" s="4" t="s">
         <v>201</v>
@@ -6465,27 +6508,50 @@
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="3">
-        <v>2601</v>
+        <v>26</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C99" s="3">
+        <v>2</v>
+      </c>
+      <c r="D99" s="3">
         <v>26</v>
       </c>
-      <c r="D99" s="3">
-        <v>2601</v>
-      </c>
-      <c r="E99" s="4"/>
+      <c r="E99" s="3"/>
       <c r="F99" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G99" s="4" t="s">
-        <v>203</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G99" s="4"/>
       <c r="H99" s="4"/>
       <c r="I99" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
+      <c r="A100" s="3">
+        <v>2601</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C100" s="3">
+        <v>26</v>
+      </c>
+      <c r="D100" s="3">
+        <v>2601</v>
+      </c>
+      <c r="E100" s="4"/>
+      <c r="F100" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="H100" s="4"/>
+      <c r="I100" s="4" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>

--- a/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/InitData.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" tabRatio="500" activeTab="8"/>
+    <workbookView windowHeight="17295" tabRatio="500" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="SysUser" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="215">
   <si>
     <t>Id</t>
   </si>
@@ -441,6 +441,18 @@
   </si>
   <si>
     <t>CugaCalibration.ViewModels.Fourier.V0FourierCenterChannelSpecularBlockerViewModel</t>
+  </si>
+  <si>
+    <t>Center Channel Flexible Aperture V2</t>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Fourier.FourierCenterChannelFlexibleApertureViewModel</t>
+  </si>
+  <si>
+    <t>Center Channel Specular Blocker V2</t>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Fourier.FourierCenterChannelSpecularBlockerViewModel</t>
   </si>
   <si>
     <t>Title</t>
@@ -570,6 +582,12 @@
     <t>CugaCalibration.ViewModels.Common.Windows.Tools.Stage.StageMapWindowViewModel</t>
   </si>
   <si>
+    <t>RTA</t>
+  </si>
+  <si>
+    <t>CugaCalibration.ViewModels.Common.Windows.Tools.Stage.RTAWindowViewModel</t>
+  </si>
+  <si>
     <t>Generate Prescan AOD Waveform</t>
   </si>
   <si>
@@ -727,7 +745,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -738,12 +756,6 @@
       <b/>
       <sz val="18"/>
       <color rgb="FF44546A"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -1111,7 +1123,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1123,6 +1135,19 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -1259,28 +1284,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1289,125 +1317,122 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1429,19 +1454,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="6" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1897,14 +1928,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I42"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="5" width="20.625" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="9" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:9">
+    <row r="1" ht="23.25" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1934,487 +1965,487 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A2" s="8">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="10">
         <v>1</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="10" t="s">
+      <c r="E2" s="10"/>
+      <c r="F2" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="10">
         <v>666666</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A3" s="9">
+      <c r="A3" s="11">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="11">
         <v>1</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="10" t="s">
+      <c r="E3" s="11"/>
+      <c r="F3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="10">
         <v>666666</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A30" s="11"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11"/>
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A31" s="11"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
+      <c r="A31" s="13"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
     </row>
     <row r="32" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
+      <c r="A32" s="13"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
     </row>
     <row r="33" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
+      <c r="A33" s="13"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
     </row>
     <row r="34" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="11"/>
+      <c r="A34" s="13"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
     </row>
     <row r="35" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
+      <c r="A35" s="13"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
     </row>
     <row r="36" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A36" s="11"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="11"/>
+      <c r="A36" s="13"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
     </row>
     <row r="37" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A37" s="11"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="11"/>
+      <c r="A37" s="13"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
     </row>
     <row r="38" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A38" s="11"/>
-      <c r="B38" s="11"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="11"/>
-      <c r="I38" s="11"/>
+      <c r="A38" s="13"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
     </row>
     <row r="39" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A39" s="11"/>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="11"/>
-      <c r="I39" s="11"/>
+      <c r="A39" s="13"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
     </row>
     <row r="40" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A40" s="11"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="11"/>
-      <c r="I40" s="11"/>
+      <c r="A40" s="13"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
     </row>
     <row r="41" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A41" s="11"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="11"/>
+      <c r="A41" s="13"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13"/>
     </row>
     <row r="42" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A42" s="11"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="11"/>
-      <c r="I42" s="11"/>
+      <c r="A42" s="13"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="13"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2431,7 +2462,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="20.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="45.375" customWidth="1"/>
@@ -2476,7 +2507,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C2" s="3">
         <v>-1</v>
@@ -2491,7 +2522,7 @@
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:9">
@@ -2499,7 +2530,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C3" s="3">
         <v>1</v>
@@ -2514,7 +2545,7 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:9">
@@ -2522,7 +2553,7 @@
         <v>1101</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C4" s="3">
         <v>11</v>
@@ -2535,11 +2566,11 @@
         <v>39</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:9">
@@ -2547,7 +2578,7 @@
         <v>1102</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C5" s="3">
         <v>11</v>
@@ -2560,11 +2591,11 @@
         <v>39</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:9">
@@ -2572,7 +2603,7 @@
         <v>1103</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C6" s="3">
         <v>11</v>
@@ -2585,11 +2616,11 @@
         <v>39</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:9">
@@ -2597,7 +2628,7 @@
         <v>1104</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C7" s="3">
         <v>11</v>
@@ -2610,11 +2641,11 @@
         <v>39</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -2627,12 +2658,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:3">
+    <row r="1" ht="23.25" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2644,156 +2675,156 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="8">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="10">
         <v>1</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="8">
+      <c r="A3" s="10">
         <v>1</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="10">
         <v>2</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="10">
         <v>2</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2806,12 +2837,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:3">
+    <row r="1" ht="23.25" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2823,156 +2854,156 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="8">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="10">
         <v>1</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="9">
+      <c r="A3" s="11">
         <v>2</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B3" s="11">
         <v>2</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2985,12 +3016,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="6" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:6">
+    <row r="1" ht="23.25" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3011,200 +3042,200 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A2" s="8">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="10">
         <v>-1</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="10">
         <v>0</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="10">
         <v>1</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="10" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:6">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3217,12 +3248,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="5" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:5">
+    <row r="1" ht="23.25" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3240,244 +3271,244 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A2" s="8">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="10">
         <v>0</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="10" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A3" s="8">
+      <c r="A3" s="10">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="10">
         <v>1</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A4" s="8">
+      <c r="A4" s="10">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="11">
         <v>2</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
+      <c r="A30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3490,7 +3521,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="20.625" customWidth="1"/>
     <col min="2" max="2" width="22.375" customWidth="1"/>
@@ -3499,7 +3530,7 @@
     <col min="5" max="5" width="23.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:5">
+    <row r="1" ht="23.25" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3517,254 +3548,254 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A2" s="8">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="10">
         <v>0</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="10" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A3" s="8">
+      <c r="A3" s="10">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="10">
         <v>1</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A4" s="8">
+      <c r="A4" s="10">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="10">
         <v>2</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A5" s="9">
+      <c r="A5" s="11">
         <v>4</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="11">
         <v>3</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="11" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
+      <c r="A30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3777,12 +3808,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:3">
+    <row r="1" ht="23.25" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3794,154 +3825,154 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
+      <c r="A30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.752083333333333" right="0.752083333333333" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3954,12 +3985,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:3">
+    <row r="1" ht="23.25" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3971,73 +4002,73 @@
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
       <c r="C2" s="3"/>
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A3" s="9"/>
-      <c r="B3" s="8"/>
+      <c r="A3" s="11"/>
+      <c r="B3" s="10"/>
       <c r="C3" s="3"/>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
       <c r="C4" s="3"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A6" s="9"/>
-      <c r="B6" s="8"/>
+      <c r="A6" s="11"/>
+      <c r="B6" s="10"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="8"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="10"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
       <c r="C11" s="3"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A12" s="9"/>
-      <c r="B12" s="8"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="10"/>
       <c r="C12" s="3"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
       <c r="C13" s="3"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
       <c r="C14" s="3"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:3">
-      <c r="A15" s="9"/>
-      <c r="B15" s="8"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="10"/>
       <c r="C15" s="3"/>
     </row>
   </sheetData>
@@ -4050,8 +4081,8 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I97"/>
-  <sheetFormatPr defaultColWidth="19.75" defaultRowHeight="14"/>
+  <dimension ref="A1:I100"/>
+  <sheetFormatPr defaultColWidth="19.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="19.75" style="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
@@ -4063,7 +4094,7 @@
     <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:9">
+    <row r="1" ht="23.25" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5376,7 +5407,7 @@
       <c r="A54" s="3">
         <v>1904</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B54" s="6" t="s">
         <v>131</v>
       </c>
       <c r="C54" s="3">
@@ -5389,11 +5420,11 @@
       <c r="F54" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G54" s="7" t="s">
+      <c r="G54" s="6" t="s">
         <v>132</v>
       </c>
       <c r="H54" s="4"/>
-      <c r="I54" s="7" t="s">
+      <c r="I54" s="6" t="s">
         <v>131</v>
       </c>
     </row>
@@ -5401,7 +5432,7 @@
       <c r="A55" s="3">
         <v>1905</v>
       </c>
-      <c r="B55" s="7" t="s">
+      <c r="B55" s="6" t="s">
         <v>133</v>
       </c>
       <c r="C55" s="3">
@@ -5414,113 +5445,113 @@
       <c r="F55" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G55" s="7" t="s">
+      <c r="G55" s="6" t="s">
         <v>134</v>
       </c>
       <c r="H55" s="4"/>
-      <c r="I55" s="7" t="s">
+      <c r="I55" s="6" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" s="3">
-        <v>2</v>
-      </c>
-      <c r="B56" s="4" t="s">
+        <v>1906</v>
+      </c>
+      <c r="B56" s="6" t="s">
         <v>135</v>
       </c>
       <c r="C56" s="3">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="D56" s="3">
-        <v>2</v>
+        <v>1906</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G56" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>136</v>
+      </c>
       <c r="H56" s="4"/>
-      <c r="I56" s="4" t="s">
+      <c r="I56" s="6" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="3">
-        <v>21</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>136</v>
+        <v>1907</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>137</v>
       </c>
       <c r="C57" s="3">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D57" s="3">
-        <v>21</v>
+        <v>1907</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G57" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>138</v>
+      </c>
       <c r="H57" s="4"/>
-      <c r="I57" s="4" t="s">
-        <v>136</v>
+      <c r="I57" s="6" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" s="3">
-        <v>2110</v>
+        <v>2</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C58" s="3">
-        <v>21</v>
+        <v>-1</v>
       </c>
       <c r="D58" s="3">
-        <v>2110</v>
+        <v>2</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>138</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="59" spans="1:9">
       <c r="A59" s="3">
-        <v>2111</v>
+        <v>21</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C59" s="3">
+        <v>2</v>
+      </c>
+      <c r="D59" s="3">
         <v>21</v>
-      </c>
-      <c r="D59" s="3">
-        <v>2111</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>140</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G59" s="4"/>
       <c r="H59" s="4"/>
       <c r="I59" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="60" spans="1:9">
       <c r="A60" s="3">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>141</v>
@@ -5529,7 +5560,7 @@
         <v>21</v>
       </c>
       <c r="D60" s="3">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3" t="s">
@@ -5545,7 +5576,7 @@
     </row>
     <row r="61" spans="1:9">
       <c r="A61" s="3">
-        <v>2113</v>
+        <v>2111</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>143</v>
@@ -5554,14 +5585,14 @@
         <v>21</v>
       </c>
       <c r="D61" s="3">
-        <v>2113</v>
+        <v>2111</v>
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H61" s="4"/>
       <c r="I61" s="4" t="s">
@@ -5570,39 +5601,41 @@
     </row>
     <row r="62" spans="1:9">
       <c r="A62" s="3">
-        <v>22</v>
+        <v>2112</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C62" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D62" s="3">
-        <v>22</v>
+        <v>2112</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G62" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>146</v>
+      </c>
       <c r="H62" s="4"/>
       <c r="I62" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="63" spans="1:9">
       <c r="A63" s="3">
-        <v>2201</v>
+        <v>2113</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C63" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D63" s="3">
-        <v>2201</v>
+        <v>2113</v>
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3" t="s">
@@ -5613,37 +5646,35 @@
       </c>
       <c r="H63" s="4"/>
       <c r="I63" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" s="3">
-        <v>2202</v>
+        <v>22</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C64" s="3">
+        <v>2</v>
+      </c>
+      <c r="D64" s="3">
         <v>22</v>
-      </c>
-      <c r="D64" s="3">
-        <v>2202</v>
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>148</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G64" s="4"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="3">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>149</v>
@@ -5652,7 +5683,7 @@
         <v>22</v>
       </c>
       <c r="D65" s="3">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3" t="s">
@@ -5668,22 +5699,24 @@
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="3">
-        <v>23</v>
+        <v>2202</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>151</v>
       </c>
       <c r="C66" s="3">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D66" s="3">
-        <v>23</v>
+        <v>2202</v>
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G66" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>152</v>
+      </c>
       <c r="H66" s="4"/>
       <c r="I66" s="4" t="s">
         <v>151</v>
@@ -5691,41 +5724,41 @@
     </row>
     <row r="67" spans="1:9">
       <c r="A67" s="3">
-        <v>2301</v>
+        <v>2203</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C67" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D67" s="3">
-        <v>2301</v>
+        <v>2203</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H67" s="4"/>
       <c r="I67" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="3">
-        <v>2302</v>
+        <v>23</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>75</v>
+        <v>155</v>
       </c>
       <c r="C68" s="3">
+        <v>2</v>
+      </c>
+      <c r="D68" s="3">
         <v>23</v>
-      </c>
-      <c r="D68" s="3">
-        <v>2302</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3" t="s">
@@ -5734,77 +5767,77 @@
       <c r="G68" s="4"/>
       <c r="H68" s="4"/>
       <c r="I68" s="4" t="s">
-        <v>75</v>
+        <v>155</v>
       </c>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="3">
-        <v>23021</v>
+        <v>2301</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C69" s="3">
-        <v>2302</v>
+        <v>23</v>
       </c>
       <c r="D69" s="3">
-        <v>23021</v>
+        <v>2301</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H69" s="4"/>
       <c r="I69" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="3">
-        <v>23022</v>
+        <v>2302</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>156</v>
+        <v>75</v>
       </c>
       <c r="C70" s="3">
+        <v>23</v>
+      </c>
+      <c r="D70" s="3">
         <v>2302</v>
-      </c>
-      <c r="D70" s="3">
-        <v>23022</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>157</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G70" s="4"/>
       <c r="H70" s="4"/>
       <c r="I70" s="4" t="s">
-        <v>156</v>
+        <v>75</v>
       </c>
     </row>
     <row r="71" spans="1:9">
       <c r="A71" s="3">
-        <v>2303</v>
+        <v>23021</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>158</v>
       </c>
       <c r="C71" s="3">
-        <v>23</v>
+        <v>2302</v>
       </c>
       <c r="D71" s="3">
-        <v>2303</v>
+        <v>23021</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G71" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>159</v>
+      </c>
       <c r="H71" s="4"/>
       <c r="I71" s="4" t="s">
         <v>158</v>
@@ -5812,41 +5845,41 @@
     </row>
     <row r="72" spans="1:9">
       <c r="A72" s="3">
-        <v>23031</v>
+        <v>23022</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="C72" s="3">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="D72" s="3">
-        <v>23031</v>
+        <v>23022</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H72" s="4"/>
       <c r="I72" s="4" t="s">
-        <v>65</v>
+        <v>160</v>
       </c>
     </row>
     <row r="73" spans="1:9">
       <c r="A73" s="3">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>74</v>
+        <v>162</v>
       </c>
       <c r="C73" s="3">
         <v>23</v>
       </c>
       <c r="D73" s="3">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3" t="s">
@@ -5855,285 +5888,283 @@
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4" t="s">
-        <v>74</v>
+        <v>162</v>
       </c>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" s="3">
-        <v>23041</v>
+        <v>23031</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="C74" s="3">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="D74" s="3">
-        <v>23041</v>
+        <v>23031</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H74" s="4"/>
       <c r="I74" s="4" t="s">
-        <v>160</v>
+        <v>65</v>
       </c>
     </row>
     <row r="75" spans="1:9">
-      <c r="A75" s="3">
-        <v>23042</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="C75" s="3">
-        <v>2304</v>
-      </c>
-      <c r="D75" s="3">
-        <v>23042</v>
-      </c>
-      <c r="E75" s="3"/>
-      <c r="F75" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="H75" s="4"/>
-      <c r="I75" s="4" t="s">
-        <v>162</v>
+      <c r="A75" s="7">
+        <v>23032</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="C75" s="9">
+        <v>2303</v>
+      </c>
+      <c r="D75" s="9">
+        <v>23032</v>
+      </c>
+      <c r="E75" s="9"/>
+      <c r="F75" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="H75" s="8"/>
+      <c r="I75" s="8" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="76" spans="1:9">
       <c r="A76" s="3">
-        <v>23043</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>164</v>
+        <v>2304</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>74</v>
       </c>
       <c r="C76" s="3">
+        <v>23</v>
+      </c>
+      <c r="D76" s="3">
         <v>2304</v>
-      </c>
-      <c r="D76" s="3">
-        <v>23043</v>
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G76" s="7" t="s">
-        <v>165</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G76" s="4"/>
       <c r="H76" s="4"/>
-      <c r="I76" s="7" t="s">
-        <v>164</v>
+      <c r="I76" s="4" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="77" spans="1:9">
       <c r="A77" s="3">
-        <v>23044</v>
-      </c>
-      <c r="B77" s="7" t="s">
+        <v>23041</v>
+      </c>
+      <c r="B77" s="4" t="s">
         <v>166</v>
       </c>
       <c r="C77" s="3">
         <v>2304</v>
       </c>
       <c r="D77" s="3">
-        <v>23044</v>
+        <v>23041</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G77" s="7" t="s">
+      <c r="G77" s="4" t="s">
         <v>167</v>
       </c>
       <c r="H77" s="4"/>
-      <c r="I77" s="7" t="s">
+      <c r="I77" s="4" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" s="3">
-        <v>23045</v>
-      </c>
-      <c r="B78" s="7" t="s">
+        <v>23042</v>
+      </c>
+      <c r="B78" s="4" t="s">
         <v>168</v>
       </c>
       <c r="C78" s="3">
         <v>2304</v>
       </c>
       <c r="D78" s="3">
-        <v>23045</v>
+        <v>23042</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G78" s="7" t="s">
+      <c r="G78" s="4" t="s">
         <v>169</v>
       </c>
       <c r="H78" s="4"/>
-      <c r="I78" s="7" t="s">
+      <c r="I78" s="4" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="3">
-        <v>23046</v>
-      </c>
-      <c r="B79" s="7" t="s">
+        <v>23043</v>
+      </c>
+      <c r="B79" s="6" t="s">
         <v>170</v>
       </c>
       <c r="C79" s="3">
         <v>2304</v>
       </c>
       <c r="D79" s="3">
-        <v>23046</v>
+        <v>23043</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G79" s="7" t="s">
+      <c r="G79" s="6" t="s">
         <v>171</v>
       </c>
       <c r="H79" s="4"/>
-      <c r="I79" s="7" t="s">
+      <c r="I79" s="6" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="80" spans="1:9">
       <c r="A80" s="3">
-        <v>23047</v>
-      </c>
-      <c r="B80" s="4" t="s">
+        <v>23044</v>
+      </c>
+      <c r="B80" s="6" t="s">
         <v>172</v>
       </c>
       <c r="C80" s="3">
         <v>2304</v>
       </c>
       <c r="D80" s="3">
-        <v>23047</v>
+        <v>23044</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G80" s="4" t="s">
+      <c r="G80" s="6" t="s">
         <v>173</v>
       </c>
       <c r="H80" s="4"/>
-      <c r="I80" s="4" t="s">
+      <c r="I80" s="6" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="3">
-        <v>2305</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>111</v>
+        <v>23045</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>174</v>
       </c>
       <c r="C81" s="3">
-        <v>23</v>
+        <v>2304</v>
       </c>
       <c r="D81" s="3">
-        <v>2305</v>
+        <v>23045</v>
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G81" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G81" s="6" t="s">
+        <v>175</v>
+      </c>
       <c r="H81" s="4"/>
-      <c r="I81" s="4" t="s">
-        <v>111</v>
+      <c r="I81" s="6" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="82" spans="1:9">
       <c r="A82" s="3">
-        <v>23051</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>174</v>
+        <v>23046</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>176</v>
       </c>
       <c r="C82" s="3">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="D82" s="3">
-        <v>23051</v>
+        <v>23046</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G82" s="4" t="s">
-        <v>175</v>
+      <c r="G82" s="6" t="s">
+        <v>177</v>
       </c>
       <c r="H82" s="4"/>
-      <c r="I82" s="4" t="s">
-        <v>174</v>
+      <c r="I82" s="6" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="3">
-        <v>23052</v>
+        <v>23047</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C83" s="3">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="D83" s="3">
-        <v>23052</v>
+        <v>23047</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H83" s="4"/>
       <c r="I83" s="4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="84" spans="1:9">
       <c r="A84" s="3">
-        <v>23053</v>
+        <v>2305</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>178</v>
+        <v>111</v>
       </c>
       <c r="C84" s="3">
+        <v>23</v>
+      </c>
+      <c r="D84" s="3">
         <v>2305</v>
-      </c>
-      <c r="D84" s="3">
-        <v>23053</v>
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G84" s="4" t="s">
-        <v>179</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G84" s="4"/>
       <c r="H84" s="4"/>
       <c r="I84" s="4" t="s">
-        <v>178</v>
+        <v>111</v>
       </c>
     </row>
     <row r="85" spans="1:9">
       <c r="A85" s="3">
-        <v>23054</v>
+        <v>23051</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>180</v>
@@ -6142,7 +6173,7 @@
         <v>2305</v>
       </c>
       <c r="D85" s="3">
-        <v>23054</v>
+        <v>23051</v>
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="3" t="s">
@@ -6158,7 +6189,7 @@
     </row>
     <row r="86" spans="1:9">
       <c r="A86" s="3">
-        <v>23055</v>
+        <v>23052</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>182</v>
@@ -6167,7 +6198,7 @@
         <v>2305</v>
       </c>
       <c r="D86" s="3">
-        <v>23055</v>
+        <v>23052</v>
       </c>
       <c r="E86" s="3"/>
       <c r="F86" s="3" t="s">
@@ -6183,7 +6214,7 @@
     </row>
     <row r="87" spans="1:9">
       <c r="A87" s="3">
-        <v>23056</v>
+        <v>23053</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>184</v>
@@ -6192,7 +6223,7 @@
         <v>2305</v>
       </c>
       <c r="D87" s="3">
-        <v>23056</v>
+        <v>23053</v>
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="3" t="s">
@@ -6208,244 +6239,319 @@
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="3">
-        <v>2306</v>
+        <v>23054</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>92</v>
+        <v>186</v>
       </c>
       <c r="C88" s="3">
-        <v>23</v>
+        <v>2305</v>
       </c>
       <c r="D88" s="3">
-        <v>2306</v>
+        <v>23054</v>
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G88" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>187</v>
+      </c>
       <c r="H88" s="4"/>
       <c r="I88" s="4" t="s">
-        <v>92</v>
+        <v>186</v>
       </c>
     </row>
     <row r="89" spans="1:9">
       <c r="A89" s="3">
-        <v>23061</v>
+        <v>23055</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C89" s="3">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="D89" s="3">
-        <v>23061</v>
+        <v>23055</v>
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H89" s="4"/>
       <c r="I89" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="90" spans="1:9">
       <c r="A90" s="3">
-        <v>24</v>
+        <v>23056</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C90" s="3">
-        <v>2</v>
+        <v>2305</v>
       </c>
       <c r="D90" s="3">
-        <v>24</v>
-      </c>
-      <c r="E90" s="4"/>
+        <v>23056</v>
+      </c>
+      <c r="E90" s="3"/>
       <c r="F90" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G90" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>191</v>
+      </c>
       <c r="H90" s="4"/>
       <c r="I90" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="91" spans="1:9">
       <c r="A91" s="3">
-        <v>2401</v>
+        <v>2306</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>189</v>
+        <v>92</v>
       </c>
       <c r="C91" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D91" s="3">
-        <v>2401</v>
-      </c>
-      <c r="E91" s="4"/>
+        <v>2306</v>
+      </c>
+      <c r="E91" s="3"/>
       <c r="F91" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G91" s="4" t="s">
-        <v>190</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G91" s="4"/>
       <c r="H91" s="4"/>
       <c r="I91" s="4" t="s">
-        <v>189</v>
+        <v>92</v>
       </c>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" s="3">
-        <v>25</v>
+        <v>23061</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C92" s="3">
-        <v>2</v>
+        <v>2306</v>
       </c>
       <c r="D92" s="3">
-        <v>25</v>
-      </c>
-      <c r="E92" s="4"/>
+        <v>23061</v>
+      </c>
+      <c r="E92" s="3"/>
       <c r="F92" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G92" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>193</v>
+      </c>
       <c r="H92" s="4"/>
       <c r="I92" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="93" spans="1:9">
       <c r="A93" s="3">
-        <v>2501</v>
+        <v>24</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C93" s="3">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D93" s="3">
-        <v>2501</v>
-      </c>
-      <c r="E93" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="E93" s="4"/>
       <c r="F93" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G93" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="H93" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="G93" s="4"/>
+      <c r="H93" s="4"/>
       <c r="I93" s="4" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
     </row>
     <row r="94" spans="1:9">
       <c r="A94" s="3">
-        <v>2502</v>
+        <v>2401</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C94" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D94" s="3">
-        <v>2502</v>
-      </c>
-      <c r="E94" s="3"/>
+        <v>2401</v>
+      </c>
+      <c r="E94" s="4"/>
       <c r="F94" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="H94" s="5"/>
-      <c r="I94" s="5" t="s">
-        <v>193</v>
+        <v>196</v>
+      </c>
+      <c r="H94" s="4"/>
+      <c r="I94" s="4" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="95" spans="1:9">
       <c r="A95" s="3">
-        <v>2503</v>
+        <v>25</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C95" s="3">
+        <v>2</v>
+      </c>
+      <c r="D95" s="3">
         <v>25</v>
       </c>
-      <c r="D95" s="3">
-        <v>2503</v>
-      </c>
-      <c r="E95" s="3"/>
+      <c r="E95" s="4"/>
       <c r="F95" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G95" s="4" t="s">
-        <v>196</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G95" s="4"/>
       <c r="H95" s="4"/>
       <c r="I95" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="96" spans="1:9">
       <c r="A96" s="3">
-        <v>26</v>
+        <v>2501</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C96" s="3">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D96" s="3">
-        <v>26</v>
+        <v>2501</v>
       </c>
       <c r="E96" s="3"/>
       <c r="F96" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G96" s="4"/>
-      <c r="H96" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="H96" s="3"/>
       <c r="I96" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="3">
+        <v>2502</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C97" s="3">
+        <v>25</v>
+      </c>
+      <c r="D97" s="3">
+        <v>2502</v>
+      </c>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G97" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="H97" s="5"/>
+      <c r="I97" s="5" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="A98" s="3">
+        <v>2503</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C98" s="3">
+        <v>25</v>
+      </c>
+      <c r="D98" s="3">
+        <v>2503</v>
+      </c>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="H98" s="4"/>
+      <c r="I98" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="A99" s="3">
+        <v>26</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C99" s="3">
+        <v>2</v>
+      </c>
+      <c r="D99" s="3">
+        <v>26</v>
+      </c>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G99" s="4"/>
+      <c r="H99" s="4"/>
+      <c r="I99" s="4" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
+      <c r="A100" s="3">
         <v>2601</v>
       </c>
-      <c r="B97" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="C97" s="3">
+      <c r="B100" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C100" s="3">
         <v>26</v>
       </c>
-      <c r="D97" s="3">
+      <c r="D100" s="3">
         <v>2601</v>
       </c>
-      <c r="E97" s="4"/>
-      <c r="F97" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G97" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="H97" s="4"/>
-      <c r="I97" s="4" t="s">
-        <v>198</v>
+      <c r="E100" s="4"/>
+      <c r="F100" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="H100" s="4"/>
+      <c r="I100" s="4" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>
